--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-534.4880000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.21877e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.479</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.498064984013751</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.13056517263901</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.54534966393635</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.709603545391055</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.67345789147953</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.48389126762358</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 22.757x + -11487.078</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>449.7324770182993</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>25508394.88950895</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.62768174120501e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.955140847797822</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-526.9590000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.21706e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.53100000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.615822070002371</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.30971990842309</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.657069891783118</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.312833693690826</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.98943798105245</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.54226836466799</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 23.298x + -11672.048</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>445.5630252428553</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1224831969.763895</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.620562417888693e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9556096219366563</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-524.96</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.21654e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.57599999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3759338438155597</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.266491423414512</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.309548961343252</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.625008559950261</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.11067964817921</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.54356734158762</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 23.310x + -11511.178</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>440.57200342307</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>361524904.7141443</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.613412393773471e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9562246042062298</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-526.364</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.21681e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.614</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7278953813868868</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.111526830766749</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.092392684115601</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.05296493605384</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.50876778046046</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 22.984x + -11131.443</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>434.918939654659</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>238070481.8131202</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.60843052491533e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9567341285612617</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-520.1990000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.21714e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.657</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4239175232880282</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.418244385936854</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.534634398464361</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.661322897361482</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.26360988055358</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.5734402858692</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 23.598x + -11316.365</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>428.9805326930563</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>351951834.0520582</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.602996283743558e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9572967929544706</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-518.6220000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.21763e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.343806164094166</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.028813004435182</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.304540802828944</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.685005772423159</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26.37018502618132</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.57321150208318</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 23.596x + -11120.506</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>374.8204554599633</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14040.15174975307</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.785913493309581e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9998481834460772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-516.563</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.21797e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-85.74299999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2465965043653856</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7742734912069574</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.204670621169021</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.406985535341656</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.44237205809437</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.57396297053552</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 23.603x + -10928.846</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>365.6853465029369</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>13851.35162018206</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.838755169454749e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9999420541558588</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-512.7569999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.21849e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-85.77500000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.592475060556911</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.549254021929868</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.618783363779842</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.098627842702488</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26.52515620004833</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.6201997380898</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 24.062x + -11028.155</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>411.4825982516712</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1122631804.411305</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.589030786070383e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9588133068477264</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-512.318</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.2186e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-85.812</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4121955186703252</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.233672573071515</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.668458148705125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.349063866725893</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.57090745224842</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.62176336246442</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 24.078x + -10849.981</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>405.9777884499951</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>886428826.5764951</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.584028753299632e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9593157670007468</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-511.091</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.21908e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.848</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2590538658664723</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.091883927589709</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.437694252952816</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.335138704223782</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.50995549484729</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.62426279911098</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 24.103x + -10685.706</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>400.6059495363203</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>874389240.8724992</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57980590450597e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9597884190171528</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-594.6099999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.3932e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.14100000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.475774105996191</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.340798365733638</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.382780009481888</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.03928351258479</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.35271666777359</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.75361082380941</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 17.630x + -10237.775</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>407.7709143410224</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12545.18482610068</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.002963919265197e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998150281767894</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-570.276</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.38816e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.389</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04694676317254729</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.771695213200041</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.085177194395737</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.746459548249609</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.16123754457142</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.86801453331059</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 18.276x + -10225.800</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>410.8387029075576</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12284.97353287469</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.033548430802535e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9994891820039503</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-552.707</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.3855e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.54000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1850965405114281</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.147893602295457</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.276609371526637</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.145533763439372</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.06246853764968</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.99463662222448</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 19.047x + -10455.185</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>484.8266879074271</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>796366444.8808361</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.990652598113316e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9440582907179439</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-542.926</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.38423e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.642</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09669975221970598</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8256110082463605</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.182731477283581</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.872594246667172</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.25437825847916</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.05229228180562</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 19.420x + -10473.118</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>478.6725991689934</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>523856921.0771014</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.967874488134689e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9456830340559175</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-531.1940000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.38341e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.72499999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6335791408776297</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.484297514765185</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.002531433575686</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.710192882424346</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.96151564682213</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.1484519955907</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 20.076x + -10723.716</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>472.7228914409149</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>517460373.484095</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.951177372400178e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9468978798471355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-527.6370000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.3832e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.79000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2772725054151764</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.278317337541601</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.596067949537625</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.344036184494658</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.10891866197506</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.15410263922493</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 20.116x + -10561.928</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>466.789279425025</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1022527497.358744</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.939213991495241e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9478156635032924</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-526.0029999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.38292e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.846</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3371762925458369</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.013924433197723</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.43869779539055</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.302741488649794</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.19344868475416</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.15259833623313</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 20.106x + -10382.571</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>460.807216954542</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>32032887.50010811</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.926628158384923e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9487789283146691</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-523.126</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.38276e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.901</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.120312834783556</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9116036561180713</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.144913857574066</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.77475913896488</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.17191207971772</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.16967435030494</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 20.227x + -10284.413</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>454.8255420182748</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>373621188.1538545</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.918950822923622e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9493776349719382</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-516.7430000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.38275e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.96599999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1636217802792677</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.096067955142881</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.417222021543542</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.864394796488423</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23.34335892261344</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.21713930138537</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 20.573x + -10323.957</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>448.7143466524704</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>122915166.3643759</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.908091545169312e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9502431792854391</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-510.6849999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.38246e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.01900000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.738026075196713</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.632282004893971</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.94876068170361</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.815732595296071</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.8487517607747</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.28212837708256</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 21.065x + -10463.504</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>442.5118569111033</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>242129805.007102</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.898921551635108e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9509534874983399</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-512.443</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.38252e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-85.07599999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7391401177011701</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.968595493828279</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.585611969117083</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.5388302555615</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.21878386703551</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.585x + -9974.061</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>385.3947832595061</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14512.37229573186</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.837559702970311e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9999959393445056</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-507.227</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.38252e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.127</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2715608159208113</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.305258456062109</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.376470415448587</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.311155078345822</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.94836444987298</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.28312877332847</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 21.073x + -10103.122</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>430.6108211227326</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>32925772.60776133</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.879020514223816e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9525751409833911</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-499.864</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.38236e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.188</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7016771247678796</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.469482987166348</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.968066630154539</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.680085860792805</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24.32197932690363</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.3412444748015</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 21.534x + -10203.679</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>424.82509227475</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>350350998.1575538</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.87167093282658e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9531575649746007</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-498.795</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.38235e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.23999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2809168972164609</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.176690574905693</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.137352179047209</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.981282355905681</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24.1586797275439</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.32769129915327</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 21.425x + -9962.520</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>419.2251962838653</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>917008079.7492678</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.863720582175968e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9538076613799175</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-496.293</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.38211e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.29600000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.09617405587563245</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7306858390665311</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.105656533393577</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.150539355246621</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24.42343665120592</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.32683850046057</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 21.418x + -9779.586</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>413.475995297416</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>169918089.9228762</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.854355722526172e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9545528211312724</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-493.8939999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.38191e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.34</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1634627236718083</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9053999980693651</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.210340920245432</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.89697110336235</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.38769466395458</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.35856119094636</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.676x + -9762.715</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>407.8608773168519</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>334897920.0237986</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.847148475461929e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9551346450905175</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-488.158</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.38217e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.393</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3959331006745198</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.12444271927814</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.689852375216731</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.553662756328057</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.81134427145725</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.40076229016793</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 22.028x + -9791.802</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>402.1940793513439</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>329347362.2599905</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.839783417340264e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9557721635545577</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-487.021</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.38204e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.437</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3419375932295302</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.084158237929219</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.613375277855167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.188023407280983</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24.81346526841397</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.41476181194837</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 22.148x + -9688.697</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>386.2119766468502</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3254.195744528191</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.870003710897893e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8676658522992389</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-483.2900000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.38201e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.488</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3894763862806926</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.195977061298191</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.639990820451866</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.186855874680746</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24.97210622964122</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.43925964484517</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 22.360x + -9628.026</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>390.8372265071988</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>854551446.8637075</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.825029071544421e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9569949429779769</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-480.167</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.38224e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.535</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4796944412396227</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.222430354674741</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.579462796360525</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.399082055532102</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25.09746798441813</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.46225202544657</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 22.563x + -9567.236</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>383.9009836199369</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9807.638003366283</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.695082237132001e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9962364533543676</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-478.583</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.38183e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.58199999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1336079939815636</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8549879087056381</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.253063567280239</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.259235063803729</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25.14070926973163</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.46557665444269</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.592x + -9408.347</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>379.7667170734993</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>414478115.7529508</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.810659795871835e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9581947374788823</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-730.5890000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.26222e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.042</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02006141162594387</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6813320833303445</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.707953526058151</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.480321398676549</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.99694208181844</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.43059951118163</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 16.031x + -9422.929</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>404.7456383436996</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12663.70046711942</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.961351237379376e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9989956283335211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-629.728</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.24867e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.63800000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2762480576915456</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.066072704473001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.257522493590164</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.659652668156382</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.09300658904428</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.94673674351195</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 18.748x + -10697.829</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>497.361488090615</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>272500641.6775718</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.803074358482611e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9431919351530109</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-587.9839999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.24229e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.883</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7168368032680483</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.642542448772186</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.829883268286677</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.50600067035771</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.84349840746794</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.1843403406146</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 20.333x + -11461.020</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>490.9292903205533</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>538263103.0608996</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.755091809728803e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9465185824057925</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-572.425</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.23792e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2031251485576933</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.078695432394456</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.229066733129253</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.048984791357706</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23.62508192127668</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.2415026110381</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.755x + -11453.904</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>485.1270312468699</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>531599230.7145907</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.724789585196178e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9486443685463221</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-559.0870000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.23538e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.136</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03395802345199635</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9319088656741357</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.111161901781046</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.356790024948748</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.34239052383703</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.30334346330827</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.231x + -11541.563</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>479.8626264619209</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>525484866.432004</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.704402094990969e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.950147569215644</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-553.617</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.2336e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.20099999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1329775345315374</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7097266183052781</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.997218785342924</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.062876720936861</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.50968509135404</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.33059210203039</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 21.448x + -11500.888</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>474.607936270931</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>268881413.8394894</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.69132117389684e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.951114823638282</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-547.098</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.23243e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-85.27</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08366829408212841</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7393174921803723</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.970054884312112</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.633529961926851</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.75138470299545</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.35871986952019</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 21.677x + -11462.620</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>469.2907598083517</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>390544936.1868502</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.679658385701025e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9520256578241579</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-541.05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.23148e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-85.324</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2351602019831642</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9440310824274031</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.422868039114056</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.255352333376808</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.1598097739164</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.40757389299669</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 22.086x + -11547.341</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>463.8590223891536</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>797670753.2086676</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.669914090478229e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9528012917036756</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-539.068</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.23045e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-85.378</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1330945602294581</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8811545346006974</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.068586909892362</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.01340445945948</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.23352874722596</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.40392988344449</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 22.055x + -11339.343</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>435.1470132697332</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19065.49048632301</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.616785888729669e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9998625505853346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-531.1100000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.23009e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.432</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4376277717160629</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.183673057268587</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.232100154517358</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.363768364743894</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25.50777088932153</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.48002114924114</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 22.722x + -11575.923</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>452.3540705714025</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>494654973.0891057</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.652048056888331e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9542824025188228</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-526.4350000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.22943e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-85.494</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1966747041883397</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9134407392466988</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.304483691803782</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.990541152965071</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25.69701343928157</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.48528646505123</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 22.770x + -11402.433</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>446.739680857137</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>977203389.2654747</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.642619133738038e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9550794879471066</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-523.701</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.22922e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.536</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3807435652225644</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.195777418575569</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.543820356756943</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.370227939882775</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.92292508756285</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.51266748418475</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 23.021x + -11384.850</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>441.2043787231522</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>362173327.5330236</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.636429486747324e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9556287687657727</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-521.796</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.22883e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.58799999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.05021640564264288</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6401151916227621</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.907868985058256</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.834980755357262</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.98172781645002</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.49221507848974</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 22.833x + -11079.838</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>435.8325133960838</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>242216250.6369408</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.628753421057765e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9563015006871644</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-520.264</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.22869e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.616</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.139709482255082</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.835509936486323</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.306556527966307</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.410321456584334</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26.13340088562437</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.51352262591496</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 23.028x + -11044.369</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>430.6467462647433</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>353121807.6940942</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.624473674092704e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9566933676713527</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-513.326</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.22842e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.666</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4287646241859284</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.237987456612016</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.491203568809191</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.537775901320875</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.3653022063356</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.57432410905598</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 23.606x + -11222.442</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>425.5678611514442</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>465815180.7540883</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.617788793708483e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9572855097640788</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-510.871</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.22817e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.708</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3865148380764288</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.081118707873803</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.424469058195723</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.359618002481254</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26.41190443918372</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.58786958777797</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 23.739x + -11128.241</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>365.2967479947008</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>13962.29282862893</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.800072698738132e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9998822223013989</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-509.14</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.22823e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.747</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4382917020114817</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.006561296247088</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.475784677602883</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.546300417133263</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26.59395066007152</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.59321992049954</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 23.792x + -10991.061</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>365.7437024421812</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13793.30733250387</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.873980059352311e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9997707903807902</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-506.6079999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.22813e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.786</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4026974429185312</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.012567217288507</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.427655325333039</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.842658370462146</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26.74030907279414</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.60104075517688</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 23.870x + -10865.366</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>410.4845870465296</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>28480514.64362854</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.598592026793065e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9590819315809704</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-501.851</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.22799e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.834</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1870615141255193</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9420821154372865</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.322813455832535</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.610268182771206</v>
+      </c>
+      <c r="J20" t="n">
+        <v>26.93514943143227</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.62590043864432</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 24.120x + -10830.897</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>405.5357371961852</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>332667321.6845441</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.594754498883078e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9594389673524796</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-498.518</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.22782e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.86799999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5226983461511077</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.326017170318513</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.705209874580485</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.318176688153188</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27.08265147976215</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.66290251126932</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 24.502x + -10889.839</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>400.6292131971126</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>656494006.9787445</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.589969247623025e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9598792407823505</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-495.9690000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.22782e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.90600000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6525958339876212</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.344528814498283</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.661386503885761</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.086375350911268</v>
+      </c>
+      <c r="J22" t="n">
+        <v>27.1659141625917</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.67765532804282</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 24.658x + -10810.363</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>395.7406033550092</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>647991773.7160977</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.585264482049269e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9603345422969221</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1281.649</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.33531e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.646</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3997101335746112</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9579531812400802</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.735497319427433</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.323191850930975</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.339553448209161</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.61148465490307</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.931x + -5726.099</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>418.0204060570979</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13280.29912317816</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.782262012239833e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9996037780309371</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1014.249</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.33344e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.31100000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5967151955278622</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.679509173521366</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.476501196981239</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.98563313399784</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.91405985065113</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.236x + -6518.576</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>406.9356579485685</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12685.62596056101</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.840975831861445e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9998888089043908</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-871.2990000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.31803e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.16500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04418395448903512</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8406701237290288</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.149325092385044</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.663839249465283</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.16753972167822</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.66840459879103</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.202x + -7485.111</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>402.9730350635263</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>12462.25431193797</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.890058265048753e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9996584835899288</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-788.005</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.30535e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.69799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0502142075191835</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3797962221137179</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.801349248435532</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.454533421364928</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15.9366079875371</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.07286087970242</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.567x + -8087.333</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>491.6636738253705</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>269674749.3423757</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.015777721681117e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9331563818601806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-727.855</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.29573e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.039</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5233815184556738</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.265704394096411</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.464744512004526</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.507658125371115</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.43268953513221</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.43320913555776</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.043x + -8860.775</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>485.9214518122515</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>399597565.6290065</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.944049037367472e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9375121193153352</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-693.7180000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.28854e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.292</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.076969724710381</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.107292483000662</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.990187261550909</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.46852211007045</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.58621265841869</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.764x + -9077.781</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>479.976610980483</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>197206831.3016371</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.892266163094472e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9407542024929905</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-662.2670000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.28259e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.48699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6005000136375176</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.50258524869654</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.449600726062259</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.469345186179327</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.40775849416005</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.77606535230156</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.753x + -9520.059</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>473.6629101608175</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>130250474.9436368</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.852393989027738e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9432845055454072</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-648.511</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.2785e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.639</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06845624205007139</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4906574316985448</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.898076374934577</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.850772477552279</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.01685330212042</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.80329664906893</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.905x + -9359.790</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>467.1998543859579</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>384480061.2012399</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.823038878499942e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9452261901838206</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-627.042</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.27535e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.768</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3844162719373275</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.355443940790754</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.419399196025323</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.331231812774295</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.69534187491804</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.95602581339388</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.805x + -9755.057</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>441.4782816300599</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19176.86040800497</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.619796231614761e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9998890413369721</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-616.804</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.27265e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.88</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1701202404786945</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8702167958898136</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.139342119021276</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.955301753832355</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.13439463484062</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.98779446968977</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.004x + -9649.280</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>454.1850923297379</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>255881195.3342048</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.777501202237959e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9483804323038032</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-851.3280000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.31674e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.20099999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3544044141700317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.240948333529991</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.351081730863987</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.158546604184598</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.61755631499368</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.75686995902248</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.478x + -7844.419</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>406.6757508190286</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12642.56926853817</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.924358387235392e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9997028775464016</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-730.226</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.29589e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.946</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5999897874378282</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.352317126395047</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.490257460014134</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.039347227454787</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.37420708027346</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.40086647281839</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.898x + -9073.048</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>403.7519722451961</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12432.76348186441</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.149230094569739e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9997357816521073</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-674.1719999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.28507e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.324</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1698237576725094</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.180341544415037</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.327529705965993</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.195336681214826</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.20239856177039</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.68099121148317</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.244x + -9633.594</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>491.0772645139172</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>135072206.8318982</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.890940657958642e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9403958798607552</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-640.63</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.27906e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.529</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5454179952246183</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.398937973783689</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.727365961141865</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.737049762833533</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.31473087706724</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.87281736834721</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.304x + -10133.097</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>486.5792081841189</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1066030428.940031</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.848622104889686e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9431254484829242</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-622.0419999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2756e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.65600000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6468688324261942</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.431477444353858</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.535392329224563</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.18396786692971</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.81016608073797</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.97273533993433</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.909x + -10350.661</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>481.3002605669151</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>131931694.6908549</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.822322986399571e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9448907885277107</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-609.261</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.27313e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.77200000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3798237901184996</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.229116883733857</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.614935696077886</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.526548905527156</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.50313580674187</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.02392868172051</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 19.235x + -10352.622</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>475.5761945644315</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>390898171.2236999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.800972400513979e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9463967156440627</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-600.997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.27132e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.866</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1235251076517488</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9754441742102534</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.872187948900396</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.710947272191799</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.7234467247179</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.04530412314432</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.374x + -10236.732</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>469.4991716414882</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>128941831.0295638</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.783459648837793e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9476695140069712</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-593.579</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.26985e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.93899999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2194417997159607</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.023845494173272</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.126436183806898</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.783635213303251</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.00509831412915</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.08828942822355</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.661x + -10235.420</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>463.4254608838797</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>380876671.3098059</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.769803435356875e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9486745646100498</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-584.5350000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.26859e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-85.026</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2266007871599048</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7975615402076944</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.92268743175522</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.920602720443727</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.40619861057819</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.12680688794293</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.925x + -10204.356</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>452.3551432983907</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19033.55547754413</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.57660098914171e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9999173347112819</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-574.345</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.26796e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.096</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4205543320746853</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.271799809568574</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.554690850673257</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.403377152249709</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.79974487726218</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.21278467146085</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 20.540x + -10422.603</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>451.4474092345619</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>247499140.3841373</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.743270847449702e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9507432195730967</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-571.0279999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.26736e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-85.155</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2535042373929217</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9700550319072805</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.19006491689411</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.124252942047283</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22.92222518536044</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.21836579054334</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.582x + -10263.565</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>445.7804411165236</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1218887979.656995</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.733676593565875e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9515292137810646</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-563.518</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.26678e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.22</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3624341700110033</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.227086479201673</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.369425581267661</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.75240656818286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.34193895378793</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.26918221924089</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 20.965x + -10325.783</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>440.2005039536013</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>481573007.1813665</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.723032509058292e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9524001624491674</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-556.8129999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.26634e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.285</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2727990876512653</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.096057014803005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.301491138172305</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.987584661558331</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23.51356602066616</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.29428391070608</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 21.160x + -10263.641</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>434.723897092129</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>237769632.4421493</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.712948978600426e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9532413970005716</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-552.0430000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.26593e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.33799999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5455520381181017</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.160940591579517</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.405711564648111</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.327624614454526</v>
+      </c>
+      <c r="J15" t="n">
+        <v>23.69331796829992</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.32539904225365</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 21.407x + -10241.786</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>371.2507098873601</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14271.00293336709</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.830378588769889e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9999349518940444</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-548.376</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.26532e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.39100000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3015502624735869</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9661854673862428</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.12152435412739</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.093404841174725</v>
+      </c>
+      <c r="J16" t="n">
+        <v>23.86988557308976</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.33485663091844</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 21.483x + -10115.925</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>370.5408170808202</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14088.60709471307</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.866074475234489e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9999189357108623</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-545.372</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.26501e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.44</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.156884837427829</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8603255926133673</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.306880512467143</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.231890674690672</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.07675127273935</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.34918501267336</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.599x + -10017.243</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>418.7338970947847</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>228612614.3248598</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.688584923609476e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9552802430315779</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-540.278</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.26465e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.492</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3006683079209203</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.041138244082948</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.099587729303634</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.989572779915354</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.19251502075264</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.38391162875087</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.886x + -10020.238</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>413.399184936012</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>225758056.4968992</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.68121973185646e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9559048362101588</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-535.605</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.26436e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.538</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4456952176819545</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.274863190948975</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.307591231035479</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.527706771257221</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24.46852268750228</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.4219028213531</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 22.209x + -10042.574</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>408.0633665346227</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>122370120.8085435</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.673873645501824e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9565441026080619</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-527.046</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.26448e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.604</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4160785005036447</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.232299277192768</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.778803121870737</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.998402178870927</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24.85712647448448</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.46456485809695</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 22.583x + -10071.807</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>396.6682220815492</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>15040.31542558245</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.716931347568358e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9999999763913315</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-528.6500000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.26408e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.63</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4452103540508591</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.143570692945262</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.272634424652358</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.529323469763023</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24.69904286047521</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.46018208192284</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 22.544x + -9901.441</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>397.5219674641309</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>542188241.5899316</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.661870710057581e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9576145308456261</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-520.4110000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.26399e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.691</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5754502226072059</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.546719961598293</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7608144066603</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.068726595157379</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25.11667288035622</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.50748958817188</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.973x + -9956.995</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>375.5911874316374</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3216.194448504606</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.15235095117835e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.7292236451365459</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1440.061</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.39652e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.28100000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1146316828067182</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7840212850958661</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.697444560885033</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.073637778868484</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7.854044009088873</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.43146814434007</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.526x + -4906.653</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>429.6230202017823</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13632.91162896371</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.76095697154734e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9997723017464323</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1093.85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.38938e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.46299999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4167006627657125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9941867980624347</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.973418795610133</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.363233524614934</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10.51004439527396</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.2843643292851</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.991x + -5956.536</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>418.3909006030254</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>13015.70243212981</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.858001589130673e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9999042869934802</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-922.6510000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.36576e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.57899999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1407654690218086</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9307829421784474</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.063164701408363</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.568052484173761</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.83533003890617</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.23755006454805</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.003x + -6971.035</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>415.9180064078726</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>12778.77446574732</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.859463378083317e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9999991021158158</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-822.5970000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.34733e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.238</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1404552189876341</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8017318981992715</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.834684822075591</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.389232816537859</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.68142902309558</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.77015761713605</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.521x + -7715.469</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>411.2921404591351</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12610.20393195065</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.978829766619678e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9996175485744294</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-759.525</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.33341e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.655</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1916619688938439</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.092626031514734</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.434438776238661</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.056207040511231</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.26086172761088</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.13889687054176</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.817x + -8355.625</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>497.9991348708024</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>275902571.6437891</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.060720263312138e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9330450462422147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-719.095</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.32392e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.952</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1457133103712917</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8412103800271707</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.009707942309766</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.621480790823135</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.31945622839273</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.34544783306758</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.657x + -8663.689</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>491.2385879836768</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>235478182.0657036</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.99405388123095e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9369498524599772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-686.039</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.31695e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.18899999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1756337913171277</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8518660094531794</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.159353487492581</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.906418277217292</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.30343342044674</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.53091970359502</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.496x + -8980.051</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>484.2022281744278</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>265067634.3005174</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.943512660502939e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9400341856764237</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-662.4690000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.31155e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.36799999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1791496812357724</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9091043665810022</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.268333221349141</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.102262764286349</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.10213949443775</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.66738375692333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.173x + -9199.664</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>477.2630158202608</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>522997955.0189785</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.905462105206098e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9424188685858628</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-644.6530000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.30746e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.51900000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05044876704027373</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8641634560604031</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.180425159899577</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.830687712391539</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.70515488251706</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.7501538257503</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.611x + -9259.913</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>470.6356380197503</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>193889728.1771298</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.874661518942262e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9444193908480624</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-626.192</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.30443e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.642</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5249074740817415</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.420562082252159</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.488979276858108</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.345392384512293</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.27296710282083</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.8818227022586</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.357x + -9554.077</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>464.3983617687056</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>381171840.461351</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.85087056957529e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.946007829065397</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1157.117</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.42306e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.005</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05960886685827692</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8709805314737928</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.7609097573077</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.081471180612329</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.662577267808693</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.80803281961077</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.217x + -5330.651</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>406.5263877950339</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12642.72418967486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.902781240056709e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9999383188321949</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-810.874</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.35224e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.29000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3163668276813403</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.133183326842582</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.266481540846609</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.013847614041132</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.92152194812426</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.83759170343708</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.741x + -7786.253</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>402.5632672503307</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12428.16809904474</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.029988712923931e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9999110807662449</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-710.1270000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.32918e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.937</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4352094542020332</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.174014612661243</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.345899164330677</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.796160662782817</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.37911636378105</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.406450606668</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 15.923x + -8918.000</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>490.7816655345515</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>403831423.0850303</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.016494255454809e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.935798926456311</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-672.891</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.31922e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.221</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06213590705918972</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8535761500454822</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.861627189955541</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.419185027535506</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.55571192495933</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.59079509749448</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.786x + -9212.278</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>485.0273788493913</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>399159616.1825728</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.950740920061707e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9396962624956577</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-647.3280000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.31428e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.39100000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3800046835878143</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.431035218039846</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.470708251277147</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.14139108526691</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.47379097674646</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.76041595398152</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.667x + -9598.420</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>479.0293725002069</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>393594127.5226604</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.913407660562732e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9420708134570979</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-630.348</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.31122e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.533</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2700908663110408</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9498596209804127</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.474221101342276</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.137233657737396</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.06979569143826</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.84147896049464</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.122x + -9671.259</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>473.0622106069381</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>519419597.5195135</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.884529039014557e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9440308768844026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-617.6009999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.30908e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.629</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4265672169254108</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.448762354855692</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.516757373651028</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.057803782017665</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.4625132331745</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.92651739183607</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.624x + -9823.447</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>467.4286805380581</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>25998813.56134218</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.861501394209685e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9456611105861568</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-604.943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.30734e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.73099999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4552319842863794</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.404668005361177</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.59702826592178</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.095742839364547</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.89436060009053</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.99006427642644</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.018x + -9892.229</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>461.9733608989825</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>506282223.6626672</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.845545453528326e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9467734134339629</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-599.747</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.30613e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.807</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1505232608781688</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.023311427474708</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.15637139061261</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.869170013938338</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.20445953005314</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.00453847256939</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.110x + -9772.808</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>456.7392632204899</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>267490486.5192766</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.831211419317002e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9478254228755277</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-590.6779999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.30519e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.878</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3095322409849081</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.318337033220233</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.392839000933385</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.354463138623346</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.57882433494729</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.05765847991218</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.456x + -9835.282</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>431.5640462242851</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>18801.07281796883</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.597913339886611e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9999972783639973</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-579.7779999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.30417e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.959</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4395331992096812</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.115723509171313</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.543292030614381</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.219296245403276</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.89699663339411</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.12188335730089</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 19.891x + -9947.877</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>446.955114352198</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>244719590.4818788</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.804911603909267e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9498015790391859</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-577.5810000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.30343e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.014</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.08662598976392412</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8735530977319437</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.125929232164609</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.845522040166058</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22.01738011180716</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.11057003409572</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.813x + -9746.406</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>442.3124520156859</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>484349398.751979</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.795544539557422e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9505111675785279</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-568.876</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.30268e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.068</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6186418229937373</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.401735886956014</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.668824821116524</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.793499492043711</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22.39248186452674</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.19282027189048</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 20.394x + -9976.647</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>437.6535848804979</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>957617410.9524475</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.786284545913437e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9512147569789502</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-565.7079999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.3021e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.126</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.213950989592435</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8952682635437815</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.071429962429696</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.060564384534883</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.48740032788779</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.17991225279945</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.301x + -9758.860</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>376.286958931379</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14384.64403881321</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.795452761962009e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9999579292659954</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-557.674</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.30167e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.182</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4689698471852871</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.280552378852972</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.652732597872371</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.834665332889926</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.8867804894568</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.24525866733592</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 20.783x + -9909.661</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>375.0470348808144</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14226.21648973086</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.803149429303379e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9998326290590018</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-553.2089999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.30108e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.227</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5472879766288816</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.502814893312586</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.896157807703604</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.771292955259984</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22.97121833171535</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.28075196465225</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.055x + -9933.115</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>423.4207669624959</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>347168929.1431149</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.760298822197493e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9532664706814449</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-548.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.30087e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.286</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3225931628812211</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.293903811219536</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.546782545464775</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.508127662851948</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23.21463974109932</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.29584037462348</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.172x + -9841.999</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>418.6335670009601</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>116107200.4301946</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.751255444743452e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9540290363052227</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-546.596</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.30049e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.32899999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4504001942063772</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.018825339997433</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.217616778885624</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.145883526887121</v>
+      </c>
+      <c r="J19" t="n">
+        <v>23.28256993521964</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.29893838289193</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 21.197x + -9705.656</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>413.8931146539479</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>113545739.5923299</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.744172360890317e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9546077214151859</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-542.307</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.30006e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.377</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3364349653934542</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.207853808999192</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.330872044191811</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.992339890089732</v>
+      </c>
+      <c r="J20" t="n">
+        <v>23.46109240877554</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.32316930768758</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.389x + -9670.692</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>409.0849011173936</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>670518833.5164906</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.737191179104628e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9551744915128674</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-536.362</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.29972e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.431</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2489376998696005</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.105595333171572</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.247979014734664</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.257693173514006</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23.70461072009237</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.35571614915852</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.652x + -9665.573</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>387.7908753102142</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6692.121581603515</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.738064730148106e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9719671782897866</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-531.24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.29958e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.486</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3435494059156975</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.19516783040611</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.325443317766465</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.610145823385347</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24.02101664322306</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.38390616017077</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 21.886x + -9637.664</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>399.4904205218741</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>219135433.561069</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.721173291768883e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9565317751274194</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1223.752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.46536e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.31999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3191663407834493</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.323581373630826</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.297582480834405</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.718923911524125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.817115927035504</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.25551928412541</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.456x + -4916.884</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>406.7013749986835</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12673.95832488556</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.041051549785037e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9997809166510686</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-868.0219999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.39868e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7769901204978937</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.410140311063439</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.691427814944546</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.837974625778998</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.31967765152675</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.41471683543011</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.469x + -7108.067</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>402.3967333229889</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12438.40576673371</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.908832667328552e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.999995659168511</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-739.688</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.37166e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.59399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2832702501702717</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.161086506325127</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.414345668445945</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.793399272524229</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.17710376477499</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.12056153617527</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.747x + -8241.052</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>399.0392363469371</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>12260.68819178515</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.044897567485924e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9994988221519534</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-673.2910000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.35893e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.039</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1903316903567134</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.097917376647189</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.287879196223056</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.850602832852489</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.03368759306585</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.48516577153818</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.281x + -8947.292</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>483.2367862327099</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>795434118.2919952</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.042513512471488e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9372152002926653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-634.595</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.35239e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.318</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1225013414020026</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.793064387829692</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.131436259027911</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.617336588400018</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.24057335814374</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.67737573901671</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.225x + -9270.857</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>476.0343846787736</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>913377199.1937584</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.982868915923945e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9409886443805884</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-609.0949999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.34888e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.51300000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1322441926297824</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7132482830140715</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.055998651993042</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.46683316136669</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.19501551085345</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.80559389034082</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.918x + -9449.577</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>468.5608150129989</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>769263496.4838506</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.94258544206764e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9437235128304052</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-588.9970000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.34727e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.67400000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4491893089745564</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.786228582966176</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.51250088378609</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.93577914790201</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.89852981274684</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.456x + -9527.183</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>461.0746054231596</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>191129122.1236848</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.911993270942463e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9459606737290084</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-571.9150000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.34625e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.79300000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2954213490297393</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.012122583285205</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.165433332542397</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.072177231206577</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.67233118301949</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.01807146389051</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.197x + -9769.072</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>453.9242508402796</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>372760312.7674243</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.889777124154979e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.94763584162269</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-558.7170000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.34624e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.899</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3381093448266241</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.257249769975397</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.4951402944205</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.939623297659938</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.12543433481855</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.10289545096438</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.760x + -9898.148</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>433.2829199540236</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18601.14084679451</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.673282442456265e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9999434124870333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-544.614</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.34624e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.008</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4359154589433544</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.423730256620228</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.220794942921865</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.938280891433217</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.64295695079005</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.17089277067454</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 20.236x + -9966.186</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>440.7223450521758</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>361616311.7910796</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.854817428250025e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9504812654111526</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-665.9810000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.37658e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.93899999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1158908043594208</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8521700584220727</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.982314245936723</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.728214939519055</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.98776676508053</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.47229885089921</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 16.221x + -9101.121</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>404.4399193174224</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12345.21611574376</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.99883031353931e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998882259251549</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-629.7900000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.36808e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.19799999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1753405892997655</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.115637792783331</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.027785560273903</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.663718991129719</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.22505132879944</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.68515496020835</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.265x + -9557.452</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>488.3659983783317</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>269850633.6384178</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.021145338287357e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9398572149639584</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-609.718</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.36447e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.343</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5850701934633005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.367071938372318</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.596247720054103</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.36359844463819</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.11954234059651</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.81762399037687</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.986x + -9835.013</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>481.8846398858158</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>461881724.3072599</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.988277955919509e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.94196544878889</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-597.199</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.36289e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.458</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4483747376507275</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.308464732147652</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.479662535741855</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.220411496441116</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.51574975438492</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.8931267023886</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.424x + -9902.703</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>474.9741872024891</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>129967435.5110029</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.964067020412649e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9436617081568603</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-591.9929999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.36206e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.541</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.246399652915849</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.050917048523854</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.378815443536467</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.87216079633553</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.69587283657493</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.90912910900869</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.519x + -9762.400</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>468.1697256762132</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>256938874.3915394</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.947734700580416e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9448496271848609</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-583.7280000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.36181e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.621</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3201659410488321</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.209104097040859</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.489387644762878</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.033866808645328</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.97046834852049</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.9600921985341</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.830x + -9770.419</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>461.8220178493131</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>17788407.85547392</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.927872500261712e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9463822055227681</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-578.8610000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.36158e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.691</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1319360301170859</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9278776668047305</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.239818105526463</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.126814411848562</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.20140078597801</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.98052124933479</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.958x + -9670.831</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>455.8673221642141</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>499497517.2968128</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.919593652997132e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9470254613061763</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-575.672</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.36135e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.748</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.07718927628230446</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9416468852430222</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.135134657264378</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.5268602865481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.21331607308323</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.99892763269111</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.074x + -9581.306</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>450.3495627653526</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>246920193.1798993</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.90864635234706e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9478747392038033</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-571.588</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.36074e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.798</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2455771177932837</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.285528780662506</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.487630330881704</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.411307495256704</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.49312924628606</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.04101803178727</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.346x + -9607.697</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>433.8294656084345</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18519.18294441571</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.681629965889808e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9998751517380779</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-565.301</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.36079e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.855</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3964586916917593</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.195324931905536</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.286015989682812</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.996566733479924</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.60167961514784</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.08380951057404</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.631x + -9635.946</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>440.1205649007259</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>248156617.5353783</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.888682204305977e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9494278332461855</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-562.8180000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.36102e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.90300000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2749191033792211</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.011234613546258</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.186659958345635</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.831192492374423</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.70626785086153</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.09040828442785</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 19.675x + -9513.391</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>382.8694290590216</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14469.59741488218</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.862969646006185e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9999393712832486</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-559.712</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.36091e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.95699999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.01402474631829343</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7259683539709454</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.305702576634166</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.008124399739439</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21.91898671473949</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.09265344524387</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.690x + -9371.072</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>430.2630813247082</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>119801808.4312982</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.870885169653327e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9508947121992659</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-557.832</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.36096e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.98999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1276273139326751</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.97281382720262</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.023885340001792</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.965798654623943</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.9057053413802</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.1168705858537</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.856x + -9344.808</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>425.4186914818209</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>350390756.63888</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.865259779459644e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9513691556777275</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-551.114</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.36134e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.047</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3171604229391747</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07774233328126</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.361017719402256</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.354861910623639</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.19928480095127</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.15933099306569</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.153x + -9375.785</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>420.4897265050199</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>584701814.4546447</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.857085210908023e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9520788412508524</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-551.1800000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.36277e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.07899999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1642306698301901</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9509172450193797</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.238658214971963</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.288497415177595</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.18211336701598</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.15305956671632</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 20.109x + -9210.874</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>415.4866774599119</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>343793953.5746257</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.852958126006104e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9525870515467489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-546.625</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.36349e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.11799999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3621367603538769</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.082851335200883</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.455579958915111</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.554513852731096</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22.29152202334002</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.19294677907739</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 20.395x + -9244.894</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>392.9751011143074</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6800.783006640148</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.356609355350524e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9070335127123301</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-543.67</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.36447e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.16800000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.07417774993210335</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6368461158630987</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.116471346194173</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.793055141053359</v>
+      </c>
+      <c r="J18" t="n">
+        <v>22.373754174085</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.19227593676838</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.390x + -9094.909</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>405.8943965311582</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>888811135.5946382</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.841049705917868e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9537673865691624</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-539.5150000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.36478e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.20399999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4275165735261316</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.292831339362761</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.511314984415803</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.224326081744509</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.48078785035523</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.24495352083824</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.781x + -9187.541</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>383.6129946062841</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3295.095923306363</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.81412877121526e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.7432309183677314</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-537.1609999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.36544e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.238</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.505567439057852</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.266764738297561</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.749316943150072</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.843899924969643</v>
+      </c>
+      <c r="J20" t="n">
+        <v>22.60127559401313</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.25628889508883</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.867x + -9111.270</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>380.2516164576234</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3259.133067576397</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.403575972039832e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.7484743821202079</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-534.6949999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.36603e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.271</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5309342504509555</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.308301696325595</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.572363745696753</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.203528694615589</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22.6016576617577</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.27619462846373</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.019x + -9078.589</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>392.8432717743761</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>107719829.1197938</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.825235297600877e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.955279690106187</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-532.751</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.3662e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.301</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7540155135865494</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.386026435887621</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.83857827464217</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.877575967946975</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22.69201878714392</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.29618691802891</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 21.175x + -9055.589</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>381.7539626031968</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6189.487186110757</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.909160522697561e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8355441216339506</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1068.698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.48587e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.322</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1522952004524268</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9707985009277427</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.094954644884572</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.581260975455717</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.05934187865892</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.02918359955979</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.561x + -5125.456</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>394.0273055527683</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11885.6028818909</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.97948087298246e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.999999213679143</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-716.629</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.4166e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.672</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7493128319177687</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.941343027615481</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.479607125652862</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.16771714433503</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.09342005273813</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.644x + -7701.822</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>467.4287572890287</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>256549186.5122571</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.181598486608101e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9336117382660001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-628.296</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.40262e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.233</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.282484200710549</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.118964661918477</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.376067775135447</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.040657739720026</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.86094483220467</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.60220700984418</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.843x + -8738.454</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>460.322971337899</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>252804608.0011402</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.061608372826926e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9406617542949743</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-587.6859999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.39783e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.511</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2622528604492774</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.111887112376603</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.283128864914738</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.923594446904668</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.20088428656643</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.81700727223844</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.982x + -9151.082</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>452.8972180414294</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>255803581.5874311</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.005989739130881e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9442940925952736</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-564.7939999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.39562e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.69</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2945883825148151</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9762829560378943</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.311597773655121</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.621600016044733</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.06686723279877</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.94560410174707</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.741x + -9348.650</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>445.0636877213517</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>243658313.1678612</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.97140394558811e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9467047746450715</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-545.7549999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.39515e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.836</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2988381937997537</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.276094195623116</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.441256422833471</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.034837395979847</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.87021715013726</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.05300945687455</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 19.425x + -9503.690</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>385.3661195390713</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14547.46765430388</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.008013279205159e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9992962544183825</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-533.202</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.39503e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.959</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08351811103036726</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7083054018467531</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.969724649697181</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.655505784152161</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.38378679168592</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.09272163989831</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.691x + -9405.700</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>430.3080223354208</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>472047266.44802</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.924431853210026e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9503222146828666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-519.3290000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.39566e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-85.05500000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.556857447700721</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.388148968740496</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.409800112945712</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.790124384708069</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.9193021905932</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.1982615453858</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 20.434x + -9633.690</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>423.6776555416881</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>118879938.0130415</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.908423511782025e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9516660269494955</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-508.28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.39635e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-85.152</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.384354701182811</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.319257943815123</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.536554187188836</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.355619648522989</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23.51931048151438</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.24952107295046</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 20.815x + -9636.609</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>417.5579821825693</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>684358810.9056885</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.894254397876975e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9528759661385404</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-501.59</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.39687e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.21899999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5255122293785485</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.383280383699607</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.502282760836736</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.546782106764319</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.94725421003658</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.29825037858569</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 21.191x + -9670.767</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>411.8004330729737</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>225184336.6018699</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.883334130830972e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.953822149758292</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>87.48389126762358</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 22.757x + -11487.078</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11487.07792864877</v>
       </c>
       <c r="Y2" t="n">
         <v>449.7324770182993</v>
       </c>
       <c r="Z2" t="n">
-        <v>25508394.88950895</v>
+        <v>534.4880000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.62768174120501e-07</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>87.54226836466799</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 23.298x + -11672.048</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11672.04758836881</v>
       </c>
       <c r="Y3" t="n">
         <v>445.5630252428553</v>
       </c>
       <c r="Z3" t="n">
-        <v>1224831969.763895</v>
+        <v>526.9590000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.620562417888693e-07</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>87.54356734158762</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 23.310x + -11511.178</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11511.17811510823</v>
       </c>
       <c r="Y4" t="n">
         <v>440.57200342307</v>
       </c>
       <c r="Z4" t="n">
-        <v>361524904.7141443</v>
+        <v>524.96</v>
       </c>
       <c r="AA4" t="n">
         <v>1.613412393773471e-07</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>87.50876778046046</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 22.984x + -11131.443</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11131.44345889026</v>
       </c>
       <c r="Y5" t="n">
         <v>434.918939654659</v>
       </c>
       <c r="Z5" t="n">
-        <v>238070481.8131202</v>
+        <v>526.364</v>
       </c>
       <c r="AA5" t="n">
         <v>1.60843052491533e-07</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>87.5734402858692</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 23.598x + -11316.365</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11316.36532269195</v>
       </c>
       <c r="Y6" t="n">
         <v>428.9805326930563</v>
       </c>
       <c r="Z6" t="n">
-        <v>351951834.0520582</v>
+        <v>520.1990000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.602996283743558e-07</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>87.57321150208318</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 23.596x + -11120.506</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11120.50638872414</v>
       </c>
       <c r="Y7" t="n">
         <v>374.8204554599633</v>
       </c>
       <c r="Z7" t="n">
-        <v>14040.15174975307</v>
+        <v>518.6220000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.785913493309581e-07</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>87.57396297053552</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 23.603x + -10928.846</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10928.84622222615</v>
       </c>
       <c r="Y8" t="n">
         <v>365.6853465029369</v>
       </c>
       <c r="Z8" t="n">
-        <v>13851.35162018206</v>
+        <v>516.563</v>
       </c>
       <c r="AA8" t="n">
         <v>1.838755169454749e-07</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>87.6201997380898</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 24.062x + -11028.155</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11028.15515365553</v>
       </c>
       <c r="Y9" t="n">
         <v>411.4825982516712</v>
       </c>
       <c r="Z9" t="n">
-        <v>1122631804.411305</v>
+        <v>512.7569999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.589030786070383e-07</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>87.62176336246442</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 24.078x + -10849.981</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10849.98111226879</v>
       </c>
       <c r="Y10" t="n">
         <v>405.9777884499951</v>
       </c>
       <c r="Z10" t="n">
-        <v>886428826.5764951</v>
+        <v>512.318</v>
       </c>
       <c r="AA10" t="n">
         <v>1.584028753299632e-07</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>87.62426279911098</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 24.103x + -10685.706</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10685.70562937584</v>
       </c>
       <c r="Y11" t="n">
         <v>400.6059495363203</v>
       </c>
       <c r="Z11" t="n">
-        <v>874389240.8724992</v>
+        <v>511.091</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57980590450597e-07</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>86.75361082380941</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 17.630x + -10237.775</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10237.77529729316</v>
       </c>
       <c r="Y2" t="n">
         <v>407.7709143410224</v>
       </c>
       <c r="Z2" t="n">
-        <v>12545.18482610068</v>
+        <v>594.6099999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>2.002963919265197e-07</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>86.86801453331059</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 18.276x + -10225.800</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10225.80026693201</v>
       </c>
       <c r="Y3" t="n">
         <v>410.8387029075576</v>
       </c>
       <c r="Z3" t="n">
-        <v>12284.97353287469</v>
+        <v>570.276</v>
       </c>
       <c r="AA3" t="n">
         <v>2.033548430802535e-07</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.99463662222448</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 19.047x + -10455.185</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10455.1848436522</v>
       </c>
       <c r="Y4" t="n">
         <v>484.8266879074271</v>
       </c>
       <c r="Z4" t="n">
-        <v>796366444.8808361</v>
+        <v>552.707</v>
       </c>
       <c r="AA4" t="n">
         <v>1.990652598113316e-07</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>87.05229228180562</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 19.420x + -10473.118</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10473.11808597432</v>
       </c>
       <c r="Y5" t="n">
         <v>478.6725991689934</v>
       </c>
       <c r="Z5" t="n">
-        <v>523856921.0771014</v>
+        <v>542.926</v>
       </c>
       <c r="AA5" t="n">
         <v>1.967874488134689e-07</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>87.1484519955907</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 20.076x + -10723.716</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10723.71554120652</v>
       </c>
       <c r="Y6" t="n">
         <v>472.7228914409149</v>
       </c>
       <c r="Z6" t="n">
-        <v>517460373.484095</v>
+        <v>531.1940000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.951177372400178e-07</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>87.15410263922493</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 20.116x + -10561.928</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10561.92770538805</v>
       </c>
       <c r="Y7" t="n">
         <v>466.789279425025</v>
       </c>
       <c r="Z7" t="n">
-        <v>1022527497.358744</v>
+        <v>527.6370000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.939213991495241e-07</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>87.15259833623313</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 20.106x + -10382.571</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10382.57052443704</v>
       </c>
       <c r="Y8" t="n">
         <v>460.807216954542</v>
       </c>
       <c r="Z8" t="n">
-        <v>32032887.50010811</v>
+        <v>526.0029999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.926628158384923e-07</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.16967435030494</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 20.227x + -10284.413</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10284.4133261859</v>
       </c>
       <c r="Y9" t="n">
         <v>454.8255420182748</v>
       </c>
       <c r="Z9" t="n">
-        <v>373621188.1538545</v>
+        <v>523.126</v>
       </c>
       <c r="AA9" t="n">
         <v>1.918950822923622e-07</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.21713930138537</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 20.573x + -10323.957</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10323.95713170192</v>
       </c>
       <c r="Y10" t="n">
         <v>448.7143466524704</v>
       </c>
       <c r="Z10" t="n">
-        <v>122915166.3643759</v>
+        <v>516.7430000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.908091545169312e-07</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.28212837708256</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 21.065x + -10463.504</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10463.5038952236</v>
       </c>
       <c r="Y11" t="n">
         <v>442.5118569111033</v>
       </c>
       <c r="Z11" t="n">
-        <v>242129805.007102</v>
+        <v>510.6849999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.898921551635108e-07</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.21878386703551</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.585x + -9974.061</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9974.061216264234</v>
       </c>
       <c r="Y12" t="n">
         <v>385.3947832595061</v>
       </c>
       <c r="Z12" t="n">
-        <v>14512.37229573186</v>
+        <v>512.443</v>
       </c>
       <c r="AA12" t="n">
         <v>1.837559702970311e-07</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.28312877332847</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 21.073x + -10103.122</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10103.12217246724</v>
       </c>
       <c r="Y13" t="n">
         <v>430.6108211227326</v>
       </c>
       <c r="Z13" t="n">
-        <v>32925772.60776133</v>
+        <v>507.227</v>
       </c>
       <c r="AA13" t="n">
         <v>1.879020514223816e-07</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.3412444748015</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 21.534x + -10203.679</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10203.67937700934</v>
       </c>
       <c r="Y14" t="n">
         <v>424.82509227475</v>
       </c>
       <c r="Z14" t="n">
-        <v>350350998.1575538</v>
+        <v>499.864</v>
       </c>
       <c r="AA14" t="n">
         <v>1.87167093282658e-07</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.32769129915327</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 21.425x + -9962.520</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9962.51997390038</v>
       </c>
       <c r="Y15" t="n">
         <v>419.2251962838653</v>
       </c>
       <c r="Z15" t="n">
-        <v>917008079.7492678</v>
+        <v>498.795</v>
       </c>
       <c r="AA15" t="n">
         <v>1.863720582175968e-07</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>87.32683850046057</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 21.418x + -9779.586</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9779.586126269876</v>
       </c>
       <c r="Y16" t="n">
         <v>413.475995297416</v>
       </c>
       <c r="Z16" t="n">
-        <v>169918089.9228762</v>
+        <v>496.293</v>
       </c>
       <c r="AA16" t="n">
         <v>1.854355722526172e-07</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.35856119094636</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.676x + -9762.715</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9762.714503639863</v>
       </c>
       <c r="Y17" t="n">
         <v>407.8608773168519</v>
       </c>
       <c r="Z17" t="n">
-        <v>334897920.0237986</v>
+        <v>493.8939999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.847148475461929e-07</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>87.40076229016793</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 22.028x + -9791.802</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9791.801966194686</v>
       </c>
       <c r="Y18" t="n">
         <v>402.1940793513439</v>
       </c>
       <c r="Z18" t="n">
-        <v>329347362.2599905</v>
+        <v>488.158</v>
       </c>
       <c r="AA18" t="n">
         <v>1.839783417340264e-07</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>87.41476181194837</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 22.148x + -9688.697</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9688.696603969463</v>
       </c>
       <c r="Y19" t="n">
         <v>386.2119766468502</v>
       </c>
       <c r="Z19" t="n">
-        <v>3254.195744528191</v>
+        <v>487.021</v>
       </c>
       <c r="AA19" t="n">
         <v>8.870003710897893e-07</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>87.43925964484517</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 22.360x + -9628.026</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9628.025938073208</v>
       </c>
       <c r="Y20" t="n">
         <v>390.8372265071988</v>
       </c>
       <c r="Z20" t="n">
-        <v>854551446.8637075</v>
+        <v>483.2900000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.825029071544421e-07</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>87.46225202544657</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 22.563x + -9567.236</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9567.236172464309</v>
       </c>
       <c r="Y21" t="n">
         <v>383.9009836199369</v>
       </c>
       <c r="Z21" t="n">
-        <v>9807.638003366283</v>
+        <v>480.167</v>
       </c>
       <c r="AA21" t="n">
         <v>2.695082237132001e-07</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>87.46557665444269</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.592x + -9408.347</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9408.347395802168</v>
       </c>
       <c r="Y22" t="n">
         <v>379.7667170734993</v>
       </c>
       <c r="Z22" t="n">
-        <v>414478115.7529508</v>
+        <v>478.583</v>
       </c>
       <c r="AA22" t="n">
         <v>1.810659795871835e-07</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>86.43059951118163</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 16.031x + -9422.929</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9422.928647581273</v>
       </c>
       <c r="Y2" t="n">
         <v>404.7456383436996</v>
       </c>
       <c r="Z2" t="n">
-        <v>12663.70046711942</v>
+        <v>730.5890000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.961351237379376e-07</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>86.94673674351195</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 18.748x + -10697.829</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10697.82883941937</v>
       </c>
       <c r="Y3" t="n">
         <v>497.361488090615</v>
       </c>
       <c r="Z3" t="n">
-        <v>272500641.6775718</v>
+        <v>629.728</v>
       </c>
       <c r="AA3" t="n">
         <v>1.803074358482611e-07</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>87.1843403406146</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 20.333x + -11461.020</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11461.02016369687</v>
       </c>
       <c r="Y4" t="n">
         <v>490.9292903205533</v>
       </c>
       <c r="Z4" t="n">
-        <v>538263103.0608996</v>
+        <v>587.9839999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.755091809728803e-07</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>87.2415026110381</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.755x + -11453.904</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11453.90399392915</v>
       </c>
       <c r="Y5" t="n">
         <v>485.1270312468699</v>
       </c>
       <c r="Z5" t="n">
-        <v>531599230.7145907</v>
+        <v>572.425</v>
       </c>
       <c r="AA5" t="n">
         <v>1.724789585196178e-07</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>87.30334346330827</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.231x + -11541.563</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11541.56319972459</v>
       </c>
       <c r="Y6" t="n">
         <v>479.8626264619209</v>
       </c>
       <c r="Z6" t="n">
-        <v>525484866.432004</v>
+        <v>559.0870000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.704402094990969e-07</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>87.33059210203039</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 21.448x + -11500.888</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11500.88834006986</v>
       </c>
       <c r="Y7" t="n">
         <v>474.607936270931</v>
       </c>
       <c r="Z7" t="n">
-        <v>268881413.8394894</v>
+        <v>553.617</v>
       </c>
       <c r="AA7" t="n">
         <v>1.69132117389684e-07</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>87.35871986952019</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 21.677x + -11462.620</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11462.61975899953</v>
       </c>
       <c r="Y8" t="n">
         <v>469.2907598083517</v>
       </c>
       <c r="Z8" t="n">
-        <v>390544936.1868502</v>
+        <v>547.098</v>
       </c>
       <c r="AA8" t="n">
         <v>1.679658385701025e-07</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>87.40757389299669</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 22.086x + -11547.341</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11547.34065857199</v>
       </c>
       <c r="Y9" t="n">
         <v>463.8590223891536</v>
       </c>
       <c r="Z9" t="n">
-        <v>797670753.2086676</v>
+        <v>541.05</v>
       </c>
       <c r="AA9" t="n">
         <v>1.669914090478229e-07</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>87.40392988344449</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 22.055x + -11339.343</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11339.343005484</v>
       </c>
       <c r="Y10" t="n">
         <v>435.1470132697332</v>
       </c>
       <c r="Z10" t="n">
-        <v>19065.49048632301</v>
+        <v>539.068</v>
       </c>
       <c r="AA10" t="n">
         <v>1.616785888729669e-07</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>87.48002114924114</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 22.722x + -11575.923</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11575.92274465447</v>
       </c>
       <c r="Y11" t="n">
         <v>452.3540705714025</v>
       </c>
       <c r="Z11" t="n">
-        <v>494654973.0891057</v>
+        <v>531.1100000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.652048056888331e-07</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>87.48528646505123</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 22.770x + -11402.433</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11402.43312596591</v>
       </c>
       <c r="Y12" t="n">
         <v>446.739680857137</v>
       </c>
       <c r="Z12" t="n">
-        <v>977203389.2654747</v>
+        <v>526.4350000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.642619133738038e-07</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>87.51266748418475</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 23.021x + -11384.850</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-11384.84990869904</v>
       </c>
       <c r="Y13" t="n">
         <v>441.2043787231522</v>
       </c>
       <c r="Z13" t="n">
-        <v>362173327.5330236</v>
+        <v>523.701</v>
       </c>
       <c r="AA13" t="n">
         <v>1.636429486747324e-07</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>87.49221507848974</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 22.833x + -11079.838</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11079.83760917102</v>
       </c>
       <c r="Y14" t="n">
         <v>435.8325133960838</v>
       </c>
       <c r="Z14" t="n">
-        <v>242216250.6369408</v>
+        <v>521.796</v>
       </c>
       <c r="AA14" t="n">
         <v>1.628753421057765e-07</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>87.51352262591496</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 23.028x + -11044.369</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11044.36899255705</v>
       </c>
       <c r="Y15" t="n">
         <v>430.6467462647433</v>
       </c>
       <c r="Z15" t="n">
-        <v>353121807.6940942</v>
+        <v>520.264</v>
       </c>
       <c r="AA15" t="n">
         <v>1.624473674092704e-07</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>87.57432410905598</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 23.606x + -11222.442</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11222.44230193034</v>
       </c>
       <c r="Y16" t="n">
         <v>425.5678611514442</v>
       </c>
       <c r="Z16" t="n">
-        <v>465815180.7540883</v>
+        <v>513.326</v>
       </c>
       <c r="AA16" t="n">
         <v>1.617788793708483e-07</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>87.58786958777797</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 23.739x + -11128.241</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11128.24050024595</v>
       </c>
       <c r="Y17" t="n">
         <v>365.2967479947008</v>
       </c>
       <c r="Z17" t="n">
-        <v>13962.29282862893</v>
+        <v>510.871</v>
       </c>
       <c r="AA17" t="n">
         <v>1.800072698738132e-07</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>87.59321992049954</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 23.792x + -10991.061</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10991.06095853327</v>
       </c>
       <c r="Y18" t="n">
         <v>365.7437024421812</v>
       </c>
       <c r="Z18" t="n">
-        <v>13793.30733250387</v>
+        <v>509.14</v>
       </c>
       <c r="AA18" t="n">
         <v>1.873980059352311e-07</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>87.60104075517688</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 23.870x + -10865.366</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10865.3657687703</v>
       </c>
       <c r="Y19" t="n">
         <v>410.4845870465296</v>
       </c>
       <c r="Z19" t="n">
-        <v>28480514.64362854</v>
+        <v>506.6079999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.598592026793065e-07</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>87.62590043864432</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 24.120x + -10830.897</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10830.89718086393</v>
       </c>
       <c r="Y20" t="n">
         <v>405.5357371961852</v>
       </c>
       <c r="Z20" t="n">
-        <v>332667321.6845441</v>
+        <v>501.851</v>
       </c>
       <c r="AA20" t="n">
         <v>1.594754498883078e-07</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>87.66290251126932</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 24.502x + -10889.839</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10889.83940663235</v>
       </c>
       <c r="Y21" t="n">
         <v>400.6292131971126</v>
       </c>
       <c r="Z21" t="n">
-        <v>656494006.9787445</v>
+        <v>498.518</v>
       </c>
       <c r="AA21" t="n">
         <v>1.589969247623025e-07</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>87.67765532804282</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 24.658x + -10810.363</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10810.36290001218</v>
       </c>
       <c r="Y22" t="n">
         <v>395.7406033550092</v>
       </c>
       <c r="Z22" t="n">
-        <v>647991773.7160977</v>
+        <v>495.9690000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.585264482049269e-07</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>83.61148465490307</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.931x + -5726.099</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5726.098901218926</v>
       </c>
       <c r="Y2" t="n">
         <v>418.0204060570979</v>
       </c>
       <c r="Z2" t="n">
-        <v>13280.29912317816</v>
+        <v>1281.649</v>
       </c>
       <c r="AA2" t="n">
         <v>1.782262012239833e-07</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>84.91405985065113</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.236x + -6518.576</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6518.575708509353</v>
       </c>
       <c r="Y3" t="n">
         <v>406.9356579485685</v>
       </c>
       <c r="Z3" t="n">
-        <v>12685.62596056101</v>
+        <v>1014.249</v>
       </c>
       <c r="AA3" t="n">
         <v>1.840975831861445e-07</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>85.66840459879103</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.202x + -7485.111</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7485.110977076128</v>
       </c>
       <c r="Y4" t="n">
         <v>402.9730350635263</v>
       </c>
       <c r="Z4" t="n">
-        <v>12462.25431193797</v>
+        <v>871.2990000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.890058265048753e-07</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.07286087970242</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.567x + -8087.333</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8087.332519489385</v>
       </c>
       <c r="Y5" t="n">
         <v>491.6636738253705</v>
       </c>
       <c r="Z5" t="n">
-        <v>269674749.3423757</v>
+        <v>788.005</v>
       </c>
       <c r="AA5" t="n">
         <v>2.015777721681117e-07</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.43320913555776</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.043x + -8860.775</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8860.775408076453</v>
       </c>
       <c r="Y6" t="n">
         <v>485.9214518122515</v>
       </c>
       <c r="Z6" t="n">
-        <v>399597565.6290065</v>
+        <v>727.855</v>
       </c>
       <c r="AA6" t="n">
         <v>1.944049037367472e-07</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.58621265841869</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.764x + -9077.781</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9077.780506269131</v>
       </c>
       <c r="Y7" t="n">
         <v>479.976610980483</v>
       </c>
       <c r="Z7" t="n">
-        <v>197206831.3016371</v>
+        <v>693.7180000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.892266163094472e-07</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.77606535230156</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.753x + -9520.059</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9520.059202138427</v>
       </c>
       <c r="Y8" t="n">
         <v>473.6629101608175</v>
       </c>
       <c r="Z8" t="n">
-        <v>130250474.9436368</v>
+        <v>662.2670000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.852393989027738e-07</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.80329664906893</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.905x + -9359.790</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9359.790435706926</v>
       </c>
       <c r="Y9" t="n">
         <v>467.1998543859579</v>
       </c>
       <c r="Z9" t="n">
-        <v>384480061.2012399</v>
+        <v>648.511</v>
       </c>
       <c r="AA9" t="n">
         <v>1.823038878499942e-07</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.95602581339388</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.805x + -9755.057</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9755.057238820251</v>
       </c>
       <c r="Y10" t="n">
         <v>441.4782816300599</v>
       </c>
       <c r="Z10" t="n">
-        <v>19176.86040800497</v>
+        <v>627.042</v>
       </c>
       <c r="AA10" t="n">
         <v>1.619796231614761e-07</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.98779446968977</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.004x + -9649.280</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9649.279662247052</v>
       </c>
       <c r="Y11" t="n">
         <v>454.1850923297379</v>
       </c>
       <c r="Z11" t="n">
-        <v>255881195.3342048</v>
+        <v>616.804</v>
       </c>
       <c r="AA11" t="n">
         <v>1.777501202237959e-07</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.75686995902248</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.478x + -7844.419</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7844.41869113777</v>
       </c>
       <c r="Y2" t="n">
         <v>406.6757508190286</v>
       </c>
       <c r="Z2" t="n">
-        <v>12642.56926853817</v>
+        <v>851.3280000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.924358387235392e-07</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>86.40086647281839</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.898x + -9073.048</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9073.047758489638</v>
       </c>
       <c r="Y3" t="n">
         <v>403.7519722451961</v>
       </c>
       <c r="Z3" t="n">
-        <v>12432.76348186441</v>
+        <v>730.226</v>
       </c>
       <c r="AA3" t="n">
         <v>2.149230094569739e-07</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.68099121148317</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.244x + -9633.594</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9633.593617101664</v>
       </c>
       <c r="Y4" t="n">
         <v>491.0772645139172</v>
       </c>
       <c r="Z4" t="n">
-        <v>135072206.8318982</v>
+        <v>674.1719999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.890940657958642e-07</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>86.87281736834721</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.304x + -10133.097</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10133.09697532537</v>
       </c>
       <c r="Y5" t="n">
         <v>486.5792081841189</v>
       </c>
       <c r="Z5" t="n">
-        <v>1066030428.940031</v>
+        <v>640.63</v>
       </c>
       <c r="AA5" t="n">
         <v>1.848622104889686e-07</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>86.97273533993433</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.909x + -10350.661</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10350.66085402469</v>
       </c>
       <c r="Y6" t="n">
         <v>481.3002605669151</v>
       </c>
       <c r="Z6" t="n">
-        <v>131931694.6908549</v>
+        <v>622.0419999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.822322986399571e-07</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>87.02392868172051</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 19.235x + -10352.622</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10352.62168042783</v>
       </c>
       <c r="Y7" t="n">
         <v>475.5761945644315</v>
       </c>
       <c r="Z7" t="n">
-        <v>390898171.2236999</v>
+        <v>609.261</v>
       </c>
       <c r="AA7" t="n">
         <v>1.800972400513979e-07</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>87.04530412314432</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.374x + -10236.732</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10236.73152171815</v>
       </c>
       <c r="Y8" t="n">
         <v>469.4991716414882</v>
       </c>
       <c r="Z8" t="n">
-        <v>128941831.0295638</v>
+        <v>600.997</v>
       </c>
       <c r="AA8" t="n">
         <v>1.783459648837793e-07</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>87.08828942822355</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.661x + -10235.420</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10235.41958354107</v>
       </c>
       <c r="Y9" t="n">
         <v>463.4254608838797</v>
       </c>
       <c r="Z9" t="n">
-        <v>380876671.3098059</v>
+        <v>593.579</v>
       </c>
       <c r="AA9" t="n">
         <v>1.769803435356875e-07</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>87.12680688794293</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.925x + -10204.356</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10204.35551686627</v>
       </c>
       <c r="Y10" t="n">
         <v>452.3551432983907</v>
       </c>
       <c r="Z10" t="n">
-        <v>19033.55547754413</v>
+        <v>584.5350000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.57660098914171e-07</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>87.21278467146085</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 20.540x + -10422.603</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10422.60324982645</v>
       </c>
       <c r="Y11" t="n">
         <v>451.4474092345619</v>
       </c>
       <c r="Z11" t="n">
-        <v>247499140.3841373</v>
+        <v>574.345</v>
       </c>
       <c r="AA11" t="n">
         <v>1.743270847449702e-07</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>87.21836579054334</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.582x + -10263.565</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10263.56464186314</v>
       </c>
       <c r="Y12" t="n">
         <v>445.7804411165236</v>
       </c>
       <c r="Z12" t="n">
-        <v>1218887979.656995</v>
+        <v>571.0279999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.733676593565875e-07</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>87.26918221924089</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 20.965x + -10325.783</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10325.78309714612</v>
       </c>
       <c r="Y13" t="n">
         <v>440.2005039536013</v>
       </c>
       <c r="Z13" t="n">
-        <v>481573007.1813665</v>
+        <v>563.518</v>
       </c>
       <c r="AA13" t="n">
         <v>1.723032509058292e-07</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>87.29428391070608</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 21.160x + -10263.641</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10263.64102231978</v>
       </c>
       <c r="Y14" t="n">
         <v>434.723897092129</v>
       </c>
       <c r="Z14" t="n">
-        <v>237769632.4421493</v>
+        <v>556.8129999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.712948978600426e-07</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>87.32539904225365</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 21.407x + -10241.786</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10241.78598667324</v>
       </c>
       <c r="Y15" t="n">
         <v>371.2507098873601</v>
       </c>
       <c r="Z15" t="n">
-        <v>14271.00293336709</v>
+        <v>552.0430000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.830378588769889e-07</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>87.33485663091844</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 21.483x + -10115.925</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10115.92548771846</v>
       </c>
       <c r="Y16" t="n">
         <v>370.5408170808202</v>
       </c>
       <c r="Z16" t="n">
-        <v>14088.60709471307</v>
+        <v>548.376</v>
       </c>
       <c r="AA16" t="n">
         <v>1.866074475234489e-07</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>87.34918501267336</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.599x + -10017.243</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10017.24339804782</v>
       </c>
       <c r="Y17" t="n">
         <v>418.7338970947847</v>
       </c>
       <c r="Z17" t="n">
-        <v>228612614.3248598</v>
+        <v>545.372</v>
       </c>
       <c r="AA17" t="n">
         <v>1.688584923609476e-07</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>87.38391162875087</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.886x + -10020.238</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10020.23849438376</v>
       </c>
       <c r="Y18" t="n">
         <v>413.399184936012</v>
       </c>
       <c r="Z18" t="n">
-        <v>225758056.4968992</v>
+        <v>540.278</v>
       </c>
       <c r="AA18" t="n">
         <v>1.68121973185646e-07</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>87.4219028213531</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 22.209x + -10042.574</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10042.57369212209</v>
       </c>
       <c r="Y19" t="n">
         <v>408.0633665346227</v>
       </c>
       <c r="Z19" t="n">
-        <v>122370120.8085435</v>
+        <v>535.605</v>
       </c>
       <c r="AA19" t="n">
         <v>1.673873645501824e-07</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>87.46456485809695</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 22.583x + -10071.807</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10071.80720284362</v>
       </c>
       <c r="Y20" t="n">
         <v>396.6682220815492</v>
       </c>
       <c r="Z20" t="n">
-        <v>15040.31542558245</v>
+        <v>527.046</v>
       </c>
       <c r="AA20" t="n">
         <v>1.716931347568358e-07</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>87.46018208192284</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 22.544x + -9901.441</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9901.44086903851</v>
       </c>
       <c r="Y21" t="n">
         <v>397.5219674641309</v>
       </c>
       <c r="Z21" t="n">
-        <v>542188241.5899316</v>
+        <v>528.6500000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.661870710057581e-07</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>87.50748958817188</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.973x + -9956.995</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9956.995427501939</v>
       </c>
       <c r="Y22" t="n">
         <v>375.5911874316374</v>
       </c>
       <c r="Z22" t="n">
-        <v>3216.194448504606</v>
+        <v>520.4110000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>3.15235095117835e-06</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>82.43146814434007</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.526x + -4906.653</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4906.653469620401</v>
       </c>
       <c r="Y2" t="n">
         <v>429.6230202017823</v>
       </c>
       <c r="Z2" t="n">
-        <v>13632.91162896371</v>
+        <v>1440.061</v>
       </c>
       <c r="AA2" t="n">
         <v>1.76095697154734e-07</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>84.2843643292851</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.991x + -5956.536</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-5956.536332184563</v>
       </c>
       <c r="Y3" t="n">
         <v>418.3909006030254</v>
       </c>
       <c r="Z3" t="n">
-        <v>13015.70243212981</v>
+        <v>1093.85</v>
       </c>
       <c r="AA3" t="n">
         <v>1.858001589130673e-07</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.23755006454805</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.003x + -6971.035</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6971.035278165876</v>
       </c>
       <c r="Y4" t="n">
         <v>415.9180064078726</v>
       </c>
       <c r="Z4" t="n">
-        <v>12778.77446574732</v>
+        <v>922.6510000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.859463378083317e-07</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>85.77015761713605</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.521x + -7715.469</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7715.468949892682</v>
       </c>
       <c r="Y5" t="n">
         <v>411.2921404591351</v>
       </c>
       <c r="Z5" t="n">
-        <v>12610.20393195065</v>
+        <v>822.5970000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.978829766619678e-07</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.13889687054176</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.817x + -8355.625</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8355.624879283245</v>
       </c>
       <c r="Y6" t="n">
         <v>497.9991348708024</v>
       </c>
       <c r="Z6" t="n">
-        <v>275902571.6437891</v>
+        <v>759.525</v>
       </c>
       <c r="AA6" t="n">
         <v>2.060720263312138e-07</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.34544783306758</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.657x + -8663.689</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8663.688710141796</v>
       </c>
       <c r="Y7" t="n">
         <v>491.2385879836768</v>
       </c>
       <c r="Z7" t="n">
-        <v>235478182.0657036</v>
+        <v>719.095</v>
       </c>
       <c r="AA7" t="n">
         <v>1.99405388123095e-07</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.53091970359502</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.496x + -8980.051</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8980.05141716383</v>
       </c>
       <c r="Y8" t="n">
         <v>484.2022281744278</v>
       </c>
       <c r="Z8" t="n">
-        <v>265067634.3005174</v>
+        <v>686.039</v>
       </c>
       <c r="AA8" t="n">
         <v>1.943512660502939e-07</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.66738375692333</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.173x + -9199.664</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9199.663776734364</v>
       </c>
       <c r="Y9" t="n">
         <v>477.2630158202608</v>
       </c>
       <c r="Z9" t="n">
-        <v>522997955.0189785</v>
+        <v>662.4690000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.905462105206098e-07</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.7501538257503</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.611x + -9259.913</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9259.912521421697</v>
       </c>
       <c r="Y10" t="n">
         <v>470.6356380197503</v>
       </c>
       <c r="Z10" t="n">
-        <v>193889728.1771298</v>
+        <v>644.6530000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.874661518942262e-07</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.8818227022586</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.357x + -9554.077</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9554.076816665018</v>
       </c>
       <c r="Y11" t="n">
         <v>464.3983617687056</v>
       </c>
       <c r="Z11" t="n">
-        <v>381171840.461351</v>
+        <v>626.192</v>
       </c>
       <c r="AA11" t="n">
         <v>1.85087056957529e-07</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>83.80803281961077</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.217x + -5330.651</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5330.651193525006</v>
       </c>
       <c r="Y2" t="n">
         <v>406.5263877950339</v>
       </c>
       <c r="Z2" t="n">
-        <v>12642.72418967486</v>
+        <v>1157.117</v>
       </c>
       <c r="AA2" t="n">
         <v>1.902781240056709e-07</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>85.83759170343708</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.741x + -7786.253</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7786.252547697837</v>
       </c>
       <c r="Y3" t="n">
         <v>402.5632672503307</v>
       </c>
       <c r="Z3" t="n">
-        <v>12428.16809904474</v>
+        <v>810.874</v>
       </c>
       <c r="AA3" t="n">
         <v>2.029988712923931e-07</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>86.406450606668</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 15.923x + -8918.000</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8918.000010221309</v>
       </c>
       <c r="Y4" t="n">
         <v>490.7816655345515</v>
       </c>
       <c r="Z4" t="n">
-        <v>403831423.0850303</v>
+        <v>710.1270000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>2.016494255454809e-07</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.59079509749448</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.786x + -9212.278</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9212.277538662594</v>
       </c>
       <c r="Y5" t="n">
         <v>485.0273788493913</v>
       </c>
       <c r="Z5" t="n">
-        <v>399159616.1825728</v>
+        <v>672.891</v>
       </c>
       <c r="AA5" t="n">
         <v>1.950740920061707e-07</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>86.76041595398152</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.667x + -9598.420</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9598.420101327862</v>
       </c>
       <c r="Y6" t="n">
         <v>479.0293725002069</v>
       </c>
       <c r="Z6" t="n">
-        <v>393594127.5226604</v>
+        <v>647.3280000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.913407660562732e-07</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>86.84147896049464</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.122x + -9671.259</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9671.259169719857</v>
       </c>
       <c r="Y7" t="n">
         <v>473.0622106069381</v>
       </c>
       <c r="Z7" t="n">
-        <v>519419597.5195135</v>
+        <v>630.348</v>
       </c>
       <c r="AA7" t="n">
         <v>1.884529039014557e-07</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>86.92651739183607</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.624x + -9823.447</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9823.446539917808</v>
       </c>
       <c r="Y8" t="n">
         <v>467.4286805380581</v>
       </c>
       <c r="Z8" t="n">
-        <v>25998813.56134218</v>
+        <v>617.6009999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.861501394209685e-07</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>86.99006427642644</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.018x + -9892.229</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9892.228548268542</v>
       </c>
       <c r="Y9" t="n">
         <v>461.9733608989825</v>
       </c>
       <c r="Z9" t="n">
-        <v>506282223.6626672</v>
+        <v>604.943</v>
       </c>
       <c r="AA9" t="n">
         <v>1.845545453528326e-07</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>87.00453847256939</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.110x + -9772.808</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9772.807842384238</v>
       </c>
       <c r="Y10" t="n">
         <v>456.7392632204899</v>
       </c>
       <c r="Z10" t="n">
-        <v>267490486.5192766</v>
+        <v>599.747</v>
       </c>
       <c r="AA10" t="n">
         <v>1.831211419317002e-07</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>87.05765847991218</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.456x + -9835.282</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9835.281599579974</v>
       </c>
       <c r="Y11" t="n">
         <v>431.5640462242851</v>
       </c>
       <c r="Z11" t="n">
-        <v>18801.07281796883</v>
+        <v>590.6779999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.597913339886611e-07</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>87.12188335730089</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 19.891x + -9947.877</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9947.876997571244</v>
       </c>
       <c r="Y12" t="n">
         <v>446.955114352198</v>
       </c>
       <c r="Z12" t="n">
-        <v>244719590.4818788</v>
+        <v>579.7779999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.804911603909267e-07</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>87.11057003409572</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.813x + -9746.406</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9746.406023358328</v>
       </c>
       <c r="Y13" t="n">
         <v>442.3124520156859</v>
       </c>
       <c r="Z13" t="n">
-        <v>484349398.751979</v>
+        <v>577.5810000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1.795544539557422e-07</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>87.19282027189048</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 20.394x + -9976.647</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9976.647378674983</v>
       </c>
       <c r="Y14" t="n">
         <v>437.6535848804979</v>
       </c>
       <c r="Z14" t="n">
-        <v>957617410.9524475</v>
+        <v>568.876</v>
       </c>
       <c r="AA14" t="n">
         <v>1.786284545913437e-07</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>87.17991225279945</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.301x + -9758.860</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9758.860268520661</v>
       </c>
       <c r="Y15" t="n">
         <v>376.286958931379</v>
       </c>
       <c r="Z15" t="n">
-        <v>14384.64403881321</v>
+        <v>565.7079999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.795452761962009e-07</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>87.24525866733592</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 20.783x + -9909.661</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9909.661166001237</v>
       </c>
       <c r="Y16" t="n">
         <v>375.0470348808144</v>
       </c>
       <c r="Z16" t="n">
-        <v>14226.21648973086</v>
+        <v>557.674</v>
       </c>
       <c r="AA16" t="n">
         <v>1.803149429303379e-07</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>87.28075196465225</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.055x + -9933.115</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9933.115345005439</v>
       </c>
       <c r="Y17" t="n">
         <v>423.4207669624959</v>
       </c>
       <c r="Z17" t="n">
-        <v>347168929.1431149</v>
+        <v>553.2089999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.760298822197493e-07</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>87.29584037462348</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.172x + -9841.999</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9841.999226486749</v>
       </c>
       <c r="Y18" t="n">
         <v>418.6335670009601</v>
       </c>
       <c r="Z18" t="n">
-        <v>116107200.4301946</v>
+        <v>548.5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.751255444743452e-07</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>87.29893838289193</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 21.197x + -9705.656</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9705.656288385184</v>
       </c>
       <c r="Y19" t="n">
         <v>413.8931146539479</v>
       </c>
       <c r="Z19" t="n">
-        <v>113545739.5923299</v>
+        <v>546.596</v>
       </c>
       <c r="AA19" t="n">
         <v>1.744172360890317e-07</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>87.32316930768758</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.389x + -9670.692</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9670.69153992405</v>
       </c>
       <c r="Y20" t="n">
         <v>409.0849011173936</v>
       </c>
       <c r="Z20" t="n">
-        <v>670518833.5164906</v>
+        <v>542.307</v>
       </c>
       <c r="AA20" t="n">
         <v>1.737191179104628e-07</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>87.35571614915852</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.652x + -9665.573</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9665.57285770849</v>
       </c>
       <c r="Y21" t="n">
         <v>387.7908753102142</v>
       </c>
       <c r="Z21" t="n">
-        <v>6692.121581603515</v>
+        <v>536.362</v>
       </c>
       <c r="AA21" t="n">
         <v>3.738064730148106e-07</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>87.38390616017077</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 21.886x + -9637.664</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9637.663903255019</v>
       </c>
       <c r="Y22" t="n">
         <v>399.4904205218741</v>
       </c>
       <c r="Z22" t="n">
-        <v>219135433.561069</v>
+        <v>531.24</v>
       </c>
       <c r="AA22" t="n">
         <v>1.721173291768883e-07</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.25551928412541</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.456x + -4916.884</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4916.883607405103</v>
       </c>
       <c r="Y2" t="n">
         <v>406.7013749986835</v>
       </c>
       <c r="Z2" t="n">
-        <v>12673.95832488556</v>
+        <v>1223.752</v>
       </c>
       <c r="AA2" t="n">
         <v>2.041051549785037e-07</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.41471683543011</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.469x + -7108.067</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7108.066875592928</v>
       </c>
       <c r="Y3" t="n">
         <v>402.3967333229889</v>
       </c>
       <c r="Z3" t="n">
-        <v>12438.40576673371</v>
+        <v>868.0219999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.908832667328552e-07</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.12056153617527</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.747x + -8241.052</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8241.051550060061</v>
       </c>
       <c r="Y4" t="n">
         <v>399.0392363469371</v>
       </c>
       <c r="Z4" t="n">
-        <v>12260.68819178515</v>
+        <v>739.688</v>
       </c>
       <c r="AA4" t="n">
         <v>2.044897567485924e-07</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.48516577153818</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.281x + -8947.292</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8947.291811173791</v>
       </c>
       <c r="Y5" t="n">
         <v>483.2367862327099</v>
       </c>
       <c r="Z5" t="n">
-        <v>795434118.2919952</v>
+        <v>673.2910000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>2.042513512471488e-07</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.67737573901671</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.225x + -9270.857</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9270.857118003354</v>
       </c>
       <c r="Y6" t="n">
         <v>476.0343846787736</v>
       </c>
       <c r="Z6" t="n">
-        <v>913377199.1937584</v>
+        <v>634.595</v>
       </c>
       <c r="AA6" t="n">
         <v>1.982868915923945e-07</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.80559389034082</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.918x + -9449.577</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9449.576603802907</v>
       </c>
       <c r="Y7" t="n">
         <v>468.5608150129989</v>
       </c>
       <c r="Z7" t="n">
-        <v>769263496.4838506</v>
+        <v>609.0949999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.94258544206764e-07</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>86.89852981274684</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.456x + -9527.183</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9527.183326988787</v>
       </c>
       <c r="Y8" t="n">
         <v>461.0746054231596</v>
       </c>
       <c r="Z8" t="n">
-        <v>191129122.1236848</v>
+        <v>588.9970000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.911993270942463e-07</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>87.01807146389051</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.197x + -9769.072</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9769.071633018755</v>
       </c>
       <c r="Y9" t="n">
         <v>453.9242508402796</v>
       </c>
       <c r="Z9" t="n">
-        <v>372760312.7674243</v>
+        <v>571.9150000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1.889777124154979e-07</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>87.10289545096438</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.760x + -9898.148</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9898.147979322495</v>
       </c>
       <c r="Y10" t="n">
         <v>433.2829199540236</v>
       </c>
       <c r="Z10" t="n">
-        <v>18601.14084679451</v>
+        <v>558.7170000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.673282442456265e-07</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>87.17089277067454</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 20.236x + -9966.186</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9966.186121799577</v>
       </c>
       <c r="Y11" t="n">
         <v>440.7223450521758</v>
       </c>
       <c r="Z11" t="n">
-        <v>361616311.7910796</v>
+        <v>544.614</v>
       </c>
       <c r="AA11" t="n">
         <v>1.854817428250025e-07</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>86.47229885089921</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 16.221x + -9101.121</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9101.12092754331</v>
       </c>
       <c r="Y2" t="n">
         <v>404.4399193174224</v>
       </c>
       <c r="Z2" t="n">
-        <v>12345.21611574376</v>
+        <v>665.9810000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.99883031353931e-07</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>86.68515496020835</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.265x + -9557.452</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9557.452151639169</v>
       </c>
       <c r="Y3" t="n">
         <v>488.3659983783317</v>
       </c>
       <c r="Z3" t="n">
-        <v>269850633.6384178</v>
+        <v>629.7900000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>2.021145338287357e-07</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>86.81762399037687</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.986x + -9835.013</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9835.01333775173</v>
       </c>
       <c r="Y4" t="n">
         <v>481.8846398858158</v>
       </c>
       <c r="Z4" t="n">
-        <v>461881724.3072599</v>
+        <v>609.718</v>
       </c>
       <c r="AA4" t="n">
         <v>1.988277955919509e-07</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.8931267023886</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.424x + -9902.703</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9902.70273760533</v>
       </c>
       <c r="Y5" t="n">
         <v>474.9741872024891</v>
       </c>
       <c r="Z5" t="n">
-        <v>129967435.5110029</v>
+        <v>597.199</v>
       </c>
       <c r="AA5" t="n">
         <v>1.964067020412649e-07</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>86.90912910900869</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.519x + -9762.400</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9762.399579159044</v>
       </c>
       <c r="Y6" t="n">
         <v>468.1697256762132</v>
       </c>
       <c r="Z6" t="n">
-        <v>256938874.3915394</v>
+        <v>591.9929999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.947734700580416e-07</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>86.9600921985341</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.830x + -9770.419</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9770.418568911437</v>
       </c>
       <c r="Y7" t="n">
         <v>461.8220178493131</v>
       </c>
       <c r="Z7" t="n">
-        <v>17788407.85547392</v>
+        <v>583.7280000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.927872500261712e-07</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>86.98052124933479</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.958x + -9670.831</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9670.831283868571</v>
       </c>
       <c r="Y8" t="n">
         <v>455.8673221642141</v>
       </c>
       <c r="Z8" t="n">
-        <v>499497517.2968128</v>
+        <v>578.8610000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.919593652997132e-07</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>86.99892763269111</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.074x + -9581.306</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9581.306293118661</v>
       </c>
       <c r="Y9" t="n">
         <v>450.3495627653526</v>
       </c>
       <c r="Z9" t="n">
-        <v>246920193.1798993</v>
+        <v>575.672</v>
       </c>
       <c r="AA9" t="n">
         <v>1.90864635234706e-07</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>87.04101803178727</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.346x + -9607.697</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9607.697271928855</v>
       </c>
       <c r="Y10" t="n">
         <v>433.8294656084345</v>
       </c>
       <c r="Z10" t="n">
-        <v>18519.18294441571</v>
+        <v>571.588</v>
       </c>
       <c r="AA10" t="n">
         <v>1.681629965889808e-07</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>87.08380951057404</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.631x + -9635.946</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9635.946465106061</v>
       </c>
       <c r="Y11" t="n">
         <v>440.1205649007259</v>
       </c>
       <c r="Z11" t="n">
-        <v>248156617.5353783</v>
+        <v>565.301</v>
       </c>
       <c r="AA11" t="n">
         <v>1.888682204305977e-07</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>87.09040828442785</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 19.675x + -9513.391</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9513.390534011367</v>
       </c>
       <c r="Y12" t="n">
         <v>382.8694290590216</v>
       </c>
       <c r="Z12" t="n">
-        <v>14469.59741488218</v>
+        <v>562.8180000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.862969646006185e-07</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>87.09265344524387</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.690x + -9371.072</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9371.071786548766</v>
       </c>
       <c r="Y13" t="n">
         <v>430.2630813247082</v>
       </c>
       <c r="Z13" t="n">
-        <v>119801808.4312982</v>
+        <v>559.712</v>
       </c>
       <c r="AA13" t="n">
         <v>1.870885169653327e-07</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>87.1168705858537</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.856x + -9344.808</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-9344.808101891927</v>
       </c>
       <c r="Y14" t="n">
         <v>425.4186914818209</v>
       </c>
       <c r="Z14" t="n">
-        <v>350390756.63888</v>
+        <v>557.832</v>
       </c>
       <c r="AA14" t="n">
         <v>1.865259779459644e-07</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>87.15933099306569</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.153x + -9375.785</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9375.785307874887</v>
       </c>
       <c r="Y15" t="n">
         <v>420.4897265050199</v>
       </c>
       <c r="Z15" t="n">
-        <v>584701814.4546447</v>
+        <v>551.114</v>
       </c>
       <c r="AA15" t="n">
         <v>1.857085210908023e-07</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>87.15305956671632</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 20.109x + -9210.874</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9210.873821406965</v>
       </c>
       <c r="Y16" t="n">
         <v>415.4866774599119</v>
       </c>
       <c r="Z16" t="n">
-        <v>343793953.5746257</v>
+        <v>551.1800000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.852958126006104e-07</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>87.19294677907739</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 20.395x + -9244.894</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9244.894357243344</v>
       </c>
       <c r="Y17" t="n">
         <v>392.9751011143074</v>
       </c>
       <c r="Z17" t="n">
-        <v>6800.783006640148</v>
+        <v>546.625</v>
       </c>
       <c r="AA17" t="n">
         <v>5.356609355350524e-07</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>87.19227593676838</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.390x + -9094.909</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9094.909101556685</v>
       </c>
       <c r="Y18" t="n">
         <v>405.8943965311582</v>
       </c>
       <c r="Z18" t="n">
-        <v>888811135.5946382</v>
+        <v>543.67</v>
       </c>
       <c r="AA18" t="n">
         <v>1.841049705917868e-07</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>87.24495352083824</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.781x + -9187.541</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9187.541307310519</v>
       </c>
       <c r="Y19" t="n">
         <v>383.6129946062841</v>
       </c>
       <c r="Z19" t="n">
-        <v>3295.095923306363</v>
+        <v>539.5150000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>2.81412877121526e-06</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>87.25628889508883</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.867x + -9111.270</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9111.269712031131</v>
       </c>
       <c r="Y20" t="n">
         <v>380.2516164576234</v>
       </c>
       <c r="Z20" t="n">
-        <v>3259.133067576397</v>
+        <v>537.1609999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>2.403575972039832e-06</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>87.27619462846373</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.019x + -9078.589</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9078.588658721843</v>
       </c>
       <c r="Y21" t="n">
         <v>392.8432717743761</v>
       </c>
       <c r="Z21" t="n">
-        <v>107719829.1197938</v>
+        <v>534.6949999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.825235297600877e-07</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>87.29618691802891</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 21.175x + -9055.589</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9055.588524306166</v>
       </c>
       <c r="Y22" t="n">
         <v>381.7539626031968</v>
       </c>
       <c r="Z22" t="n">
-        <v>6189.487186110757</v>
+        <v>532.751</v>
       </c>
       <c r="AA22" t="n">
         <v>6.909160522697561e-07</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.02918359955979</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.561x + -5125.456</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5125.45594776426</v>
       </c>
       <c r="Y2" t="n">
         <v>394.0273055527683</v>
       </c>
       <c r="Z2" t="n">
-        <v>11885.6028818909</v>
+        <v>1068.698</v>
       </c>
       <c r="AA2" t="n">
         <v>1.97948087298246e-07</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.09342005273813</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.644x + -7701.822</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7701.821708693514</v>
       </c>
       <c r="Y3" t="n">
         <v>467.4287572890287</v>
       </c>
       <c r="Z3" t="n">
-        <v>256549186.5122571</v>
+        <v>716.629</v>
       </c>
       <c r="AA3" t="n">
         <v>2.181598486608101e-07</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.60220700984418</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.843x + -8738.454</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8738.453666687641</v>
       </c>
       <c r="Y4" t="n">
         <v>460.322971337899</v>
       </c>
       <c r="Z4" t="n">
-        <v>252804608.0011402</v>
+        <v>628.296</v>
       </c>
       <c r="AA4" t="n">
         <v>2.061608372826926e-07</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>86.81700727223844</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.982x + -9151.082</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9151.082280136625</v>
       </c>
       <c r="Y5" t="n">
         <v>452.8972180414294</v>
       </c>
       <c r="Z5" t="n">
-        <v>255803581.5874311</v>
+        <v>587.6859999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>2.005989739130881e-07</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.94560410174707</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.741x + -9348.650</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9348.650045344886</v>
       </c>
       <c r="Y6" t="n">
         <v>445.0636877213517</v>
       </c>
       <c r="Z6" t="n">
-        <v>243658313.1678612</v>
+        <v>564.7939999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.97140394558811e-07</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>87.05300945687455</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 19.425x + -9503.690</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9503.690102312696</v>
       </c>
       <c r="Y7" t="n">
         <v>385.3661195390713</v>
       </c>
       <c r="Z7" t="n">
-        <v>14547.46765430388</v>
+        <v>545.7549999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>2.008013279205159e-07</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>87.09272163989831</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.691x + -9405.700</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9405.70016972862</v>
       </c>
       <c r="Y8" t="n">
         <v>430.3080223354208</v>
       </c>
       <c r="Z8" t="n">
-        <v>472047266.44802</v>
+        <v>533.202</v>
       </c>
       <c r="AA8" t="n">
         <v>1.924431853210026e-07</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>87.1982615453858</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 20.434x + -9633.690</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9633.690206354831</v>
       </c>
       <c r="Y9" t="n">
         <v>423.6776555416881</v>
       </c>
       <c r="Z9" t="n">
-        <v>118879938.0130415</v>
+        <v>519.3290000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.908423511782025e-07</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.24952107295046</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 20.815x + -9636.609</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9636.609214677765</v>
       </c>
       <c r="Y10" t="n">
         <v>417.5579821825693</v>
       </c>
       <c r="Z10" t="n">
-        <v>684358810.9056885</v>
+        <v>508.28</v>
       </c>
       <c r="AA10" t="n">
         <v>1.894254397876975e-07</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>87.29825037858569</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 21.191x + -9670.767</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9670.766551158607</v>
       </c>
       <c r="Y11" t="n">
         <v>411.8004330729737</v>
       </c>
       <c r="Z11" t="n">
-        <v>225184336.6018699</v>
+        <v>501.59</v>
       </c>
       <c r="AA11" t="n">
         <v>1.883334130830972e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>87.48389126762358</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 22.757x + -11487.078</t>
-        </is>
+      <c r="W2" t="n">
+        <v>22.75694325943202</v>
       </c>
       <c r="X2" t="n">
         <v>-11487.07792864877</v>
@@ -600,7 +598,7 @@
         <v>449.7324770182993</v>
       </c>
       <c r="Z2" t="n">
-        <v>534.4880000000001</v>
+        <v>25508394.88950895</v>
       </c>
       <c r="AA2" t="n">
         <v>1.62768174120501e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>87.54226836466799</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 23.298x + -11672.048</t>
-        </is>
+      <c r="W3" t="n">
+        <v>23.29816343455167</v>
       </c>
       <c r="X3" t="n">
         <v>-11672.04758836881</v>
@@ -652,7 +648,7 @@
         <v>445.5630252428553</v>
       </c>
       <c r="Z3" t="n">
-        <v>526.9590000000001</v>
+        <v>1224831969.763895</v>
       </c>
       <c r="AA3" t="n">
         <v>1.620562417888693e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.54356734158762</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 23.310x + -11511.178</t>
-        </is>
+      <c r="W4" t="n">
+        <v>23.31049877075992</v>
       </c>
       <c r="X4" t="n">
         <v>-11511.17811510823</v>
@@ -704,7 +698,7 @@
         <v>440.57200342307</v>
       </c>
       <c r="Z4" t="n">
-        <v>524.96</v>
+        <v>361524904.7141443</v>
       </c>
       <c r="AA4" t="n">
         <v>1.613412393773471e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>87.50876778046046</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.984x + -11131.443</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.98447655082196</v>
       </c>
       <c r="X5" t="n">
         <v>-11131.44345889026</v>
@@ -756,7 +748,7 @@
         <v>434.918939654659</v>
       </c>
       <c r="Z5" t="n">
-        <v>526.364</v>
+        <v>238070481.8131202</v>
       </c>
       <c r="AA5" t="n">
         <v>1.60843052491533e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>87.5734402858692</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.598x + -11316.365</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.5978199794432</v>
       </c>
       <c r="X6" t="n">
         <v>-11316.36532269195</v>
@@ -808,7 +798,7 @@
         <v>428.9805326930563</v>
       </c>
       <c r="Z6" t="n">
-        <v>520.1990000000001</v>
+        <v>351951834.0520582</v>
       </c>
       <c r="AA6" t="n">
         <v>1.602996283743558e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>87.57321150208318</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 23.596x + -11120.506</t>
-        </is>
+      <c r="W7" t="n">
+        <v>23.59559264896013</v>
       </c>
       <c r="X7" t="n">
         <v>-11120.50638872414</v>
@@ -860,7 +848,7 @@
         <v>374.8204554599633</v>
       </c>
       <c r="Z7" t="n">
-        <v>518.6220000000001</v>
+        <v>14040.15174975307</v>
       </c>
       <c r="AA7" t="n">
         <v>1.785913493309581e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>87.57396297053552</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 23.603x + -10928.846</t>
-        </is>
+      <c r="W8" t="n">
+        <v>23.60291016483175</v>
       </c>
       <c r="X8" t="n">
         <v>-10928.84622222615</v>
@@ -912,7 +898,7 @@
         <v>365.6853465029369</v>
       </c>
       <c r="Z8" t="n">
-        <v>516.563</v>
+        <v>13851.35162018206</v>
       </c>
       <c r="AA8" t="n">
         <v>1.838755169454749e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>87.6201997380898</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 24.062x + -11028.155</t>
-        </is>
+      <c r="W9" t="n">
+        <v>24.06203076246477</v>
       </c>
       <c r="X9" t="n">
         <v>-11028.15515365553</v>
@@ -964,7 +948,7 @@
         <v>411.4825982516712</v>
       </c>
       <c r="Z9" t="n">
-        <v>512.7569999999999</v>
+        <v>1122631804.411305</v>
       </c>
       <c r="AA9" t="n">
         <v>1.589030786070383e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>87.62176336246442</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.078x + -10849.981</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.07786908152043</v>
       </c>
       <c r="X10" t="n">
         <v>-10849.98111226879</v>
@@ -1016,7 +998,7 @@
         <v>405.9777884499951</v>
       </c>
       <c r="Z10" t="n">
-        <v>512.318</v>
+        <v>886428826.5764951</v>
       </c>
       <c r="AA10" t="n">
         <v>1.584028753299632e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>87.62426279911098</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 24.103x + -10685.706</t>
-        </is>
+      <c r="W11" t="n">
+        <v>24.10322973688432</v>
       </c>
       <c r="X11" t="n">
         <v>-10685.70562937584</v>
@@ -1068,7 +1048,7 @@
         <v>400.6059495363203</v>
       </c>
       <c r="Z11" t="n">
-        <v>511.091</v>
+        <v>874389240.8724992</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57980590450597e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>86.75361082380941</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 17.630x + -10237.775</t>
-        </is>
+      <c r="W2" t="n">
+        <v>17.6301883770523</v>
       </c>
       <c r="X2" t="n">
         <v>-10237.77529729316</v>
@@ -1266,7 +1244,7 @@
         <v>407.7709143410224</v>
       </c>
       <c r="Z2" t="n">
-        <v>594.6099999999999</v>
+        <v>12545.18482610068</v>
       </c>
       <c r="AA2" t="n">
         <v>2.002963919265197e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>86.86801453331059</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 18.276x + -10225.800</t>
-        </is>
+      <c r="W3" t="n">
+        <v>18.27553172399951</v>
       </c>
       <c r="X3" t="n">
         <v>-10225.80026693201</v>
@@ -1318,7 +1294,7 @@
         <v>410.8387029075576</v>
       </c>
       <c r="Z3" t="n">
-        <v>570.276</v>
+        <v>12284.97353287469</v>
       </c>
       <c r="AA3" t="n">
         <v>2.033548430802535e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.99463662222448</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.047x + -10455.185</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.04702207835942</v>
       </c>
       <c r="X4" t="n">
         <v>-10455.1848436522</v>
@@ -1370,7 +1344,7 @@
         <v>484.8266879074271</v>
       </c>
       <c r="Z4" t="n">
-        <v>552.707</v>
+        <v>796366444.8808361</v>
       </c>
       <c r="AA4" t="n">
         <v>1.990652598113316e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>87.05229228180562</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.420x + -10473.118</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.42024977459458</v>
       </c>
       <c r="X5" t="n">
         <v>-10473.11808597432</v>
@@ -1422,7 +1394,7 @@
         <v>478.6725991689934</v>
       </c>
       <c r="Z5" t="n">
-        <v>542.926</v>
+        <v>523856921.0771014</v>
       </c>
       <c r="AA5" t="n">
         <v>1.967874488134689e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>87.1484519955907</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 20.076x + -10723.716</t>
-        </is>
+      <c r="W6" t="n">
+        <v>20.0762762800646</v>
       </c>
       <c r="X6" t="n">
         <v>-10723.71554120652</v>
@@ -1474,7 +1444,7 @@
         <v>472.7228914409149</v>
       </c>
       <c r="Z6" t="n">
-        <v>531.1940000000001</v>
+        <v>517460373.484095</v>
       </c>
       <c r="AA6" t="n">
         <v>1.951177372400178e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>87.15410263922493</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 20.116x + -10561.928</t>
-        </is>
+      <c r="W7" t="n">
+        <v>20.11620436901852</v>
       </c>
       <c r="X7" t="n">
         <v>-10561.92770538805</v>
@@ -1526,7 +1494,7 @@
         <v>466.789279425025</v>
       </c>
       <c r="Z7" t="n">
-        <v>527.6370000000001</v>
+        <v>1022527497.358744</v>
       </c>
       <c r="AA7" t="n">
         <v>1.939213991495241e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>87.15259833623313</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 20.106x + -10382.571</t>
-        </is>
+      <c r="W8" t="n">
+        <v>20.10555932756268</v>
       </c>
       <c r="X8" t="n">
         <v>-10382.57052443704</v>
@@ -1578,7 +1544,7 @@
         <v>460.807216954542</v>
       </c>
       <c r="Z8" t="n">
-        <v>526.0029999999999</v>
+        <v>32032887.50010811</v>
       </c>
       <c r="AA8" t="n">
         <v>1.926628158384923e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.16967435030494</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 20.227x + -10284.413</t>
-        </is>
+      <c r="W9" t="n">
+        <v>20.227060204375</v>
       </c>
       <c r="X9" t="n">
         <v>-10284.4133261859</v>
@@ -1630,7 +1594,7 @@
         <v>454.8255420182748</v>
       </c>
       <c r="Z9" t="n">
-        <v>523.126</v>
+        <v>373621188.1538545</v>
       </c>
       <c r="AA9" t="n">
         <v>1.918950822923622e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.21713930138537</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 20.573x + -10323.957</t>
-        </is>
+      <c r="W10" t="n">
+        <v>20.57261359278333</v>
       </c>
       <c r="X10" t="n">
         <v>-10323.95713170192</v>
@@ -1682,7 +1644,7 @@
         <v>448.7143466524704</v>
       </c>
       <c r="Z10" t="n">
-        <v>516.7430000000001</v>
+        <v>122915166.3643759</v>
       </c>
       <c r="AA10" t="n">
         <v>1.908091545169312e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.28212837708256</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 21.065x + -10463.504</t>
-        </is>
+      <c r="W11" t="n">
+        <v>21.06530631163319</v>
       </c>
       <c r="X11" t="n">
         <v>-10463.5038952236</v>
@@ -1734,7 +1694,7 @@
         <v>442.5118569111033</v>
       </c>
       <c r="Z11" t="n">
-        <v>510.6849999999999</v>
+        <v>242129805.007102</v>
       </c>
       <c r="AA11" t="n">
         <v>1.898921551635108e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.21878386703551</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.585x + -9974.061</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.58479756704478</v>
       </c>
       <c r="X12" t="n">
         <v>-9974.061216264234</v>
@@ -1786,7 +1744,7 @@
         <v>385.3947832595061</v>
       </c>
       <c r="Z12" t="n">
-        <v>512.443</v>
+        <v>14512.37229573186</v>
       </c>
       <c r="AA12" t="n">
         <v>1.837559702970311e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.28312877332847</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 21.073x + -10103.122</t>
-        </is>
+      <c r="W13" t="n">
+        <v>21.07307454636441</v>
       </c>
       <c r="X13" t="n">
         <v>-10103.12217246724</v>
@@ -1838,7 +1794,7 @@
         <v>430.6108211227326</v>
       </c>
       <c r="Z13" t="n">
-        <v>507.227</v>
+        <v>32925772.60776133</v>
       </c>
       <c r="AA13" t="n">
         <v>1.879020514223816e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.3412444748015</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 21.534x + -10203.679</t>
-        </is>
+      <c r="W14" t="n">
+        <v>21.53437854716059</v>
       </c>
       <c r="X14" t="n">
         <v>-10203.67937700934</v>
@@ -1890,7 +1844,7 @@
         <v>424.82509227475</v>
       </c>
       <c r="Z14" t="n">
-        <v>499.864</v>
+        <v>350350998.1575538</v>
       </c>
       <c r="AA14" t="n">
         <v>1.87167093282658e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.32769129915327</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 21.425x + -9962.520</t>
-        </is>
+      <c r="W15" t="n">
+        <v>21.42500507312465</v>
       </c>
       <c r="X15" t="n">
         <v>-9962.51997390038</v>
@@ -1942,7 +1894,7 @@
         <v>419.2251962838653</v>
       </c>
       <c r="Z15" t="n">
-        <v>498.795</v>
+        <v>917008079.7492678</v>
       </c>
       <c r="AA15" t="n">
         <v>1.863720582175968e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>87.32683850046057</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 21.418x + -9779.586</t>
-        </is>
+      <c r="W16" t="n">
+        <v>21.41816009015758</v>
       </c>
       <c r="X16" t="n">
         <v>-9779.586126269876</v>
@@ -1994,7 +1944,7 @@
         <v>413.475995297416</v>
       </c>
       <c r="Z16" t="n">
-        <v>496.293</v>
+        <v>169918089.9228762</v>
       </c>
       <c r="AA16" t="n">
         <v>1.854355722526172e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.35856119094636</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.676x + -9762.715</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.67575560179438</v>
       </c>
       <c r="X17" t="n">
         <v>-9762.714503639863</v>
@@ -2046,7 +1994,7 @@
         <v>407.8608773168519</v>
       </c>
       <c r="Z17" t="n">
-        <v>493.8939999999999</v>
+        <v>334897920.0237986</v>
       </c>
       <c r="AA17" t="n">
         <v>1.847148475461929e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>87.40076229016793</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 22.028x + -9791.802</t>
-        </is>
+      <c r="W18" t="n">
+        <v>22.02817729008412</v>
       </c>
       <c r="X18" t="n">
         <v>-9791.801966194686</v>
@@ -2098,7 +2044,7 @@
         <v>402.1940793513439</v>
       </c>
       <c r="Z18" t="n">
-        <v>488.158</v>
+        <v>329347362.2599905</v>
       </c>
       <c r="AA18" t="n">
         <v>1.839783417340264e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>87.41476181194837</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 22.148x + -9688.697</t>
-        </is>
+      <c r="W19" t="n">
+        <v>22.14762714149477</v>
       </c>
       <c r="X19" t="n">
         <v>-9688.696603969463</v>
@@ -2150,7 +2094,7 @@
         <v>386.2119766468502</v>
       </c>
       <c r="Z19" t="n">
-        <v>487.021</v>
+        <v>3254.195744528191</v>
       </c>
       <c r="AA19" t="n">
         <v>8.870003710897893e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>87.43925964484517</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 22.360x + -9628.026</t>
-        </is>
+      <c r="W20" t="n">
+        <v>22.3597933157277</v>
       </c>
       <c r="X20" t="n">
         <v>-9628.025938073208</v>
@@ -2202,7 +2144,7 @@
         <v>390.8372265071988</v>
       </c>
       <c r="Z20" t="n">
-        <v>483.2900000000001</v>
+        <v>854551446.8637075</v>
       </c>
       <c r="AA20" t="n">
         <v>1.825029071544421e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>87.46225202544657</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 22.563x + -9567.236</t>
-        </is>
+      <c r="W21" t="n">
+        <v>22.56264523749822</v>
       </c>
       <c r="X21" t="n">
         <v>-9567.236172464309</v>
@@ -2254,7 +2194,7 @@
         <v>383.9009836199369</v>
       </c>
       <c r="Z21" t="n">
-        <v>480.167</v>
+        <v>9807.638003366283</v>
       </c>
       <c r="AA21" t="n">
         <v>2.695082237132001e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>87.46557665444269</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.592x + -9408.347</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.59228138957229</v>
       </c>
       <c r="X22" t="n">
         <v>-9408.347395802168</v>
@@ -2306,7 +2244,7 @@
         <v>379.7667170734993</v>
       </c>
       <c r="Z22" t="n">
-        <v>478.583</v>
+        <v>414478115.7529508</v>
       </c>
       <c r="AA22" t="n">
         <v>1.810659795871835e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>86.43059951118163</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.031x + -9422.929</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.031162259784</v>
       </c>
       <c r="X2" t="n">
         <v>-9422.928647581273</v>
@@ -2504,7 +2440,7 @@
         <v>404.7456383436996</v>
       </c>
       <c r="Z2" t="n">
-        <v>730.5890000000001</v>
+        <v>12663.70046711942</v>
       </c>
       <c r="AA2" t="n">
         <v>1.961351237379376e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>86.94673674351195</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 18.748x + -10697.829</t>
-        </is>
+      <c r="W3" t="n">
+        <v>18.7476574448952</v>
       </c>
       <c r="X3" t="n">
         <v>-10697.82883941937</v>
@@ -2556,7 +2490,7 @@
         <v>497.361488090615</v>
       </c>
       <c r="Z3" t="n">
-        <v>629.728</v>
+        <v>272500641.6775718</v>
       </c>
       <c r="AA3" t="n">
         <v>1.803074358482611e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>87.1843403406146</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 20.333x + -11461.020</t>
-        </is>
+      <c r="W4" t="n">
+        <v>20.33258849785576</v>
       </c>
       <c r="X4" t="n">
         <v>-11461.02016369687</v>
@@ -2608,7 +2540,7 @@
         <v>490.9292903205533</v>
       </c>
       <c r="Z4" t="n">
-        <v>587.9839999999999</v>
+        <v>538263103.0608996</v>
       </c>
       <c r="AA4" t="n">
         <v>1.755091809728803e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>87.2415026110381</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.755x + -11453.904</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.75459768106075</v>
       </c>
       <c r="X5" t="n">
         <v>-11453.90399392915</v>
@@ -2660,7 +2590,7 @@
         <v>485.1270312468699</v>
       </c>
       <c r="Z5" t="n">
-        <v>572.425</v>
+        <v>531599230.7145907</v>
       </c>
       <c r="AA5" t="n">
         <v>1.724789585196178e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>87.30334346330827</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.231x + -11541.563</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.23127879177869</v>
       </c>
       <c r="X6" t="n">
         <v>-11541.56319972459</v>
@@ -2712,7 +2640,7 @@
         <v>479.8626264619209</v>
       </c>
       <c r="Z6" t="n">
-        <v>559.0870000000001</v>
+        <v>525484866.432004</v>
       </c>
       <c r="AA6" t="n">
         <v>1.704402094990969e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>87.33059210203039</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 21.448x + -11500.888</t>
-        </is>
+      <c r="W7" t="n">
+        <v>21.44832106403827</v>
       </c>
       <c r="X7" t="n">
         <v>-11500.88834006986</v>
@@ -2764,7 +2690,7 @@
         <v>474.607936270931</v>
       </c>
       <c r="Z7" t="n">
-        <v>553.617</v>
+        <v>268881413.8394894</v>
       </c>
       <c r="AA7" t="n">
         <v>1.69132117389684e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>87.35871986952019</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 21.677x + -11462.620</t>
-        </is>
+      <c r="W8" t="n">
+        <v>21.67705964981787</v>
       </c>
       <c r="X8" t="n">
         <v>-11462.61975899953</v>
@@ -2816,7 +2740,7 @@
         <v>469.2907598083517</v>
       </c>
       <c r="Z8" t="n">
-        <v>547.098</v>
+        <v>390544936.1868502</v>
       </c>
       <c r="AA8" t="n">
         <v>1.679658385701025e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>87.40757389299669</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 22.086x + -11547.341</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22.08613573582901</v>
       </c>
       <c r="X9" t="n">
         <v>-11547.34065857199</v>
@@ -2868,7 +2790,7 @@
         <v>463.8590223891536</v>
       </c>
       <c r="Z9" t="n">
-        <v>541.05</v>
+        <v>797670753.2086676</v>
       </c>
       <c r="AA9" t="n">
         <v>1.669914090478229e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>87.40392988344449</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 22.055x + -11339.343</t>
-        </is>
+      <c r="W10" t="n">
+        <v>22.05509184559907</v>
       </c>
       <c r="X10" t="n">
         <v>-11339.343005484</v>
@@ -2920,7 +2840,7 @@
         <v>435.1470132697332</v>
       </c>
       <c r="Z10" t="n">
-        <v>539.068</v>
+        <v>19065.49048632301</v>
       </c>
       <c r="AA10" t="n">
         <v>1.616785888729669e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>87.48002114924114</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 22.722x + -11575.923</t>
-        </is>
+      <c r="W11" t="n">
+        <v>22.72194872631269</v>
       </c>
       <c r="X11" t="n">
         <v>-11575.92274465447</v>
@@ -2972,7 +2890,7 @@
         <v>452.3540705714025</v>
       </c>
       <c r="Z11" t="n">
-        <v>531.1100000000001</v>
+        <v>494654973.0891057</v>
       </c>
       <c r="AA11" t="n">
         <v>1.652048056888331e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>87.48528646505123</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 22.770x + -11402.433</t>
-        </is>
+      <c r="W12" t="n">
+        <v>22.76958536501676</v>
       </c>
       <c r="X12" t="n">
         <v>-11402.43312596591</v>
@@ -3024,7 +2940,7 @@
         <v>446.739680857137</v>
       </c>
       <c r="Z12" t="n">
-        <v>526.4350000000001</v>
+        <v>977203389.2654747</v>
       </c>
       <c r="AA12" t="n">
         <v>1.642619133738038e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>87.51266748418475</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 23.021x + -11384.850</t>
-        </is>
+      <c r="W13" t="n">
+        <v>23.02055762487994</v>
       </c>
       <c r="X13" t="n">
         <v>-11384.84990869904</v>
@@ -3076,7 +2990,7 @@
         <v>441.2043787231522</v>
       </c>
       <c r="Z13" t="n">
-        <v>523.701</v>
+        <v>362173327.5330236</v>
       </c>
       <c r="AA13" t="n">
         <v>1.636429486747324e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.49221507848974</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 22.833x + -11079.838</t>
-        </is>
+      <c r="W14" t="n">
+        <v>22.83257488128287</v>
       </c>
       <c r="X14" t="n">
         <v>-11079.83760917102</v>
@@ -3128,7 +3040,7 @@
         <v>435.8325133960838</v>
       </c>
       <c r="Z14" t="n">
-        <v>521.796</v>
+        <v>242216250.6369408</v>
       </c>
       <c r="AA14" t="n">
         <v>1.628753421057765e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>87.51352262591496</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 23.028x + -11044.369</t>
-        </is>
+      <c r="W15" t="n">
+        <v>23.02848473922619</v>
       </c>
       <c r="X15" t="n">
         <v>-11044.36899255705</v>
@@ -3180,7 +3090,7 @@
         <v>430.6467462647433</v>
       </c>
       <c r="Z15" t="n">
-        <v>520.264</v>
+        <v>353121807.6940942</v>
       </c>
       <c r="AA15" t="n">
         <v>1.624473674092704e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.57432410905598</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 23.606x + -11222.442</t>
-        </is>
+      <c r="W16" t="n">
+        <v>23.60642840734059</v>
       </c>
       <c r="X16" t="n">
         <v>-11222.44230193034</v>
@@ -3232,7 +3140,7 @@
         <v>425.5678611514442</v>
       </c>
       <c r="Z16" t="n">
-        <v>513.326</v>
+        <v>465815180.7540883</v>
       </c>
       <c r="AA16" t="n">
         <v>1.617788793708483e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.58786958777797</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 23.739x + -11128.241</t>
-        </is>
+      <c r="W17" t="n">
+        <v>23.73914996465069</v>
       </c>
       <c r="X17" t="n">
         <v>-11128.24050024595</v>
@@ -3284,7 +3190,7 @@
         <v>365.2967479947008</v>
       </c>
       <c r="Z17" t="n">
-        <v>510.871</v>
+        <v>13962.29282862893</v>
       </c>
       <c r="AA17" t="n">
         <v>1.800072698738132e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>87.59321992049954</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 23.792x + -10991.061</t>
-        </is>
+      <c r="W18" t="n">
+        <v>23.79198503063794</v>
       </c>
       <c r="X18" t="n">
         <v>-10991.06095853327</v>
@@ -3336,7 +3240,7 @@
         <v>365.7437024421812</v>
       </c>
       <c r="Z18" t="n">
-        <v>509.14</v>
+        <v>13793.30733250387</v>
       </c>
       <c r="AA18" t="n">
         <v>1.873980059352311e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>87.60104075517688</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 23.870x + -10865.366</t>
-        </is>
+      <c r="W19" t="n">
+        <v>23.86964032774446</v>
       </c>
       <c r="X19" t="n">
         <v>-10865.3657687703</v>
@@ -3388,7 +3290,7 @@
         <v>410.4845870465296</v>
       </c>
       <c r="Z19" t="n">
-        <v>506.6079999999999</v>
+        <v>28480514.64362854</v>
       </c>
       <c r="AA19" t="n">
         <v>1.598592026793065e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.62590043864432</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 24.120x + -10830.897</t>
-        </is>
+      <c r="W20" t="n">
+        <v>24.11987506486819</v>
       </c>
       <c r="X20" t="n">
         <v>-10830.89718086393</v>
@@ -3440,7 +3340,7 @@
         <v>405.5357371961852</v>
       </c>
       <c r="Z20" t="n">
-        <v>501.851</v>
+        <v>332667321.6845441</v>
       </c>
       <c r="AA20" t="n">
         <v>1.594754498883078e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.66290251126932</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 24.502x + -10889.839</t>
-        </is>
+      <c r="W21" t="n">
+        <v>24.50218679043504</v>
       </c>
       <c r="X21" t="n">
         <v>-10889.83940663235</v>
@@ -3492,7 +3390,7 @@
         <v>400.6292131971126</v>
       </c>
       <c r="Z21" t="n">
-        <v>498.518</v>
+        <v>656494006.9787445</v>
       </c>
       <c r="AA21" t="n">
         <v>1.589969247623025e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.67765532804282</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 24.658x + -10810.363</t>
-        </is>
+      <c r="W22" t="n">
+        <v>24.65801046179894</v>
       </c>
       <c r="X22" t="n">
         <v>-10810.36290001218</v>
@@ -3544,7 +3440,7 @@
         <v>395.7406033550092</v>
       </c>
       <c r="Z22" t="n">
-        <v>495.9690000000001</v>
+        <v>647991773.7160977</v>
       </c>
       <c r="AA22" t="n">
         <v>1.585264482049269e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>83.61148465490307</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.931x + -5726.099</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.931361708390968</v>
       </c>
       <c r="X2" t="n">
         <v>-5726.098901218926</v>
@@ -3742,7 +3636,7 @@
         <v>418.0204060570979</v>
       </c>
       <c r="Z2" t="n">
-        <v>1281.649</v>
+        <v>13280.29912317816</v>
       </c>
       <c r="AA2" t="n">
         <v>1.782262012239833e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>84.91405985065113</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.236x + -6518.576</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.23591938899878</v>
       </c>
       <c r="X3" t="n">
         <v>-6518.575708509353</v>
@@ -3794,7 +3686,7 @@
         <v>406.9356579485685</v>
       </c>
       <c r="Z3" t="n">
-        <v>1014.249</v>
+        <v>12685.62596056101</v>
       </c>
       <c r="AA3" t="n">
         <v>1.840975831861445e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.66840459879103</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.202x + -7485.111</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.20219815765341</v>
       </c>
       <c r="X4" t="n">
         <v>-7485.110977076128</v>
@@ -3846,7 +3736,7 @@
         <v>402.9730350635263</v>
       </c>
       <c r="Z4" t="n">
-        <v>871.2990000000001</v>
+        <v>12462.25431193797</v>
       </c>
       <c r="AA4" t="n">
         <v>1.890058265048753e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.07286087970242</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.567x + -8087.333</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.56684513451065</v>
       </c>
       <c r="X5" t="n">
         <v>-8087.332519489385</v>
@@ -3898,7 +3786,7 @@
         <v>491.6636738253705</v>
       </c>
       <c r="Z5" t="n">
-        <v>788.005</v>
+        <v>269674749.3423757</v>
       </c>
       <c r="AA5" t="n">
         <v>2.015777721681117e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.43320913555776</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.043x + -8860.775</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.04292176921274</v>
       </c>
       <c r="X6" t="n">
         <v>-8860.775408076453</v>
@@ -3950,7 +3836,7 @@
         <v>485.9214518122515</v>
       </c>
       <c r="Z6" t="n">
-        <v>727.855</v>
+        <v>399597565.6290065</v>
       </c>
       <c r="AA6" t="n">
         <v>1.944049037367472e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.58621265841869</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.764x + -9077.781</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.76377519673984</v>
       </c>
       <c r="X7" t="n">
         <v>-9077.780506269131</v>
@@ -4002,7 +3886,7 @@
         <v>479.976610980483</v>
       </c>
       <c r="Z7" t="n">
-        <v>693.7180000000001</v>
+        <v>197206831.3016371</v>
       </c>
       <c r="AA7" t="n">
         <v>1.892266163094472e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.77606535230156</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.753x + -9520.059</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.75324396651028</v>
       </c>
       <c r="X8" t="n">
         <v>-9520.059202138427</v>
@@ -4054,7 +3936,7 @@
         <v>473.6629101608175</v>
       </c>
       <c r="Z8" t="n">
-        <v>662.2670000000001</v>
+        <v>130250474.9436368</v>
       </c>
       <c r="AA8" t="n">
         <v>1.852393989027738e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.80329664906893</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.905x + -9359.790</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.90479430418617</v>
       </c>
       <c r="X9" t="n">
         <v>-9359.790435706926</v>
@@ -4106,7 +3986,7 @@
         <v>467.1998543859579</v>
       </c>
       <c r="Z9" t="n">
-        <v>648.511</v>
+        <v>384480061.2012399</v>
       </c>
       <c r="AA9" t="n">
         <v>1.823038878499942e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.95602581339388</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.805x + -9755.057</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.80497656734565</v>
       </c>
       <c r="X10" t="n">
         <v>-9755.057238820251</v>
@@ -4158,7 +4036,7 @@
         <v>441.4782816300599</v>
       </c>
       <c r="Z10" t="n">
-        <v>627.042</v>
+        <v>19176.86040800497</v>
       </c>
       <c r="AA10" t="n">
         <v>1.619796231614761e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.98779446968977</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.004x + -9649.280</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.00367767416309</v>
       </c>
       <c r="X11" t="n">
         <v>-9649.279662247052</v>
@@ -4210,7 +4086,7 @@
         <v>454.1850923297379</v>
       </c>
       <c r="Z11" t="n">
-        <v>616.804</v>
+        <v>255881195.3342048</v>
       </c>
       <c r="AA11" t="n">
         <v>1.777501202237959e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.75686995902248</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.478x + -7844.419</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.47849269998558</v>
       </c>
       <c r="X2" t="n">
         <v>-7844.41869113777</v>
@@ -4408,7 +4282,7 @@
         <v>406.6757508190286</v>
       </c>
       <c r="Z2" t="n">
-        <v>851.3280000000001</v>
+        <v>12642.56926853817</v>
       </c>
       <c r="AA2" t="n">
         <v>1.924358387235392e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>86.40086647281839</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.898x + -9073.048</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.89838146188267</v>
       </c>
       <c r="X3" t="n">
         <v>-9073.047758489638</v>
@@ -4460,7 +4332,7 @@
         <v>403.7519722451961</v>
       </c>
       <c r="Z3" t="n">
-        <v>730.226</v>
+        <v>12432.76348186441</v>
       </c>
       <c r="AA3" t="n">
         <v>2.149230094569739e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.68099121148317</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.244x + -9633.594</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.24360535910375</v>
       </c>
       <c r="X4" t="n">
         <v>-9633.593617101664</v>
@@ -4512,7 +4382,7 @@
         <v>491.0772645139172</v>
       </c>
       <c r="Z4" t="n">
-        <v>674.1719999999999</v>
+        <v>135072206.8318982</v>
       </c>
       <c r="AA4" t="n">
         <v>1.890940657958642e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.87281736834721</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.304x + -10133.097</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.30365586519027</v>
       </c>
       <c r="X5" t="n">
         <v>-10133.09697532537</v>
@@ -4564,7 +4432,7 @@
         <v>486.5792081841189</v>
       </c>
       <c r="Z5" t="n">
-        <v>640.63</v>
+        <v>1066030428.940031</v>
       </c>
       <c r="AA5" t="n">
         <v>1.848622104889686e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>86.97273533993433</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.909x + -10350.661</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.90896901900303</v>
       </c>
       <c r="X6" t="n">
         <v>-10350.66085402469</v>
@@ -4616,7 +4482,7 @@
         <v>481.3002605669151</v>
       </c>
       <c r="Z6" t="n">
-        <v>622.0419999999999</v>
+        <v>131931694.6908549</v>
       </c>
       <c r="AA6" t="n">
         <v>1.822322986399571e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>87.02392868172051</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 19.235x + -10352.622</t>
-        </is>
+      <c r="W7" t="n">
+        <v>19.23483551983694</v>
       </c>
       <c r="X7" t="n">
         <v>-10352.62168042783</v>
@@ -4668,7 +4532,7 @@
         <v>475.5761945644315</v>
       </c>
       <c r="Z7" t="n">
-        <v>609.261</v>
+        <v>390898171.2236999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.800972400513979e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>87.04530412314432</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.374x + -10236.732</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.37423764942856</v>
       </c>
       <c r="X8" t="n">
         <v>-10236.73152171815</v>
@@ -4720,7 +4582,7 @@
         <v>469.4991716414882</v>
       </c>
       <c r="Z8" t="n">
-        <v>600.997</v>
+        <v>128941831.0295638</v>
       </c>
       <c r="AA8" t="n">
         <v>1.783459648837793e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>87.08828942822355</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.661x + -10235.420</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.66076169421184</v>
       </c>
       <c r="X9" t="n">
         <v>-10235.41958354107</v>
@@ -4772,7 +4632,7 @@
         <v>463.4254608838797</v>
       </c>
       <c r="Z9" t="n">
-        <v>593.579</v>
+        <v>380876671.3098059</v>
       </c>
       <c r="AA9" t="n">
         <v>1.769803435356875e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>87.12680688794293</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.925x + -10204.356</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.92478131305116</v>
       </c>
       <c r="X10" t="n">
         <v>-10204.35551686627</v>
@@ -4824,7 +4682,7 @@
         <v>452.3551432983907</v>
       </c>
       <c r="Z10" t="n">
-        <v>584.5350000000001</v>
+        <v>19033.55547754413</v>
       </c>
       <c r="AA10" t="n">
         <v>1.57660098914171e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>87.21278467146085</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 20.540x + -10422.603</t>
-        </is>
+      <c r="W11" t="n">
+        <v>20.54042114758403</v>
       </c>
       <c r="X11" t="n">
         <v>-10422.60324982645</v>
@@ -4876,7 +4732,7 @@
         <v>451.4474092345619</v>
       </c>
       <c r="Z11" t="n">
-        <v>574.345</v>
+        <v>247499140.3841373</v>
       </c>
       <c r="AA11" t="n">
         <v>1.743270847449702e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>87.21836579054334</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.582x + -10263.565</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.58169882942542</v>
       </c>
       <c r="X12" t="n">
         <v>-10263.56464186314</v>
@@ -4928,7 +4782,7 @@
         <v>445.7804411165236</v>
       </c>
       <c r="Z12" t="n">
-        <v>571.0279999999999</v>
+        <v>1218887979.656995</v>
       </c>
       <c r="AA12" t="n">
         <v>1.733676593565875e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>87.26918221924089</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 20.965x + -10325.783</t>
-        </is>
+      <c r="W13" t="n">
+        <v>20.96529037908487</v>
       </c>
       <c r="X13" t="n">
         <v>-10325.78309714612</v>
@@ -4980,7 +4832,7 @@
         <v>440.2005039536013</v>
       </c>
       <c r="Z13" t="n">
-        <v>563.518</v>
+        <v>481573007.1813665</v>
       </c>
       <c r="AA13" t="n">
         <v>1.723032509058292e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>87.29428391070608</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 21.160x + -10263.641</t>
-        </is>
+      <c r="W14" t="n">
+        <v>21.16008480675994</v>
       </c>
       <c r="X14" t="n">
         <v>-10263.64102231978</v>
@@ -5032,7 +4882,7 @@
         <v>434.723897092129</v>
       </c>
       <c r="Z14" t="n">
-        <v>556.8129999999999</v>
+        <v>237769632.4421493</v>
       </c>
       <c r="AA14" t="n">
         <v>1.712948978600426e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.32539904225365</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 21.407x + -10241.786</t>
-        </is>
+      <c r="W15" t="n">
+        <v>21.40661618350779</v>
       </c>
       <c r="X15" t="n">
         <v>-10241.78598667324</v>
@@ -5084,7 +4932,7 @@
         <v>371.2507098873601</v>
       </c>
       <c r="Z15" t="n">
-        <v>552.0430000000001</v>
+        <v>14271.00293336709</v>
       </c>
       <c r="AA15" t="n">
         <v>1.830378588769889e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.33485663091844</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 21.483x + -10115.925</t>
-        </is>
+      <c r="W16" t="n">
+        <v>21.48269046211154</v>
       </c>
       <c r="X16" t="n">
         <v>-10115.92548771846</v>
@@ -5136,7 +4982,7 @@
         <v>370.5408170808202</v>
       </c>
       <c r="Z16" t="n">
-        <v>548.376</v>
+        <v>14088.60709471307</v>
       </c>
       <c r="AA16" t="n">
         <v>1.866074475234489e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>87.34918501267336</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.599x + -10017.243</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.59897751061589</v>
       </c>
       <c r="X17" t="n">
         <v>-10017.24339804782</v>
@@ -5188,7 +5032,7 @@
         <v>418.7338970947847</v>
       </c>
       <c r="Z17" t="n">
-        <v>545.372</v>
+        <v>228612614.3248598</v>
       </c>
       <c r="AA17" t="n">
         <v>1.688584923609476e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.38391162875087</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.886x + -10020.238</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.88609463819268</v>
       </c>
       <c r="X18" t="n">
         <v>-10020.23849438376</v>
@@ -5240,7 +5082,7 @@
         <v>413.399184936012</v>
       </c>
       <c r="Z18" t="n">
-        <v>540.278</v>
+        <v>225758056.4968992</v>
       </c>
       <c r="AA18" t="n">
         <v>1.68121973185646e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.4219028213531</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 22.209x + -10042.574</t>
-        </is>
+      <c r="W19" t="n">
+        <v>22.20905654856715</v>
       </c>
       <c r="X19" t="n">
         <v>-10042.57369212209</v>
@@ -5292,7 +5132,7 @@
         <v>408.0633665346227</v>
       </c>
       <c r="Z19" t="n">
-        <v>535.605</v>
+        <v>122370120.8085435</v>
       </c>
       <c r="AA19" t="n">
         <v>1.673873645501824e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.46456485809695</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 22.583x + -10071.807</t>
-        </is>
+      <c r="W20" t="n">
+        <v>22.58325389037036</v>
       </c>
       <c r="X20" t="n">
         <v>-10071.80720284362</v>
@@ -5344,7 +5182,7 @@
         <v>396.6682220815492</v>
       </c>
       <c r="Z20" t="n">
-        <v>527.046</v>
+        <v>15040.31542558245</v>
       </c>
       <c r="AA20" t="n">
         <v>1.716931347568358e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.46018208192284</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 22.544x + -9901.441</t>
-        </is>
+      <c r="W21" t="n">
+        <v>22.5442326720281</v>
       </c>
       <c r="X21" t="n">
         <v>-9901.44086903851</v>
@@ -5396,7 +5232,7 @@
         <v>397.5219674641309</v>
       </c>
       <c r="Z21" t="n">
-        <v>528.6500000000001</v>
+        <v>542188241.5899316</v>
       </c>
       <c r="AA21" t="n">
         <v>1.661870710057581e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>87.50748958817188</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.973x + -9956.995</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.97267493502651</v>
       </c>
       <c r="X22" t="n">
         <v>-9956.995427501939</v>
@@ -5448,7 +5282,7 @@
         <v>375.5911874316374</v>
       </c>
       <c r="Z22" t="n">
-        <v>520.4110000000001</v>
+        <v>3216.194448504606</v>
       </c>
       <c r="AA22" t="n">
         <v>3.15235095117835e-06</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>82.43146814434007</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.526x + -4906.653</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.526180134975394</v>
       </c>
       <c r="X2" t="n">
         <v>-4906.653469620401</v>
@@ -5646,7 +5478,7 @@
         <v>429.6230202017823</v>
       </c>
       <c r="Z2" t="n">
-        <v>1440.061</v>
+        <v>13632.91162896371</v>
       </c>
       <c r="AA2" t="n">
         <v>1.76095697154734e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.2843643292851</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.991x + -5956.536</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.991118926571867</v>
       </c>
       <c r="X3" t="n">
         <v>-5956.536332184563</v>
@@ -5698,7 +5528,7 @@
         <v>418.3909006030254</v>
       </c>
       <c r="Z3" t="n">
-        <v>1093.85</v>
+        <v>13015.70243212981</v>
       </c>
       <c r="AA3" t="n">
         <v>1.858001589130673e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.23755006454805</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.003x + -6971.035</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.00301676073075</v>
       </c>
       <c r="X4" t="n">
         <v>-6971.035278165876</v>
@@ -5750,7 +5578,7 @@
         <v>415.9180064078726</v>
       </c>
       <c r="Z4" t="n">
-        <v>922.6510000000001</v>
+        <v>12778.77446574732</v>
       </c>
       <c r="AA4" t="n">
         <v>1.859463378083317e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>85.77015761713605</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.521x + -7715.469</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.52098910127571</v>
       </c>
       <c r="X5" t="n">
         <v>-7715.468949892682</v>
@@ -5802,7 +5628,7 @@
         <v>411.2921404591351</v>
       </c>
       <c r="Z5" t="n">
-        <v>822.5970000000001</v>
+        <v>12610.20393195065</v>
       </c>
       <c r="AA5" t="n">
         <v>1.978829766619678e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.13889687054176</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.817x + -8355.625</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.81675557844247</v>
       </c>
       <c r="X6" t="n">
         <v>-8355.624879283245</v>
@@ -5854,7 +5678,7 @@
         <v>497.9991348708024</v>
       </c>
       <c r="Z6" t="n">
-        <v>759.525</v>
+        <v>275902571.6437891</v>
       </c>
       <c r="AA6" t="n">
         <v>2.060720263312138e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.34544783306758</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.657x + -8663.689</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.65665373048136</v>
       </c>
       <c r="X7" t="n">
         <v>-8663.688710141796</v>
@@ -5906,7 +5728,7 @@
         <v>491.2385879836768</v>
       </c>
       <c r="Z7" t="n">
-        <v>719.095</v>
+        <v>235478182.0657036</v>
       </c>
       <c r="AA7" t="n">
         <v>1.99405388123095e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.53091970359502</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.496x + -8980.051</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.49594230121561</v>
       </c>
       <c r="X8" t="n">
         <v>-8980.05141716383</v>
@@ -5958,7 +5778,7 @@
         <v>484.2022281744278</v>
       </c>
       <c r="Z8" t="n">
-        <v>686.039</v>
+        <v>265067634.3005174</v>
       </c>
       <c r="AA8" t="n">
         <v>1.943512660502939e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.66738375692333</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.173x + -9199.664</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.17303966190399</v>
       </c>
       <c r="X9" t="n">
         <v>-9199.663776734364</v>
@@ -6010,7 +5828,7 @@
         <v>477.2630158202608</v>
       </c>
       <c r="Z9" t="n">
-        <v>662.4690000000001</v>
+        <v>522997955.0189785</v>
       </c>
       <c r="AA9" t="n">
         <v>1.905462105206098e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.7501538257503</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.611x + -9259.913</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.61139418433698</v>
       </c>
       <c r="X10" t="n">
         <v>-9259.912521421697</v>
@@ -6062,7 +5878,7 @@
         <v>470.6356380197503</v>
       </c>
       <c r="Z10" t="n">
-        <v>644.6530000000001</v>
+        <v>193889728.1771298</v>
       </c>
       <c r="AA10" t="n">
         <v>1.874661518942262e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.8818227022586</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.357x + -9554.077</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.35662202035759</v>
       </c>
       <c r="X11" t="n">
         <v>-9554.076816665018</v>
@@ -6114,7 +5928,7 @@
         <v>464.3983617687056</v>
       </c>
       <c r="Z11" t="n">
-        <v>626.192</v>
+        <v>381171840.461351</v>
       </c>
       <c r="AA11" t="n">
         <v>1.85087056957529e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>83.80803281961077</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.217x + -5330.651</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.217191926709539</v>
       </c>
       <c r="X2" t="n">
         <v>-5330.651193525006</v>
@@ -6312,7 +6124,7 @@
         <v>406.5263877950339</v>
       </c>
       <c r="Z2" t="n">
-        <v>1157.117</v>
+        <v>12642.72418967486</v>
       </c>
       <c r="AA2" t="n">
         <v>1.902781240056709e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.83759170343708</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.741x + -7786.253</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.74083065649531</v>
       </c>
       <c r="X3" t="n">
         <v>-7786.252547697837</v>
@@ -6364,7 +6174,7 @@
         <v>402.5632672503307</v>
       </c>
       <c r="Z3" t="n">
-        <v>810.874</v>
+        <v>12428.16809904474</v>
       </c>
       <c r="AA3" t="n">
         <v>2.029988712923931e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.406450606668</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.923x + -8918.000</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.92315153544811</v>
       </c>
       <c r="X4" t="n">
         <v>-8918.000010221309</v>
@@ -6416,7 +6224,7 @@
         <v>490.7816655345515</v>
       </c>
       <c r="Z4" t="n">
-        <v>710.1270000000001</v>
+        <v>403831423.0850303</v>
       </c>
       <c r="AA4" t="n">
         <v>2.016494255454809e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.59079509749448</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.786x + -9212.278</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.78636139048578</v>
       </c>
       <c r="X5" t="n">
         <v>-9212.277538662594</v>
@@ -6468,7 +6274,7 @@
         <v>485.0273788493913</v>
       </c>
       <c r="Z5" t="n">
-        <v>672.891</v>
+        <v>399159616.1825728</v>
       </c>
       <c r="AA5" t="n">
         <v>1.950740920061707e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>86.76041595398152</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.667x + -9598.420</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.66730197519954</v>
       </c>
       <c r="X6" t="n">
         <v>-9598.420101327862</v>
@@ -6520,7 +6324,7 @@
         <v>479.0293725002069</v>
       </c>
       <c r="Z6" t="n">
-        <v>647.3280000000001</v>
+        <v>393594127.5226604</v>
       </c>
       <c r="AA6" t="n">
         <v>1.913407660562732e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.84147896049464</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.122x + -9671.259</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.12168655372665</v>
       </c>
       <c r="X7" t="n">
         <v>-9671.259169719857</v>
@@ -6572,7 +6374,7 @@
         <v>473.0622106069381</v>
       </c>
       <c r="Z7" t="n">
-        <v>630.348</v>
+        <v>519419597.5195135</v>
       </c>
       <c r="AA7" t="n">
         <v>1.884529039014557e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.92651739183607</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.624x + -9823.447</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.62408867942026</v>
       </c>
       <c r="X8" t="n">
         <v>-9823.446539917808</v>
@@ -6624,7 +6424,7 @@
         <v>467.4286805380581</v>
       </c>
       <c r="Z8" t="n">
-        <v>617.6009999999999</v>
+        <v>25998813.56134218</v>
       </c>
       <c r="AA8" t="n">
         <v>1.861501394209685e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>86.99006427642644</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.018x + -9892.229</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.01803486729019</v>
       </c>
       <c r="X9" t="n">
         <v>-9892.228548268542</v>
@@ -6676,7 +6474,7 @@
         <v>461.9733608989825</v>
       </c>
       <c r="Z9" t="n">
-        <v>604.943</v>
+        <v>506282223.6626672</v>
       </c>
       <c r="AA9" t="n">
         <v>1.845545453528326e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>87.00453847256939</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.110x + -9772.808</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.11009969566631</v>
       </c>
       <c r="X10" t="n">
         <v>-9772.807842384238</v>
@@ -6728,7 +6524,7 @@
         <v>456.7392632204899</v>
       </c>
       <c r="Z10" t="n">
-        <v>599.747</v>
+        <v>267490486.5192766</v>
       </c>
       <c r="AA10" t="n">
         <v>1.831211419317002e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>87.05765847991218</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.456x + -9835.282</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.45573065087112</v>
       </c>
       <c r="X11" t="n">
         <v>-9835.281599579974</v>
@@ -6780,7 +6574,7 @@
         <v>431.5640462242851</v>
       </c>
       <c r="Z11" t="n">
-        <v>590.6779999999999</v>
+        <v>18801.07281796883</v>
       </c>
       <c r="AA11" t="n">
         <v>1.597913339886611e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>87.12188335730089</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 19.891x + -9947.877</t>
-        </is>
+      <c r="W12" t="n">
+        <v>19.89063917113916</v>
       </c>
       <c r="X12" t="n">
         <v>-9947.876997571244</v>
@@ -6832,7 +6624,7 @@
         <v>446.955114352198</v>
       </c>
       <c r="Z12" t="n">
-        <v>579.7779999999999</v>
+        <v>244719590.4818788</v>
       </c>
       <c r="AA12" t="n">
         <v>1.804911603909267e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>87.11057003409572</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.813x + -9746.406</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.81262760123422</v>
       </c>
       <c r="X13" t="n">
         <v>-9746.406023358328</v>
@@ -6884,7 +6674,7 @@
         <v>442.3124520156859</v>
       </c>
       <c r="Z13" t="n">
-        <v>577.5810000000001</v>
+        <v>484349398.751979</v>
       </c>
       <c r="AA13" t="n">
         <v>1.795544539557422e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>87.19282027189048</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 20.394x + -9976.647</t>
-        </is>
+      <c r="W14" t="n">
+        <v>20.39410805037572</v>
       </c>
       <c r="X14" t="n">
         <v>-9976.647378674983</v>
@@ -6936,7 +6724,7 @@
         <v>437.6535848804979</v>
       </c>
       <c r="Z14" t="n">
-        <v>568.876</v>
+        <v>957617410.9524475</v>
       </c>
       <c r="AA14" t="n">
         <v>1.786284545913437e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>87.17991225279945</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.301x + -9758.860</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.30061086878671</v>
       </c>
       <c r="X15" t="n">
         <v>-9758.860268520661</v>
@@ -6988,7 +6774,7 @@
         <v>376.286958931379</v>
       </c>
       <c r="Z15" t="n">
-        <v>565.7079999999999</v>
+        <v>14384.64403881321</v>
       </c>
       <c r="AA15" t="n">
         <v>1.795452761962009e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>87.24525866733592</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 20.783x + -9909.661</t>
-        </is>
+      <c r="W16" t="n">
+        <v>20.78294006953185</v>
       </c>
       <c r="X16" t="n">
         <v>-9909.661166001237</v>
@@ -7040,7 +6824,7 @@
         <v>375.0470348808144</v>
       </c>
       <c r="Z16" t="n">
-        <v>557.674</v>
+        <v>14226.21648973086</v>
       </c>
       <c r="AA16" t="n">
         <v>1.803149429303379e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>87.28075196465225</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.055x + -9933.115</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.05462758697695</v>
       </c>
       <c r="X17" t="n">
         <v>-9933.115345005439</v>
@@ -7092,7 +6874,7 @@
         <v>423.4207669624959</v>
       </c>
       <c r="Z17" t="n">
-        <v>553.2089999999999</v>
+        <v>347168929.1431149</v>
       </c>
       <c r="AA17" t="n">
         <v>1.760298822197493e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.29584037462348</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.172x + -9841.999</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.17228227836089</v>
       </c>
       <c r="X18" t="n">
         <v>-9841.999226486749</v>
@@ -7144,7 +6924,7 @@
         <v>418.6335670009601</v>
       </c>
       <c r="Z18" t="n">
-        <v>548.5</v>
+        <v>116107200.4301946</v>
       </c>
       <c r="AA18" t="n">
         <v>1.751255444743452e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.29893838289193</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 21.197x + -9705.656</t>
-        </is>
+      <c r="W19" t="n">
+        <v>21.19660210689043</v>
       </c>
       <c r="X19" t="n">
         <v>-9705.656288385184</v>
@@ -7196,7 +6974,7 @@
         <v>413.8931146539479</v>
       </c>
       <c r="Z19" t="n">
-        <v>546.596</v>
+        <v>113545739.5923299</v>
       </c>
       <c r="AA19" t="n">
         <v>1.744172360890317e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.32316930768758</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.389x + -9670.692</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.38875905435805</v>
       </c>
       <c r="X20" t="n">
         <v>-9670.69153992405</v>
@@ -7248,7 +7024,7 @@
         <v>409.0849011173936</v>
       </c>
       <c r="Z20" t="n">
-        <v>542.307</v>
+        <v>670518833.5164906</v>
       </c>
       <c r="AA20" t="n">
         <v>1.737191179104628e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.35571614915852</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.652x + -9665.573</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.65240109565561</v>
       </c>
       <c r="X21" t="n">
         <v>-9665.57285770849</v>
@@ -7300,7 +7074,7 @@
         <v>387.7908753102142</v>
       </c>
       <c r="Z21" t="n">
-        <v>536.362</v>
+        <v>6692.121581603515</v>
       </c>
       <c r="AA21" t="n">
         <v>3.738064730148106e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>87.38390616017077</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 21.886x + -9637.664</t>
-        </is>
+      <c r="W22" t="n">
+        <v>21.8860488247102</v>
       </c>
       <c r="X22" t="n">
         <v>-9637.663903255019</v>
@@ -7352,7 +7124,7 @@
         <v>399.4904205218741</v>
       </c>
       <c r="Z22" t="n">
-        <v>531.24</v>
+        <v>219135433.561069</v>
       </c>
       <c r="AA22" t="n">
         <v>1.721173291768883e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.25551928412541</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.456x + -4916.884</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.455935831900218</v>
       </c>
       <c r="X2" t="n">
         <v>-4916.883607405103</v>
@@ -7550,7 +7320,7 @@
         <v>406.7013749986835</v>
       </c>
       <c r="Z2" t="n">
-        <v>1223.752</v>
+        <v>12673.95832488556</v>
       </c>
       <c r="AA2" t="n">
         <v>2.041051549785037e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.41471683543011</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.469x + -7108.067</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.46889401353725</v>
       </c>
       <c r="X3" t="n">
         <v>-7108.066875592928</v>
@@ -7602,7 +7370,7 @@
         <v>402.3967333229889</v>
       </c>
       <c r="Z3" t="n">
-        <v>868.0219999999999</v>
+        <v>12438.40576673371</v>
       </c>
       <c r="AA3" t="n">
         <v>1.908832667328552e-07</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.12056153617527</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.747x + -8241.052</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.7465143923594</v>
       </c>
       <c r="X4" t="n">
         <v>-8241.051550060061</v>
@@ -7654,7 +7420,7 @@
         <v>399.0392363469371</v>
       </c>
       <c r="Z4" t="n">
-        <v>739.688</v>
+        <v>12260.68819178515</v>
       </c>
       <c r="AA4" t="n">
         <v>2.044897567485924e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.48516577153818</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.281x + -8947.292</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.2806791870285</v>
       </c>
       <c r="X5" t="n">
         <v>-8947.291811173791</v>
@@ -7706,7 +7470,7 @@
         <v>483.2367862327099</v>
       </c>
       <c r="Z5" t="n">
-        <v>673.2910000000001</v>
+        <v>795434118.2919952</v>
       </c>
       <c r="AA5" t="n">
         <v>2.042513512471488e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.67737573901671</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.225x + -9270.857</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.22479987946551</v>
       </c>
       <c r="X6" t="n">
         <v>-9270.857118003354</v>
@@ -7758,7 +7520,7 @@
         <v>476.0343846787736</v>
       </c>
       <c r="Z6" t="n">
-        <v>634.595</v>
+        <v>913377199.1937584</v>
       </c>
       <c r="AA6" t="n">
         <v>1.982868915923945e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.80559389034082</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.918x + -9449.577</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.91769719831354</v>
       </c>
       <c r="X7" t="n">
         <v>-9449.576603802907</v>
@@ -7810,7 +7570,7 @@
         <v>468.5608150129989</v>
       </c>
       <c r="Z7" t="n">
-        <v>609.0949999999999</v>
+        <v>769263496.4838506</v>
       </c>
       <c r="AA7" t="n">
         <v>1.94258544206764e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.89852981274684</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.456x + -9527.183</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.45570112438506</v>
       </c>
       <c r="X8" t="n">
         <v>-9527.183326988787</v>
@@ -7862,7 +7620,7 @@
         <v>461.0746054231596</v>
       </c>
       <c r="Z8" t="n">
-        <v>588.9970000000001</v>
+        <v>191129122.1236848</v>
       </c>
       <c r="AA8" t="n">
         <v>1.911993270942463e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>87.01807146389051</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.197x + -9769.072</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.19698561240869</v>
       </c>
       <c r="X9" t="n">
         <v>-9769.071633018755</v>
@@ -7914,7 +7670,7 @@
         <v>453.9242508402796</v>
       </c>
       <c r="Z9" t="n">
-        <v>571.9150000000002</v>
+        <v>372760312.7674243</v>
       </c>
       <c r="AA9" t="n">
         <v>1.889777124154979e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>87.10289545096438</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.760x + -9898.148</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.7600536932658</v>
       </c>
       <c r="X10" t="n">
         <v>-9898.147979322495</v>
@@ -7966,7 +7720,7 @@
         <v>433.2829199540236</v>
       </c>
       <c r="Z10" t="n">
-        <v>558.7170000000001</v>
+        <v>18601.14084679451</v>
       </c>
       <c r="AA10" t="n">
         <v>1.673282442456265e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>87.17089277067454</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 20.236x + -9966.186</t>
-        </is>
+      <c r="W11" t="n">
+        <v>20.23578563964865</v>
       </c>
       <c r="X11" t="n">
         <v>-9966.186121799577</v>
@@ -8018,7 +7770,7 @@
         <v>440.7223450521758</v>
       </c>
       <c r="Z11" t="n">
-        <v>544.614</v>
+        <v>361616311.7910796</v>
       </c>
       <c r="AA11" t="n">
         <v>1.854817428250025e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>86.47229885089921</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.221x + -9101.121</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.22114759837187</v>
       </c>
       <c r="X2" t="n">
         <v>-9101.12092754331</v>
@@ -8216,7 +7966,7 @@
         <v>404.4399193174224</v>
       </c>
       <c r="Z2" t="n">
-        <v>665.9810000000001</v>
+        <v>12345.21611574376</v>
       </c>
       <c r="AA2" t="n">
         <v>1.99883031353931e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.68515496020835</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.265x + -9557.452</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.26531340498492</v>
       </c>
       <c r="X3" t="n">
         <v>-9557.452151639169</v>
@@ -8268,7 +8016,7 @@
         <v>488.3659983783317</v>
       </c>
       <c r="Z3" t="n">
-        <v>629.7900000000001</v>
+        <v>269850633.6384178</v>
       </c>
       <c r="AA3" t="n">
         <v>2.021145338287357e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.81762399037687</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.986x + -9835.013</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.98557043939468</v>
       </c>
       <c r="X4" t="n">
         <v>-9835.01333775173</v>
@@ -8320,7 +8066,7 @@
         <v>481.8846398858158</v>
       </c>
       <c r="Z4" t="n">
-        <v>609.718</v>
+        <v>461881724.3072599</v>
       </c>
       <c r="AA4" t="n">
         <v>1.988277955919509e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.8931267023886</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.424x + -9902.703</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.42354229138594</v>
       </c>
       <c r="X5" t="n">
         <v>-9902.70273760533</v>
@@ -8372,7 +8116,7 @@
         <v>474.9741872024891</v>
       </c>
       <c r="Z5" t="n">
-        <v>597.199</v>
+        <v>129967435.5110029</v>
       </c>
       <c r="AA5" t="n">
         <v>1.964067020412649e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>86.90912910900869</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.519x + -9762.400</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.51911349111962</v>
       </c>
       <c r="X6" t="n">
         <v>-9762.399579159044</v>
@@ -8424,7 +8166,7 @@
         <v>468.1697256762132</v>
       </c>
       <c r="Z6" t="n">
-        <v>591.9929999999999</v>
+        <v>256938874.3915394</v>
       </c>
       <c r="AA6" t="n">
         <v>1.947734700580416e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>86.9600921985341</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.830x + -9770.419</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.8301787328163</v>
       </c>
       <c r="X7" t="n">
         <v>-9770.418568911437</v>
@@ -8476,7 +8216,7 @@
         <v>461.8220178493131</v>
       </c>
       <c r="Z7" t="n">
-        <v>583.7280000000001</v>
+        <v>17788407.85547392</v>
       </c>
       <c r="AA7" t="n">
         <v>1.927872500261712e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.98052124933479</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.958x + -9670.831</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.95781768805162</v>
       </c>
       <c r="X8" t="n">
         <v>-9670.831283868571</v>
@@ -8528,7 +8266,7 @@
         <v>455.8673221642141</v>
       </c>
       <c r="Z8" t="n">
-        <v>578.8610000000001</v>
+        <v>499497517.2968128</v>
       </c>
       <c r="AA8" t="n">
         <v>1.919593652997132e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.99892763269111</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.074x + -9581.306</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.07430598264733</v>
       </c>
       <c r="X9" t="n">
         <v>-9581.306293118661</v>
@@ -8580,7 +8316,7 @@
         <v>450.3495627653526</v>
       </c>
       <c r="Z9" t="n">
-        <v>575.672</v>
+        <v>246920193.1798993</v>
       </c>
       <c r="AA9" t="n">
         <v>1.90864635234706e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>87.04101803178727</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.346x + -9607.697</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.34612417454283</v>
       </c>
       <c r="X10" t="n">
         <v>-9607.697271928855</v>
@@ -8632,7 +8366,7 @@
         <v>433.8294656084345</v>
       </c>
       <c r="Z10" t="n">
-        <v>571.588</v>
+        <v>18519.18294441571</v>
       </c>
       <c r="AA10" t="n">
         <v>1.681629965889808e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>87.08380951057404</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.631x + -9635.946</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.63050628420563</v>
       </c>
       <c r="X11" t="n">
         <v>-9635.946465106061</v>
@@ -8684,7 +8416,7 @@
         <v>440.1205649007259</v>
       </c>
       <c r="Z11" t="n">
-        <v>565.301</v>
+        <v>248156617.5353783</v>
       </c>
       <c r="AA11" t="n">
         <v>1.888682204305977e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>87.09040828442785</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 19.675x + -9513.391</t>
-        </is>
+      <c r="W12" t="n">
+        <v>19.67510395075628</v>
       </c>
       <c r="X12" t="n">
         <v>-9513.390534011367</v>
@@ -8736,7 +8466,7 @@
         <v>382.8694290590216</v>
       </c>
       <c r="Z12" t="n">
-        <v>562.8180000000001</v>
+        <v>14469.59741488218</v>
       </c>
       <c r="AA12" t="n">
         <v>1.862969646006185e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>87.09265344524387</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.690x + -9371.072</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.69032393829497</v>
       </c>
       <c r="X13" t="n">
         <v>-9371.071786548766</v>
@@ -8788,7 +8516,7 @@
         <v>430.2630813247082</v>
       </c>
       <c r="Z13" t="n">
-        <v>559.712</v>
+        <v>119801808.4312982</v>
       </c>
       <c r="AA13" t="n">
         <v>1.870885169653327e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>87.1168705858537</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.856x + -9344.808</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.8559978885862</v>
       </c>
       <c r="X14" t="n">
         <v>-9344.808101891927</v>
@@ -8840,7 +8566,7 @@
         <v>425.4186914818209</v>
       </c>
       <c r="Z14" t="n">
-        <v>557.832</v>
+        <v>350390756.63888</v>
       </c>
       <c r="AA14" t="n">
         <v>1.865259779459644e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>87.15933099306569</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.153x + -9375.785</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.15328987989476</v>
       </c>
       <c r="X15" t="n">
         <v>-9375.785307874887</v>
@@ -8892,7 +8616,7 @@
         <v>420.4897265050199</v>
       </c>
       <c r="Z15" t="n">
-        <v>551.114</v>
+        <v>584701814.4546447</v>
       </c>
       <c r="AA15" t="n">
         <v>1.857085210908023e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>87.15305956671632</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 20.109x + -9210.874</t>
-        </is>
+      <c r="W16" t="n">
+        <v>20.108821981592</v>
       </c>
       <c r="X16" t="n">
         <v>-9210.873821406965</v>
@@ -8944,7 +8666,7 @@
         <v>415.4866774599119</v>
       </c>
       <c r="Z16" t="n">
-        <v>551.1800000000001</v>
+        <v>343793953.5746257</v>
       </c>
       <c r="AA16" t="n">
         <v>1.852958126006104e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>87.19294677907739</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.395x + -9244.894</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.39502863661771</v>
       </c>
       <c r="X17" t="n">
         <v>-9244.894357243344</v>
@@ -8996,7 +8716,7 @@
         <v>392.9751011143074</v>
       </c>
       <c r="Z17" t="n">
-        <v>546.625</v>
+        <v>6800.783006640148</v>
       </c>
       <c r="AA17" t="n">
         <v>5.356609355350524e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>87.19227593676838</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.390x + -9094.909</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.39014789756453</v>
       </c>
       <c r="X18" t="n">
         <v>-9094.909101556685</v>
@@ -9048,7 +8766,7 @@
         <v>405.8943965311582</v>
       </c>
       <c r="Z18" t="n">
-        <v>543.67</v>
+        <v>888811135.5946382</v>
       </c>
       <c r="AA18" t="n">
         <v>1.841049705917868e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.24495352083824</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.781x + -9187.541</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.78063461813544</v>
       </c>
       <c r="X19" t="n">
         <v>-9187.541307310519</v>
@@ -9100,7 +8816,7 @@
         <v>383.6129946062841</v>
       </c>
       <c r="Z19" t="n">
-        <v>539.5150000000001</v>
+        <v>3295.095923306363</v>
       </c>
       <c r="AA19" t="n">
         <v>2.81412877121526e-06</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.25628889508883</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.867x + -9111.270</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.86661998500331</v>
       </c>
       <c r="X20" t="n">
         <v>-9111.269712031131</v>
@@ -9152,7 +8866,7 @@
         <v>380.2516164576234</v>
       </c>
       <c r="Z20" t="n">
-        <v>537.1609999999999</v>
+        <v>3259.133067576397</v>
       </c>
       <c r="AA20" t="n">
         <v>2.403575972039832e-06</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.27619462846373</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.019x + -9078.589</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.01934702871606</v>
       </c>
       <c r="X21" t="n">
         <v>-9078.588658721843</v>
@@ -9204,7 +8916,7 @@
         <v>392.8432717743761</v>
       </c>
       <c r="Z21" t="n">
-        <v>534.6949999999999</v>
+        <v>107719829.1197938</v>
       </c>
       <c r="AA21" t="n">
         <v>1.825235297600877e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.29618691802891</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 21.175x + -9055.589</t>
-        </is>
+      <c r="W22" t="n">
+        <v>21.17499992964578</v>
       </c>
       <c r="X22" t="n">
         <v>-9055.588524306166</v>
@@ -9256,7 +8966,7 @@
         <v>381.7539626031968</v>
       </c>
       <c r="Z22" t="n">
-        <v>532.751</v>
+        <v>6189.487186110757</v>
       </c>
       <c r="AA22" t="n">
         <v>6.909160522697561e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.02918359955979</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.561x + -5125.456</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.561208770010582</v>
       </c>
       <c r="X2" t="n">
         <v>-5125.45594776426</v>
@@ -9454,7 +9162,7 @@
         <v>394.0273055527683</v>
       </c>
       <c r="Z2" t="n">
-        <v>1068.698</v>
+        <v>11885.6028818909</v>
       </c>
       <c r="AA2" t="n">
         <v>1.97948087298246e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.09342005273813</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.644x + -7701.822</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.643746121247</v>
       </c>
       <c r="X3" t="n">
         <v>-7701.821708693514</v>
@@ -9506,7 +9212,7 @@
         <v>467.4287572890287</v>
       </c>
       <c r="Z3" t="n">
-        <v>716.629</v>
+        <v>256549186.5122571</v>
       </c>
       <c r="AA3" t="n">
         <v>2.181598486608101e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.60220700984418</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.843x + -8738.454</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.84287355208352</v>
       </c>
       <c r="X4" t="n">
         <v>-8738.453666687641</v>
@@ -9558,7 +9262,7 @@
         <v>460.322971337899</v>
       </c>
       <c r="Z4" t="n">
-        <v>628.296</v>
+        <v>252804608.0011402</v>
       </c>
       <c r="AA4" t="n">
         <v>2.061608372826926e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.81700727223844</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.982x + -9151.082</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.98207848188511</v>
       </c>
       <c r="X5" t="n">
         <v>-9151.082280136625</v>
@@ -9610,7 +9312,7 @@
         <v>452.8972180414294</v>
       </c>
       <c r="Z5" t="n">
-        <v>587.6859999999999</v>
+        <v>255803581.5874311</v>
       </c>
       <c r="AA5" t="n">
         <v>2.005989739130881e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.94560410174707</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.741x + -9348.650</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.74069219158655</v>
       </c>
       <c r="X6" t="n">
         <v>-9348.650045344886</v>
@@ -9662,7 +9362,7 @@
         <v>445.0636877213517</v>
       </c>
       <c r="Z6" t="n">
-        <v>564.7939999999999</v>
+        <v>243658313.1678612</v>
       </c>
       <c r="AA6" t="n">
         <v>1.97140394558811e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>87.05300945687455</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 19.425x + -9503.690</t>
-        </is>
+      <c r="W7" t="n">
+        <v>19.42498420527015</v>
       </c>
       <c r="X7" t="n">
         <v>-9503.690102312696</v>
@@ -9714,7 +9412,7 @@
         <v>385.3661195390713</v>
       </c>
       <c r="Z7" t="n">
-        <v>545.7549999999999</v>
+        <v>14547.46765430388</v>
       </c>
       <c r="AA7" t="n">
         <v>2.008013279205159e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>87.09272163989831</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.691x + -9405.700</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.69078659868019</v>
       </c>
       <c r="X8" t="n">
         <v>-9405.70016972862</v>
@@ -9766,7 +9462,7 @@
         <v>430.3080223354208</v>
       </c>
       <c r="Z8" t="n">
-        <v>533.202</v>
+        <v>472047266.44802</v>
       </c>
       <c r="AA8" t="n">
         <v>1.924431853210026e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>87.1982615453858</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 20.434x + -9633.690</t>
-        </is>
+      <c r="W9" t="n">
+        <v>20.43377896695346</v>
       </c>
       <c r="X9" t="n">
         <v>-9633.690206354831</v>
@@ -9818,7 +9512,7 @@
         <v>423.6776555416881</v>
       </c>
       <c r="Z9" t="n">
-        <v>519.3290000000001</v>
+        <v>118879938.0130415</v>
       </c>
       <c r="AA9" t="n">
         <v>1.908423511782025e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.24952107295046</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 20.815x + -9636.609</t>
-        </is>
+      <c r="W10" t="n">
+        <v>20.81519695331701</v>
       </c>
       <c r="X10" t="n">
         <v>-9636.609214677765</v>
@@ -9870,7 +9562,7 @@
         <v>417.5579821825693</v>
       </c>
       <c r="Z10" t="n">
-        <v>508.28</v>
+        <v>684358810.9056885</v>
       </c>
       <c r="AA10" t="n">
         <v>1.894254397876975e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>87.29825037858569</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 21.191x + -9670.767</t>
-        </is>
+      <c r="W11" t="n">
+        <v>21.19119635597688</v>
       </c>
       <c r="X11" t="n">
         <v>-9670.766551158607</v>
@@ -9922,7 +9612,7 @@
         <v>411.8004330729737</v>
       </c>
       <c r="Z11" t="n">
-        <v>501.59</v>
+        <v>225184336.6018699</v>
       </c>
       <c r="AA11" t="n">
         <v>1.883334130830972e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-534.4880000000001</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-526.9590000000001</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-524.96</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-526.364</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-520.1990000000001</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-518.6220000000001</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-516.563</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-512.7569999999999</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-512.318</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-511.091</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1281.649</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-1014.249</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-871.2990000000001</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-788.005</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-727.855</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-693.7180000000001</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-662.2670000000001</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-648.511</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-627.042</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-616.804</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1440.061</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-1093.85</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-922.6510000000001</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-822.5970000000001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-759.525</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-719.095</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-686.039</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-662.4690000000001</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-644.6530000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-626.192</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1223.752</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-868.0219999999999</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-739.688</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-673.2910000000001</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-634.595</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-609.0949999999999</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-588.9970000000001</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-571.9150000000002</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-558.7170000000001</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-544.614</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1068.698</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-716.629</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-628.296</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-587.6859999999999</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-564.7939999999999</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-545.7549999999999</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-533.202</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-519.3290000000001</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-508.28</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-501.59</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-534.4880000000001</v>
+        <v>111.034</v>
       </c>
       <c r="D2" t="n">
         <v>1.21877e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-526.9590000000001</v>
+        <v>110.8</v>
       </c>
       <c r="D3" t="n">
         <v>1.21706e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-524.96</v>
+        <v>107.058</v>
       </c>
       <c r="D4" t="n">
         <v>1.21654e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-526.364</v>
+        <v>101.009</v>
       </c>
       <c r="D5" t="n">
         <v>1.21681e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-520.1990000000001</v>
+        <v>100.884</v>
       </c>
       <c r="D6" t="n">
         <v>1.21714e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-518.6220000000001</v>
+        <v>96.67000000000002</v>
       </c>
       <c r="D7" t="n">
         <v>1.21763e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-516.563</v>
+        <v>92.58099999999996</v>
       </c>
       <c r="D8" t="n">
         <v>1.21797e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-512.7569999999999</v>
+        <v>92.83600000000001</v>
       </c>
       <c r="D9" t="n">
         <v>1.21849e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-512.318</v>
+        <v>88.91300000000001</v>
       </c>
       <c r="D10" t="n">
         <v>1.2186e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-511.091</v>
+        <v>85.56799999999998</v>
       </c>
       <c r="D11" t="n">
         <v>1.21908e-07</v>
@@ -1042,7 +1042,7 @@
         <v>24.10322973688432</v>
       </c>
       <c r="X11" t="n">
-        <v>-10685.70562937584</v>
+        <v>-10685.70562937583</v>
       </c>
       <c r="Y11" t="n">
         <v>400.6059495363203</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-594.6099999999999</v>
+        <v>152.116</v>
       </c>
       <c r="D2" t="n">
         <v>1.3932e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-570.276</v>
+        <v>136.16</v>
       </c>
       <c r="D3" t="n">
         <v>1.38816e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-552.707</v>
+        <v>130.073</v>
       </c>
       <c r="D4" t="n">
         <v>1.3855e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-542.926</v>
+        <v>123.693</v>
       </c>
       <c r="D5" t="n">
         <v>1.38423e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-531.1940000000001</v>
+        <v>123.217</v>
       </c>
       <c r="D6" t="n">
         <v>1.38341e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-527.6370000000001</v>
+        <v>117.8629999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.3832e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-526.0029999999999</v>
+        <v>112.949</v>
       </c>
       <c r="D8" t="n">
         <v>1.38292e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-523.126</v>
+        <v>109.577</v>
       </c>
       <c r="D9" t="n">
         <v>1.38276e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-516.7430000000001</v>
+        <v>107.128</v>
       </c>
       <c r="D10" t="n">
         <v>1.38275e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-510.6849999999999</v>
+        <v>107.184</v>
       </c>
       <c r="D11" t="n">
         <v>1.38246e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-512.443</v>
+        <v>98.173</v>
       </c>
       <c r="D12" t="n">
         <v>1.38252e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-507.227</v>
+        <v>97.65899999999999</v>
       </c>
       <c r="D13" t="n">
         <v>1.38252e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-499.864</v>
+        <v>97.04899999999998</v>
       </c>
       <c r="D14" t="n">
         <v>1.38236e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-498.795</v>
+        <v>91.786</v>
       </c>
       <c r="D15" t="n">
         <v>1.38235e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-496.293</v>
+        <v>87.50200000000001</v>
       </c>
       <c r="D16" t="n">
         <v>1.38211e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-493.8939999999999</v>
+        <v>86.09699999999998</v>
       </c>
       <c r="D17" t="n">
         <v>1.38191e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-488.158</v>
+        <v>84.90300000000002</v>
       </c>
       <c r="D18" t="n">
         <v>1.38217e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-487.021</v>
+        <v>81.95100000000002</v>
       </c>
       <c r="D19" t="n">
         <v>1.38204e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-483.2900000000001</v>
+        <v>79.39999999999998</v>
       </c>
       <c r="D20" t="n">
         <v>1.38201e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-480.167</v>
+        <v>77.44400000000002</v>
       </c>
       <c r="D21" t="n">
         <v>1.38224e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-478.583</v>
+        <v>74.32099999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.38183e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-730.5890000000001</v>
+        <v>159.045</v>
       </c>
       <c r="D2" t="n">
         <v>1.26222e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-629.728</v>
+        <v>148.058</v>
       </c>
       <c r="D3" t="n">
         <v>1.24867e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-587.9839999999999</v>
+        <v>144.494</v>
       </c>
       <c r="D4" t="n">
         <v>1.24229e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-572.425</v>
+        <v>134.744</v>
       </c>
       <c r="D5" t="n">
         <v>1.23792e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-559.0870000000001</v>
+        <v>129.321</v>
       </c>
       <c r="D6" t="n">
         <v>1.23538e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-553.617</v>
+        <v>125.398</v>
       </c>
       <c r="D7" t="n">
         <v>1.2336e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-547.098</v>
+        <v>120.6</v>
       </c>
       <c r="D8" t="n">
         <v>1.23243e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-541.05</v>
+        <v>119.231</v>
       </c>
       <c r="D9" t="n">
         <v>1.23148e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-539.068</v>
+        <v>113.814</v>
       </c>
       <c r="D10" t="n">
         <v>1.23045e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-531.1100000000001</v>
+        <v>114.1</v>
       </c>
       <c r="D11" t="n">
         <v>1.23009e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-526.4350000000001</v>
+        <v>109.333</v>
       </c>
       <c r="D12" t="n">
         <v>1.22943e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-523.701</v>
+        <v>106.611</v>
       </c>
       <c r="D13" t="n">
         <v>1.22922e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-521.796</v>
+        <v>101.192</v>
       </c>
       <c r="D14" t="n">
         <v>1.22883e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-520.264</v>
+        <v>100.108</v>
       </c>
       <c r="D15" t="n">
         <v>1.22869e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-513.326</v>
+        <v>99.22000000000003</v>
       </c>
       <c r="D16" t="n">
         <v>1.22842e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-510.871</v>
+        <v>96.62399999999997</v>
       </c>
       <c r="D17" t="n">
         <v>1.22817e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-509.14</v>
+        <v>93.05500000000001</v>
       </c>
       <c r="D18" t="n">
         <v>1.22823e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-506.6079999999999</v>
+        <v>90.387</v>
       </c>
       <c r="D19" t="n">
         <v>1.22813e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-501.851</v>
+        <v>88.02199999999999</v>
       </c>
       <c r="D20" t="n">
         <v>1.22799e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-498.518</v>
+        <v>87.18299999999999</v>
       </c>
       <c r="D21" t="n">
         <v>1.22782e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-495.9690000000001</v>
+        <v>85.15499999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.22782e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1281.649</v>
+        <v>209.035</v>
       </c>
       <c r="D2" t="n">
         <v>1.33531e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-1014.249</v>
+        <v>154.019</v>
       </c>
       <c r="D3" t="n">
         <v>1.33344e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-871.2990000000001</v>
+        <v>144.379</v>
       </c>
       <c r="D4" t="n">
         <v>1.31803e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-788.005</v>
+        <v>133.923</v>
       </c>
       <c r="D5" t="n">
         <v>1.30535e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-727.855</v>
+        <v>135.055</v>
       </c>
       <c r="D6" t="n">
         <v>1.29573e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-693.7180000000001</v>
+        <v>126.454</v>
       </c>
       <c r="D7" t="n">
         <v>1.28854e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-662.2670000000001</v>
+        <v>126.4</v>
       </c>
       <c r="D8" t="n">
         <v>1.28259e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-648.511</v>
+        <v>115.272</v>
       </c>
       <c r="D9" t="n">
         <v>1.2785e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-627.042</v>
+        <v>116.248</v>
       </c>
       <c r="D10" t="n">
         <v>1.27535e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-616.804</v>
+        <v>108.895</v>
       </c>
       <c r="D11" t="n">
         <v>1.27265e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-851.3280000000001</v>
+        <v>155.151</v>
       </c>
       <c r="D2" t="n">
         <v>1.31674e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-730.226</v>
+        <v>147.662</v>
       </c>
       <c r="D3" t="n">
         <v>1.29589e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-674.1719999999999</v>
+        <v>136.335</v>
       </c>
       <c r="D4" t="n">
         <v>1.28507e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-640.63</v>
+        <v>134.586</v>
       </c>
       <c r="D5" t="n">
         <v>1.27906e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-622.0419999999999</v>
+        <v>132.3480000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.2756e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-609.261</v>
+        <v>126.07</v>
       </c>
       <c r="D7" t="n">
         <v>1.27313e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-600.997</v>
+        <v>120.049</v>
       </c>
       <c r="D8" t="n">
         <v>1.27132e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-593.579</v>
+        <v>117.192</v>
       </c>
       <c r="D9" t="n">
         <v>1.26985e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-584.5350000000001</v>
+        <v>112.386</v>
       </c>
       <c r="D10" t="n">
         <v>1.26859e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-574.345</v>
+        <v>112.249</v>
       </c>
       <c r="D11" t="n">
         <v>1.26796e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-571.0279999999999</v>
+        <v>106.749</v>
       </c>
       <c r="D12" t="n">
         <v>1.26736e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-563.518</v>
+        <v>104.573</v>
       </c>
       <c r="D13" t="n">
         <v>1.26678e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-556.8129999999999</v>
+        <v>101.169</v>
       </c>
       <c r="D14" t="n">
         <v>1.26634e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-552.0430000000001</v>
+        <v>98.55499999999995</v>
       </c>
       <c r="D15" t="n">
         <v>1.26593e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-548.376</v>
+        <v>95.04999999999995</v>
       </c>
       <c r="D16" t="n">
         <v>1.26532e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-545.372</v>
+        <v>91.50100000000003</v>
       </c>
       <c r="D17" t="n">
         <v>1.26501e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-540.278</v>
+        <v>89.58100000000002</v>
       </c>
       <c r="D18" t="n">
         <v>1.26465e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-535.605</v>
+        <v>88.363</v>
       </c>
       <c r="D19" t="n">
         <v>1.26436e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-527.046</v>
+        <v>86.37099999999998</v>
       </c>
       <c r="D20" t="n">
         <v>1.26448e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-528.6500000000001</v>
+        <v>83.75</v>
       </c>
       <c r="D21" t="n">
         <v>1.26408e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-520.4110000000001</v>
+        <v>82.41199999999998</v>
       </c>
       <c r="D22" t="n">
         <v>1.26399e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1440.061</v>
+        <v>210.2189999999999</v>
       </c>
       <c r="D2" t="n">
         <v>1.39652e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-1093.85</v>
+        <v>161.701</v>
       </c>
       <c r="D3" t="n">
         <v>1.38938e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-922.6510000000001</v>
+        <v>146.492</v>
       </c>
       <c r="D4" t="n">
         <v>1.36576e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-822.5970000000001</v>
+        <v>138.17</v>
       </c>
       <c r="D5" t="n">
         <v>1.34733e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-759.525</v>
+        <v>134.57</v>
       </c>
       <c r="D6" t="n">
         <v>1.33341e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-719.095</v>
+        <v>128.045</v>
       </c>
       <c r="D7" t="n">
         <v>1.32392e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-686.039</v>
+        <v>122.949</v>
       </c>
       <c r="D8" t="n">
         <v>1.31695e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-662.4690000000001</v>
+        <v>118.582</v>
       </c>
       <c r="D9" t="n">
         <v>1.31155e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-644.6530000000001</v>
+        <v>112.477</v>
       </c>
       <c r="D10" t="n">
         <v>1.30746e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-626.192</v>
+        <v>112.05</v>
       </c>
       <c r="D11" t="n">
         <v>1.30443e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-1157.117</v>
+        <v>156.597</v>
       </c>
       <c r="D2" t="n">
         <v>1.42306e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-810.874</v>
+        <v>144.466</v>
       </c>
       <c r="D3" t="n">
         <v>1.35224e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-710.1270000000001</v>
+        <v>140.4159999999999</v>
       </c>
       <c r="D4" t="n">
         <v>1.32918e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-672.891</v>
+        <v>131.302</v>
       </c>
       <c r="D5" t="n">
         <v>1.31922e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-647.3280000000001</v>
+        <v>129.833</v>
       </c>
       <c r="D6" t="n">
         <v>1.31428e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-630.348</v>
+        <v>123.119</v>
       </c>
       <c r="D7" t="n">
         <v>1.31122e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-617.6009999999999</v>
+        <v>121.6370000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.30908e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-604.943</v>
+        <v>117.744</v>
       </c>
       <c r="D9" t="n">
         <v>1.30734e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-599.747</v>
+        <v>111.126</v>
       </c>
       <c r="D10" t="n">
         <v>1.30613e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-590.6779999999999</v>
+        <v>109.556</v>
       </c>
       <c r="D11" t="n">
         <v>1.30519e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-579.7779999999999</v>
+        <v>107.623</v>
       </c>
       <c r="D12" t="n">
         <v>1.30417e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-577.5810000000001</v>
+        <v>102.094</v>
       </c>
       <c r="D13" t="n">
         <v>1.30343e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-568.876</v>
+        <v>103.254</v>
       </c>
       <c r="D14" t="n">
         <v>1.30268e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-565.7079999999999</v>
+        <v>98.05700000000002</v>
       </c>
       <c r="D15" t="n">
         <v>1.3021e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-557.674</v>
+        <v>97.98000000000002</v>
       </c>
       <c r="D16" t="n">
         <v>1.30167e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-553.2089999999999</v>
+        <v>97.19100000000003</v>
       </c>
       <c r="D17" t="n">
         <v>1.30108e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-548.5</v>
+        <v>93.07099999999997</v>
       </c>
       <c r="D18" t="n">
         <v>1.30087e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-546.596</v>
+        <v>89.29300000000001</v>
       </c>
       <c r="D19" t="n">
         <v>1.30049e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-542.307</v>
+        <v>87.60700000000003</v>
       </c>
       <c r="D20" t="n">
         <v>1.30006e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-536.362</v>
+        <v>85.87400000000002</v>
       </c>
       <c r="D21" t="n">
         <v>1.29972e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-531.24</v>
+        <v>83.32300000000004</v>
       </c>
       <c r="D22" t="n">
         <v>1.29958e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1223.752</v>
+        <v>164.145</v>
       </c>
       <c r="D2" t="n">
         <v>1.46536e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-868.0219999999999</v>
+        <v>150.611</v>
       </c>
       <c r="D3" t="n">
         <v>1.39868e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-739.688</v>
+        <v>141.379</v>
       </c>
       <c r="D4" t="n">
         <v>1.37166e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-673.2910000000001</v>
+        <v>134.634</v>
       </c>
       <c r="D5" t="n">
         <v>1.35893e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-634.595</v>
+        <v>127.058</v>
       </c>
       <c r="D6" t="n">
         <v>1.35239e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-609.0949999999999</v>
+        <v>120.492</v>
       </c>
       <c r="D7" t="n">
         <v>1.34888e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-588.9970000000001</v>
+        <v>113.827</v>
       </c>
       <c r="D8" t="n">
         <v>1.34727e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-571.9150000000002</v>
+        <v>111.611</v>
       </c>
       <c r="D9" t="n">
         <v>1.34625e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-558.7170000000001</v>
+        <v>107.979</v>
       </c>
       <c r="D10" t="n">
         <v>1.34624e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-544.614</v>
+        <v>103.611</v>
       </c>
       <c r="D11" t="n">
         <v>1.34624e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-665.9810000000001</v>
+        <v>137.29</v>
       </c>
       <c r="D2" t="n">
         <v>1.37658e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-629.7900000000001</v>
+        <v>132.749</v>
       </c>
       <c r="D3" t="n">
         <v>1.36808e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-609.718</v>
+        <v>130.929</v>
       </c>
       <c r="D4" t="n">
         <v>1.36447e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-597.199</v>
+        <v>126.822</v>
       </c>
       <c r="D5" t="n">
         <v>1.36289e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-591.9929999999999</v>
+        <v>120.126</v>
       </c>
       <c r="D6" t="n">
         <v>1.36206e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-583.7280000000001</v>
+        <v>116.328</v>
       </c>
       <c r="D7" t="n">
         <v>1.36181e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-578.8610000000001</v>
+        <v>111.123</v>
       </c>
       <c r="D8" t="n">
         <v>1.36158e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-575.672</v>
+        <v>106.431</v>
       </c>
       <c r="D9" t="n">
         <v>1.36135e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-571.588</v>
+        <v>104.567</v>
       </c>
       <c r="D10" t="n">
         <v>1.36074e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-565.301</v>
+        <v>102.786</v>
       </c>
       <c r="D11" t="n">
         <v>1.36079e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-562.8180000000001</v>
+        <v>98.75400000000002</v>
       </c>
       <c r="D12" t="n">
         <v>1.36102e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-559.712</v>
+        <v>94.11799999999999</v>
       </c>
       <c r="D13" t="n">
         <v>1.36091e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-557.832</v>
+        <v>93.03299999999996</v>
       </c>
       <c r="D14" t="n">
         <v>1.36096e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-551.114</v>
+        <v>91.27699999999999</v>
       </c>
       <c r="D15" t="n">
         <v>1.36134e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-551.1800000000001</v>
+        <v>87.447</v>
       </c>
       <c r="D16" t="n">
         <v>1.36277e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-546.625</v>
+        <v>86.803</v>
       </c>
       <c r="D17" t="n">
         <v>1.36349e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-543.67</v>
+        <v>82.68099999999998</v>
       </c>
       <c r="D18" t="n">
         <v>1.36447e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-539.5150000000001</v>
+        <v>82.83499999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.36478e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-537.1609999999999</v>
+        <v>81.00900000000001</v>
       </c>
       <c r="D20" t="n">
         <v>1.36544e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-534.6949999999999</v>
+        <v>79.14699999999999</v>
       </c>
       <c r="D21" t="n">
         <v>1.36603e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-532.751</v>
+        <v>78.04400000000004</v>
       </c>
       <c r="D22" t="n">
         <v>1.3662e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1068.698</v>
+        <v>132.198</v>
       </c>
       <c r="D2" t="n">
         <v>1.48587e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-716.629</v>
+        <v>121.381</v>
       </c>
       <c r="D3" t="n">
         <v>1.4166e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-628.296</v>
+        <v>117.897</v>
       </c>
       <c r="D4" t="n">
         <v>1.40262e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-587.6859999999999</v>
+        <v>112.633</v>
       </c>
       <c r="D5" t="n">
         <v>1.39783e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-564.7939999999999</v>
+        <v>107.253</v>
       </c>
       <c r="D6" t="n">
         <v>1.39562e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-545.7549999999999</v>
+        <v>102.761</v>
       </c>
       <c r="D7" t="n">
         <v>1.39515e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-533.202</v>
+        <v>96.03199999999998</v>
       </c>
       <c r="D8" t="n">
         <v>1.39503e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-519.3290000000001</v>
+        <v>94.892</v>
       </c>
       <c r="D9" t="n">
         <v>1.39566e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-508.28</v>
+        <v>90.32500000000005</v>
       </c>
       <c r="D10" t="n">
         <v>1.39635e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-501.59</v>
+        <v>87.31099999999998</v>
       </c>
       <c r="D11" t="n">
         <v>1.39687e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>111.034</v>
       </c>
+      <c r="C2" t="n">
+        <v>1122.741662274879</v>
+      </c>
       <c r="D2" t="n">
         <v>1.21877e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>110.8</v>
       </c>
+      <c r="C3" t="n">
+        <v>1279.874880047833</v>
+      </c>
       <c r="D3" t="n">
         <v>1.21706e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>107.058</v>
       </c>
+      <c r="C4" t="n">
+        <v>1280.486235558827</v>
+      </c>
       <c r="D4" t="n">
         <v>1.21654e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>101.009</v>
       </c>
+      <c r="C5" t="n">
+        <v>1049.966106713347</v>
+      </c>
       <c r="D5" t="n">
         <v>1.21681e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>100.884</v>
       </c>
+      <c r="C6" t="n">
+        <v>1265.180157607039</v>
+      </c>
       <c r="D6" t="n">
         <v>1.21714e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>96.67000000000002</v>
       </c>
+      <c r="C7" t="n">
+        <v>1229.198318517923</v>
+      </c>
       <c r="D7" t="n">
         <v>1.21763e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>92.58099999999996</v>
       </c>
+      <c r="C8" t="n">
+        <v>1275.96806466648</v>
+      </c>
       <c r="D8" t="n">
         <v>1.21797e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>92.83600000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1545.136573206637</v>
+      </c>
       <c r="D9" t="n">
         <v>1.21849e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>88.91300000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>1437.643633889568</v>
+      </c>
       <c r="D10" t="n">
         <v>1.2186e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>85.56799999999998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1440.962428784783</v>
       </c>
       <c r="D11" t="n">
         <v>1.21908e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>152.116</v>
       </c>
+      <c r="C2" t="n">
+        <v>1158.052584995958</v>
+      </c>
       <c r="D2" t="n">
         <v>1.3932e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>136.16</v>
       </c>
+      <c r="C3" t="n">
+        <v>970.4537743303221</v>
+      </c>
       <c r="D3" t="n">
         <v>1.38816e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>130.073</v>
       </c>
+      <c r="C4" t="n">
+        <v>973.3300432246264</v>
+      </c>
       <c r="D4" t="n">
         <v>1.3855e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>123.693</v>
       </c>
+      <c r="C5" t="n">
+        <v>960.6564782591602</v>
+      </c>
       <c r="D5" t="n">
         <v>1.38423e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>123.217</v>
       </c>
+      <c r="C6" t="n">
+        <v>1065.558087822046</v>
+      </c>
       <c r="D6" t="n">
         <v>1.38341e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>117.8629999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1016.132982432172</v>
+      </c>
       <c r="D7" t="n">
         <v>1.3832e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>112.949</v>
       </c>
+      <c r="C8" t="n">
+        <v>1011.338781701568</v>
+      </c>
       <c r="D8" t="n">
         <v>1.38292e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>109.577</v>
       </c>
+      <c r="C9" t="n">
+        <v>957.9365299796642</v>
+      </c>
       <c r="D9" t="n">
         <v>1.38276e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>107.128</v>
       </c>
+      <c r="C10" t="n">
+        <v>1031.018556650496</v>
+      </c>
       <c r="D10" t="n">
         <v>1.38275e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>107.184</v>
       </c>
+      <c r="C11" t="n">
+        <v>1289.084343123685</v>
+      </c>
       <c r="D11" t="n">
         <v>1.38246e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>98.173</v>
       </c>
+      <c r="C12" t="n">
+        <v>940.8527741993943</v>
+      </c>
       <c r="D12" t="n">
         <v>1.38252e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>97.65899999999999</v>
       </c>
+      <c r="C13" t="n">
+        <v>1055.114043491164</v>
+      </c>
       <c r="D13" t="n">
         <v>1.38252e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>97.04899999999998</v>
       </c>
+      <c r="C14" t="n">
+        <v>1195.902374718577</v>
+      </c>
       <c r="D14" t="n">
         <v>1.38236e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>91.786</v>
       </c>
+      <c r="C15" t="n">
+        <v>1092.227374981745</v>
+      </c>
       <c r="D15" t="n">
         <v>1.38235e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>87.50200000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>1058.999931553616</v>
+      </c>
       <c r="D16" t="n">
         <v>1.38211e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>86.09699999999998</v>
       </c>
+      <c r="C17" t="n">
+        <v>1066.91867473423</v>
+      </c>
       <c r="D17" t="n">
         <v>1.38191e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>84.90300000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>1226.026119207718</v>
+      </c>
       <c r="D18" t="n">
         <v>1.38217e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>81.95100000000002</v>
       </c>
+      <c r="C19" t="n">
+        <v>1173.816976959743</v>
+      </c>
       <c r="D19" t="n">
         <v>1.38204e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>79.39999999999998</v>
       </c>
+      <c r="C20" t="n">
+        <v>1189.142268512911</v>
+      </c>
       <c r="D20" t="n">
         <v>1.38201e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>77.44400000000002</v>
       </c>
+      <c r="C21" t="n">
+        <v>1296.820145462669</v>
+      </c>
       <c r="D21" t="n">
         <v>1.38224e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>74.32099999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1231.493400678894</v>
       </c>
       <c r="D22" t="n">
         <v>1.38183e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>159.045</v>
       </c>
+      <c r="C2" t="n">
+        <v>1158.02455300956</v>
+      </c>
       <c r="D2" t="n">
         <v>1.26222e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>148.058</v>
       </c>
+      <c r="C3" t="n">
+        <v>1047.47297542439</v>
+      </c>
       <c r="D3" t="n">
         <v>1.24867e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>144.494</v>
       </c>
+      <c r="C4" t="n">
+        <v>1177.757821910586</v>
+      </c>
       <c r="D4" t="n">
         <v>1.24229e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>134.744</v>
       </c>
+      <c r="C5" t="n">
+        <v>1033.162750477414</v>
+      </c>
       <c r="D5" t="n">
         <v>1.23792e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>129.321</v>
       </c>
+      <c r="C6" t="n">
+        <v>1008.32001038719</v>
+      </c>
       <c r="D6" t="n">
         <v>1.23538e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>125.398</v>
       </c>
+      <c r="C7" t="n">
+        <v>1028.603751201471</v>
+      </c>
       <c r="D7" t="n">
         <v>1.2336e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>120.6</v>
       </c>
+      <c r="C8" t="n">
+        <v>989.4925425537057</v>
+      </c>
       <c r="D8" t="n">
         <v>1.23243e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>119.231</v>
       </c>
+      <c r="C9" t="n">
+        <v>1055.90102231171</v>
+      </c>
       <c r="D9" t="n">
         <v>1.23148e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>113.814</v>
       </c>
+      <c r="C10" t="n">
+        <v>1041.67981592214</v>
+      </c>
       <c r="D10" t="n">
         <v>1.23045e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>114.1</v>
       </c>
+      <c r="C11" t="n">
+        <v>1156.338246051769</v>
+      </c>
       <c r="D11" t="n">
         <v>1.23009e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>109.333</v>
       </c>
+      <c r="C12" t="n">
+        <v>1109.152132895335</v>
+      </c>
       <c r="D12" t="n">
         <v>1.22943e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>106.611</v>
       </c>
+      <c r="C13" t="n">
+        <v>1163.109125483596</v>
+      </c>
       <c r="D13" t="n">
         <v>1.22922e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>101.192</v>
       </c>
+      <c r="C14" t="n">
+        <v>1057.358223791863</v>
+      </c>
       <c r="D14" t="n">
         <v>1.22883e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>100.108</v>
       </c>
+      <c r="C15" t="n">
+        <v>1096.239877428677</v>
+      </c>
       <c r="D15" t="n">
         <v>1.22869e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>99.22000000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>1273.300340756153</v>
+      </c>
       <c r="D16" t="n">
         <v>1.22842e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>96.62399999999997</v>
       </c>
+      <c r="C17" t="n">
+        <v>1381.224062462744</v>
+      </c>
       <c r="D17" t="n">
         <v>1.22817e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>93.05500000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>1199.488976808801</v>
+      </c>
       <c r="D18" t="n">
         <v>1.22823e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>90.387</v>
       </c>
+      <c r="C19" t="n">
+        <v>1230.78777967036</v>
+      </c>
       <c r="D19" t="n">
         <v>1.22813e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>88.02199999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>1300.720744304423</v>
+      </c>
       <c r="D20" t="n">
         <v>1.22799e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>87.18299999999999</v>
       </c>
+      <c r="C21" t="n">
+        <v>1388.888351323479</v>
+      </c>
       <c r="D21" t="n">
         <v>1.22782e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>85.15499999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1539.63457063241</v>
       </c>
       <c r="D22" t="n">
         <v>1.22782e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>209.035</v>
       </c>
+      <c r="C2" t="n">
+        <v>2643.789572726341</v>
+      </c>
       <c r="D2" t="n">
         <v>1.33531e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>154.019</v>
       </c>
+      <c r="C3" t="n">
+        <v>996.1845897541477</v>
+      </c>
       <c r="D3" t="n">
         <v>1.33344e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>144.379</v>
       </c>
+      <c r="C4" t="n">
+        <v>1021.949889376084</v>
+      </c>
       <c r="D4" t="n">
         <v>1.31803e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>133.923</v>
       </c>
+      <c r="C5" t="n">
+        <v>912.022027951748</v>
+      </c>
       <c r="D5" t="n">
         <v>1.30535e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>135.055</v>
       </c>
+      <c r="C6" t="n">
+        <v>1148.657876703629</v>
+      </c>
       <c r="D6" t="n">
         <v>1.29573e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>126.454</v>
       </c>
+      <c r="C7" t="n">
+        <v>1025.15621820514</v>
+      </c>
       <c r="D7" t="n">
         <v>1.28854e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>126.4</v>
       </c>
+      <c r="C8" t="n">
+        <v>1217.286065684708</v>
+      </c>
       <c r="D8" t="n">
         <v>1.28259e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>115.272</v>
       </c>
+      <c r="C9" t="n">
+        <v>983.719593997243</v>
+      </c>
       <c r="D9" t="n">
         <v>1.2785e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>116.248</v>
       </c>
+      <c r="C10" t="n">
+        <v>1184.20254081543</v>
+      </c>
       <c r="D10" t="n">
         <v>1.27535e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>108.895</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1042.691437737922</v>
       </c>
       <c r="D11" t="n">
         <v>1.27265e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>155.151</v>
       </c>
+      <c r="C2" t="n">
+        <v>1103.404530857678</v>
+      </c>
       <c r="D2" t="n">
         <v>1.31674e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>147.662</v>
       </c>
+      <c r="C3" t="n">
+        <v>1130.83455855947</v>
+      </c>
       <c r="D3" t="n">
         <v>1.29589e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>136.335</v>
       </c>
+      <c r="C4" t="n">
+        <v>1032.618790728345</v>
+      </c>
       <c r="D4" t="n">
         <v>1.28507e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>134.586</v>
       </c>
+      <c r="C5" t="n">
+        <v>1103.128901420841</v>
+      </c>
       <c r="D5" t="n">
         <v>1.27906e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>132.3480000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1182.085323827921</v>
+      </c>
       <c r="D6" t="n">
         <v>1.2756e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>126.07</v>
       </c>
+      <c r="C7" t="n">
+        <v>1109.752179695507</v>
+      </c>
       <c r="D7" t="n">
         <v>1.27313e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>120.049</v>
       </c>
+      <c r="C8" t="n">
+        <v>1039.063654003086</v>
+      </c>
       <c r="D8" t="n">
         <v>1.27132e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>117.192</v>
       </c>
+      <c r="C9" t="n">
+        <v>1073.658771559905</v>
+      </c>
       <c r="D9" t="n">
         <v>1.26985e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>112.386</v>
       </c>
+      <c r="C10" t="n">
+        <v>997.549922844421</v>
+      </c>
       <c r="D10" t="n">
         <v>1.26859e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>112.249</v>
       </c>
+      <c r="C11" t="n">
+        <v>1216.99695337526</v>
+      </c>
       <c r="D11" t="n">
         <v>1.26796e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>106.749</v>
       </c>
+      <c r="C12" t="n">
+        <v>1103.850852041727</v>
+      </c>
       <c r="D12" t="n">
         <v>1.26736e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>104.573</v>
       </c>
+      <c r="C13" t="n">
+        <v>1222.368995521193</v>
+      </c>
       <c r="D13" t="n">
         <v>1.26678e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>101.169</v>
       </c>
+      <c r="C14" t="n">
+        <v>1207.059766125852</v>
+      </c>
       <c r="D14" t="n">
         <v>1.26634e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>98.55499999999995</v>
       </c>
+      <c r="C15" t="n">
+        <v>1219.590923293906</v>
+      </c>
       <c r="D15" t="n">
         <v>1.26593e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>95.04999999999995</v>
       </c>
+      <c r="C16" t="n">
+        <v>1148.061002173263</v>
+      </c>
       <c r="D16" t="n">
         <v>1.26532e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>91.50100000000003</v>
       </c>
+      <c r="C17" t="n">
+        <v>1182.993583628027</v>
+      </c>
       <c r="D17" t="n">
         <v>1.26501e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>89.58100000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>1190.342001831529</v>
+      </c>
       <c r="D18" t="n">
         <v>1.26465e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>88.363</v>
       </c>
+      <c r="C19" t="n">
+        <v>1405.448328981055</v>
+      </c>
       <c r="D19" t="n">
         <v>1.26436e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>86.37099999999998</v>
       </c>
+      <c r="C20" t="n">
+        <v>1470.80188225358</v>
+      </c>
       <c r="D20" t="n">
         <v>1.26448e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>83.75</v>
       </c>
+      <c r="C21" t="n">
+        <v>1455.196093228655</v>
+      </c>
       <c r="D21" t="n">
         <v>1.26408e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>82.41199999999998</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1773.537207127594</v>
       </c>
       <c r="D22" t="n">
         <v>1.26399e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>210.2189999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>2359.939086937136</v>
+      </c>
       <c r="D2" t="n">
         <v>1.39652e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>161.701</v>
       </c>
+      <c r="C3" t="n">
+        <v>1213.229944636781</v>
+      </c>
       <c r="D3" t="n">
         <v>1.38938e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>146.492</v>
       </c>
+      <c r="C4" t="n">
+        <v>1080.630655736488</v>
+      </c>
       <c r="D4" t="n">
         <v>1.36576e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>138.17</v>
       </c>
+      <c r="C5" t="n">
+        <v>1012.296523676937</v>
+      </c>
       <c r="D5" t="n">
         <v>1.34733e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>134.57</v>
       </c>
+      <c r="C6" t="n">
+        <v>1061.092724218701</v>
+      </c>
       <c r="D6" t="n">
         <v>1.33341e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>128.045</v>
       </c>
+      <c r="C7" t="n">
+        <v>1051.848698773465</v>
+      </c>
       <c r="D7" t="n">
         <v>1.32392e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>122.949</v>
       </c>
+      <c r="C8" t="n">
+        <v>1023.582371831255</v>
+      </c>
       <c r="D8" t="n">
         <v>1.31695e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>118.582</v>
       </c>
+      <c r="C9" t="n">
+        <v>1072.44472888291</v>
+      </c>
       <c r="D9" t="n">
         <v>1.31155e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>112.477</v>
       </c>
+      <c r="C10" t="n">
+        <v>1025.661816279425</v>
+      </c>
       <c r="D10" t="n">
         <v>1.30746e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>112.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1283.878746732733</v>
       </c>
       <c r="D11" t="n">
         <v>1.30443e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>156.597</v>
       </c>
+      <c r="C2" t="n">
+        <v>1163.452015238964</v>
+      </c>
       <c r="D2" t="n">
         <v>1.42306e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>144.466</v>
       </c>
+      <c r="C3" t="n">
+        <v>1041.435274115405</v>
+      </c>
       <c r="D3" t="n">
         <v>1.35224e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>140.4159999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>1059.467741471273</v>
+      </c>
       <c r="D4" t="n">
         <v>1.32918e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>131.302</v>
       </c>
+      <c r="C5" t="n">
+        <v>947.4126166327284</v>
+      </c>
       <c r="D5" t="n">
         <v>1.31922e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>129.833</v>
       </c>
+      <c r="C6" t="n">
+        <v>1103.02785397401</v>
+      </c>
       <c r="D6" t="n">
         <v>1.31428e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>123.119</v>
       </c>
+      <c r="C7" t="n">
+        <v>1018.073763783344</v>
+      </c>
       <c r="D7" t="n">
         <v>1.31122e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>121.6370000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1135.459616912134</v>
+      </c>
       <c r="D8" t="n">
         <v>1.30908e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>117.744</v>
       </c>
+      <c r="C9" t="n">
+        <v>1091.44860630519</v>
+      </c>
       <c r="D9" t="n">
         <v>1.30734e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>111.126</v>
       </c>
+      <c r="C10" t="n">
+        <v>1033.710589136977</v>
+      </c>
       <c r="D10" t="n">
         <v>1.30613e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>109.556</v>
       </c>
+      <c r="C11" t="n">
+        <v>1111.14077669072</v>
+      </c>
       <c r="D11" t="n">
         <v>1.30519e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>107.623</v>
       </c>
+      <c r="C12" t="n">
+        <v>1154.038641858809</v>
+      </c>
       <c r="D12" t="n">
         <v>1.30417e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>102.094</v>
       </c>
+      <c r="C13" t="n">
+        <v>986.8981265301948</v>
+      </c>
       <c r="D13" t="n">
         <v>1.30343e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>103.254</v>
       </c>
+      <c r="C14" t="n">
+        <v>1193.764220349209</v>
+      </c>
       <c r="D14" t="n">
         <v>1.30268e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>98.05700000000002</v>
       </c>
+      <c r="C15" t="n">
+        <v>1019.748058931598</v>
+      </c>
       <c r="D15" t="n">
         <v>1.3021e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>97.98000000000002</v>
       </c>
+      <c r="C16" t="n">
+        <v>1189.948053595146</v>
+      </c>
       <c r="D16" t="n">
         <v>1.30167e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>97.19100000000003</v>
       </c>
+      <c r="C17" t="n">
+        <v>1311.887432640683</v>
+      </c>
       <c r="D17" t="n">
         <v>1.30108e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>93.07099999999997</v>
       </c>
+      <c r="C18" t="n">
+        <v>1212.699557708002</v>
+      </c>
       <c r="D18" t="n">
         <v>1.30087e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>89.29300000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>1070.583422218474</v>
+      </c>
       <c r="D19" t="n">
         <v>1.30049e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>87.60700000000003</v>
       </c>
+      <c r="C20" t="n">
+        <v>1160.722349859492</v>
+      </c>
       <c r="D20" t="n">
         <v>1.30006e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>85.87400000000002</v>
       </c>
+      <c r="C21" t="n">
+        <v>1304.559223552188</v>
+      </c>
       <c r="D21" t="n">
         <v>1.29972e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>83.32300000000004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1215.305039881726</v>
       </c>
       <c r="D22" t="n">
         <v>1.29958e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>164.145</v>
       </c>
+      <c r="C2" t="n">
+        <v>1255.80980786205</v>
+      </c>
       <c r="D2" t="n">
         <v>1.46536e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>150.611</v>
       </c>
+      <c r="C3" t="n">
+        <v>1107.115626127752</v>
+      </c>
       <c r="D3" t="n">
         <v>1.39868e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>141.379</v>
       </c>
+      <c r="C4" t="n">
+        <v>1000.206041668434</v>
+      </c>
       <c r="D4" t="n">
         <v>1.37166e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>134.634</v>
       </c>
+      <c r="C5" t="n">
+        <v>1000.157846104174</v>
+      </c>
       <c r="D5" t="n">
         <v>1.35893e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>127.058</v>
       </c>
+      <c r="C6" t="n">
+        <v>960.0230227551526</v>
+      </c>
       <c r="D6" t="n">
         <v>1.35239e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>120.492</v>
       </c>
+      <c r="C7" t="n">
+        <v>969.5653888213758</v>
+      </c>
       <c r="D7" t="n">
         <v>1.34888e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>113.827</v>
       </c>
+      <c r="C8" t="n">
+        <v>923.0865994699102</v>
+      </c>
       <c r="D8" t="n">
         <v>1.34727e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>111.611</v>
       </c>
+      <c r="C9" t="n">
+        <v>1006.304417225533</v>
+      </c>
       <c r="D9" t="n">
         <v>1.34625e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>107.979</v>
       </c>
+      <c r="C10" t="n">
+        <v>1111.378115128727</v>
+      </c>
       <c r="D10" t="n">
         <v>1.34624e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>103.611</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1143.57240934804</v>
       </c>
       <c r="D11" t="n">
         <v>1.34624e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>137.29</v>
       </c>
+      <c r="C2" t="n">
+        <v>979.8305464705882</v>
+      </c>
       <c r="D2" t="n">
         <v>1.37658e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>132.749</v>
       </c>
+      <c r="C3" t="n">
+        <v>964.5952938566454</v>
+      </c>
       <c r="D3" t="n">
         <v>1.36808e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>130.929</v>
       </c>
+      <c r="C4" t="n">
+        <v>1038.479552603714</v>
+      </c>
       <c r="D4" t="n">
         <v>1.36447e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>126.822</v>
       </c>
+      <c r="C5" t="n">
+        <v>1046.76818274176</v>
+      </c>
       <c r="D5" t="n">
         <v>1.36289e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>120.126</v>
       </c>
+      <c r="C6" t="n">
+        <v>990.5088401429487</v>
+      </c>
       <c r="D6" t="n">
         <v>1.36206e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>116.328</v>
       </c>
+      <c r="C7" t="n">
+        <v>1031.950715761211</v>
+      </c>
       <c r="D7" t="n">
         <v>1.36181e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>111.123</v>
       </c>
+      <c r="C8" t="n">
+        <v>1030.84451196451</v>
+      </c>
       <c r="D8" t="n">
         <v>1.36158e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>106.431</v>
       </c>
+      <c r="C9" t="n">
+        <v>971.7208900437239</v>
+      </c>
       <c r="D9" t="n">
         <v>1.36135e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>104.567</v>
       </c>
+      <c r="C10" t="n">
+        <v>1024.32566357718</v>
+      </c>
       <c r="D10" t="n">
         <v>1.36074e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>102.786</v>
       </c>
+      <c r="C11" t="n">
+        <v>1077.522493135924</v>
+      </c>
       <c r="D11" t="n">
         <v>1.36079e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>98.75400000000002</v>
       </c>
+      <c r="C12" t="n">
+        <v>994.5099983067635</v>
+      </c>
       <c r="D12" t="n">
         <v>1.36102e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>94.11799999999999</v>
       </c>
+      <c r="C13" t="n">
+        <v>992.1539921021799</v>
+      </c>
       <c r="D13" t="n">
         <v>1.36091e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>93.03299999999996</v>
       </c>
+      <c r="C14" t="n">
+        <v>991.1879716898829</v>
+      </c>
       <c r="D14" t="n">
         <v>1.36096e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>91.27699999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>1099.822213150909</v>
+      </c>
       <c r="D15" t="n">
         <v>1.36134e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>87.447</v>
       </c>
+      <c r="C16" t="n">
+        <v>990.0702302213865</v>
+      </c>
       <c r="D16" t="n">
         <v>1.36277e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>86.803</v>
       </c>
+      <c r="C17" t="n">
+        <v>1149.640203432681</v>
+      </c>
       <c r="D17" t="n">
         <v>1.36349e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>82.68099999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>1089.662904311614</v>
+      </c>
       <c r="D18" t="n">
         <v>1.36447e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>82.83499999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>1233.470705629034</v>
+      </c>
       <c r="D19" t="n">
         <v>1.36478e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>81.00900000000001</v>
       </c>
+      <c r="C20" t="n">
+        <v>1215.796057556671</v>
+      </c>
       <c r="D20" t="n">
         <v>1.36544e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>79.14699999999999</v>
       </c>
+      <c r="C21" t="n">
+        <v>1313.980347482655</v>
+      </c>
       <c r="D21" t="n">
         <v>1.36603e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>78.04400000000004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1258.178056584324</v>
       </c>
       <c r="D22" t="n">
         <v>1.3662e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>132.198</v>
       </c>
+      <c r="C2" t="n">
+        <v>1100.035775917173</v>
+      </c>
       <c r="D2" t="n">
         <v>1.48587e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>121.381</v>
       </c>
+      <c r="C3" t="n">
+        <v>932.229388860159</v>
+      </c>
       <c r="D3" t="n">
         <v>1.4166e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>117.897</v>
       </c>
+      <c r="C4" t="n">
+        <v>1018.304647277355</v>
+      </c>
       <c r="D4" t="n">
         <v>1.40262e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>112.633</v>
       </c>
+      <c r="C5" t="n">
+        <v>1028.210968145772</v>
+      </c>
       <c r="D5" t="n">
         <v>1.39783e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>107.253</v>
       </c>
+      <c r="C6" t="n">
+        <v>1043.828025669308</v>
+      </c>
       <c r="D6" t="n">
         <v>1.39562e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>102.761</v>
       </c>
+      <c r="C7" t="n">
+        <v>1100.801712569618</v>
+      </c>
       <c r="D7" t="n">
         <v>1.39515e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>96.03199999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>997.8732534491644</v>
+      </c>
       <c r="D8" t="n">
         <v>1.39503e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>94.892</v>
       </c>
+      <c r="C9" t="n">
+        <v>1227.852638126394</v>
+      </c>
       <c r="D9" t="n">
         <v>1.39566e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>90.32500000000005</v>
       </c>
+      <c r="C10" t="n">
+        <v>1259.548712205572</v>
+      </c>
       <c r="D10" t="n">
         <v>1.39635e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>87.31099999999998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1231.891983627613</v>
       </c>
       <c r="D11" t="n">
         <v>1.39687e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -565,7 +565,7 @@
         <v>111.034</v>
       </c>
       <c r="C2" t="n">
-        <v>1122.741662274879</v>
+        <v>393.1375121203559</v>
       </c>
       <c r="D2" t="n">
         <v>1.21877e-07</v>
@@ -598,16 +598,13 @@
         <v>-11487.07792864877</v>
       </c>
       <c r="Y2" t="n">
-        <v>449.7324770182993</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>25508394.88950895</v>
+        <v>115.5092190178254</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62768174120501e-07</v>
+        <v>1.413227815671875e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.955140847797822</v>
+        <v>0.9988396973911638</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>110.8</v>
       </c>
       <c r="C3" t="n">
-        <v>1279.874880047833</v>
+        <v>389.9470332465943</v>
       </c>
       <c r="D3" t="n">
         <v>1.21706e-07</v>
@@ -651,16 +648,13 @@
         <v>-11672.04758836881</v>
       </c>
       <c r="Y3" t="n">
-        <v>445.5630252428553</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1224831969.763895</v>
+        <v>115.0396688281925</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.620562417888693e-07</v>
+        <v>1.437609888003083e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9556096219366563</v>
+        <v>0.9988362067970054</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>107.058</v>
       </c>
       <c r="C4" t="n">
-        <v>1280.486235558827</v>
+        <v>369.0961940355513</v>
       </c>
       <c r="D4" t="n">
         <v>1.21654e-07</v>
@@ -704,16 +698,13 @@
         <v>-11511.17811510823</v>
       </c>
       <c r="Y4" t="n">
-        <v>440.57200342307</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>361524904.7141443</v>
+        <v>132.068863318476</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.613412393773471e-07</v>
+        <v>1.570583015879457e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9562246042062298</v>
+        <v>0.999500924167575</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>101.009</v>
       </c>
       <c r="C5" t="n">
-        <v>1049.966106713347</v>
+        <v>364.346271688827</v>
       </c>
       <c r="D5" t="n">
         <v>1.21681e-07</v>
@@ -757,16 +748,13 @@
         <v>-11131.44345889026</v>
       </c>
       <c r="Y5" t="n">
-        <v>434.918939654659</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>238070481.8131202</v>
+        <v>130.9867566470461</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.60843052491533e-07</v>
+        <v>1.612990674537793e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9567341285612617</v>
+        <v>0.9993955617918182</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>100.884</v>
       </c>
       <c r="C6" t="n">
-        <v>1265.180157607039</v>
+        <v>360.7839381604804</v>
       </c>
       <c r="D6" t="n">
         <v>1.21714e-07</v>
@@ -810,16 +798,13 @@
         <v>-11316.36532269195</v>
       </c>
       <c r="Y6" t="n">
-        <v>428.9805326930563</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>351951834.0520582</v>
+        <v>127.5376804222755</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.602996283743558e-07</v>
+        <v>1.593846945440637e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9572967929544706</v>
+        <v>0.9996314215325894</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>96.67000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>1229.198318517923</v>
+        <v>356.5982934557671</v>
       </c>
       <c r="D7" t="n">
         <v>1.21763e-07</v>
@@ -863,16 +848,13 @@
         <v>-11120.50638872414</v>
       </c>
       <c r="Y7" t="n">
-        <v>374.8204554599633</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14040.15174975307</v>
+        <v>125.4162914120047</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.785913493309581e-07</v>
+        <v>1.607748093762147e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9998481834460772</v>
+        <v>0.9997189049285887</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>92.58099999999996</v>
       </c>
       <c r="C8" t="n">
-        <v>1275.96806466648</v>
+        <v>352.3763342996183</v>
       </c>
       <c r="D8" t="n">
         <v>1.21797e-07</v>
@@ -916,16 +898,13 @@
         <v>-10928.84622222615</v>
       </c>
       <c r="Y8" t="n">
-        <v>365.6853465029369</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>13851.35162018206</v>
+        <v>122.8375684266353</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.838755169454749e-07</v>
+        <v>1.61324777700663e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9999420541558588</v>
+        <v>0.9998222867757806</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>92.83600000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1545.136573206637</v>
+        <v>363.5614150790643</v>
       </c>
       <c r="D9" t="n">
         <v>1.21849e-07</v>
@@ -969,16 +948,13 @@
         <v>-11028.15515365553</v>
       </c>
       <c r="Y9" t="n">
-        <v>411.4825982516712</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1122631804.411305</v>
+        <v>105.6634490798958</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.589030786070383e-07</v>
+        <v>1.557502360943997e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9588133068477264</v>
+        <v>0.9996830018059121</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>88.91300000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>1437.643633889568</v>
+        <v>358.5103441400158</v>
       </c>
       <c r="D10" t="n">
         <v>1.2186e-07</v>
@@ -1022,16 +998,13 @@
         <v>-10849.98111226879</v>
       </c>
       <c r="Y10" t="n">
-        <v>405.9777884499951</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>886428826.5764951</v>
+        <v>105.3298916078426</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.584028753299632e-07</v>
+        <v>1.589970239593471e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9593157670007468</v>
+        <v>0.9997109639480265</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>85.56799999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>1440.962428784783</v>
+        <v>200.0221333728622</v>
       </c>
       <c r="D11" t="n">
         <v>1.21908e-07</v>
@@ -1075,10 +1048,7 @@
         <v>-10685.70562937583</v>
       </c>
       <c r="Y11" t="n">
-        <v>400.6059495363203</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>874389240.8724992</v>
+        <v>688.1847661636911</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57980590450597e-07</v>
@@ -1241,7 +1211,7 @@
         <v>152.116</v>
       </c>
       <c r="C2" t="n">
-        <v>1158.052584995958</v>
+        <v>397.9971359368768</v>
       </c>
       <c r="D2" t="n">
         <v>1.3932e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-10237.77529729316</v>
       </c>
       <c r="Y2" t="n">
-        <v>407.7709143410224</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12545.18482610068</v>
+        <v>169.1221412056266</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.002963919265197e-07</v>
+        <v>1.70874929464842e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9998150281767894</v>
+        <v>0.9902306890580912</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>136.16</v>
       </c>
       <c r="C3" t="n">
-        <v>970.4537743303221</v>
+        <v>405.3060154318479</v>
       </c>
       <c r="D3" t="n">
         <v>1.38816e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-10225.80026693201</v>
       </c>
       <c r="Y3" t="n">
-        <v>410.8387029075576</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12284.97353287469</v>
+        <v>139.7627506829501</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.033548430802535e-07</v>
+        <v>1.311460490657483e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9994891820039503</v>
+        <v>0.9992986426930887</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>130.073</v>
       </c>
       <c r="C4" t="n">
-        <v>973.3300432246264</v>
+        <v>130.073</v>
       </c>
       <c r="D4" t="n">
         <v>1.3855e-07</v>
@@ -1379,11 +1343,10 @@
       <c r="X4" t="n">
         <v>-10455.1848436522</v>
       </c>
-      <c r="Y4" t="n">
-        <v>484.8266879074271</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>796366444.8808361</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.990652598113316e-07</v>
@@ -1400,7 +1363,7 @@
         <v>123.693</v>
       </c>
       <c r="C5" t="n">
-        <v>960.6564782591602</v>
+        <v>338.4030253664025</v>
       </c>
       <c r="D5" t="n">
         <v>1.38423e-07</v>
@@ -1433,16 +1396,13 @@
         <v>-10473.11808597432</v>
       </c>
       <c r="Y5" t="n">
-        <v>478.6725991689934</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>523856921.0771014</v>
+        <v>203.8611802395478</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.967874488134689e-07</v>
+        <v>1.897739720493704e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9456830340559175</v>
+        <v>0.999781192171183</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1413,7 @@
         <v>123.217</v>
       </c>
       <c r="C6" t="n">
-        <v>1065.558087822046</v>
+        <v>123.217</v>
       </c>
       <c r="D6" t="n">
         <v>1.38341e-07</v>
@@ -1485,11 +1445,10 @@
       <c r="X6" t="n">
         <v>-10723.71554120652</v>
       </c>
-      <c r="Y6" t="n">
-        <v>472.7228914409149</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>517460373.484095</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.951177372400178e-07</v>
@@ -1506,7 +1465,7 @@
         <v>117.8629999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1016.132982432172</v>
+        <v>366.7396458556032</v>
       </c>
       <c r="D7" t="n">
         <v>1.3832e-07</v>
@@ -1539,16 +1498,13 @@
         <v>-10561.92770538805</v>
       </c>
       <c r="Y7" t="n">
-        <v>466.789279425025</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1022527497.358744</v>
+        <v>155.0987466663495</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.939213991495241e-07</v>
+        <v>1.637765891326427e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9478156635032924</v>
+        <v>0.9959902103872866</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1515,7 @@
         <v>112.949</v>
       </c>
       <c r="C8" t="n">
-        <v>1011.338781701568</v>
+        <v>112.949</v>
       </c>
       <c r="D8" t="n">
         <v>1.38292e-07</v>
@@ -1591,11 +1547,10 @@
       <c r="X8" t="n">
         <v>-10382.57052443704</v>
       </c>
-      <c r="Y8" t="n">
-        <v>460.807216954542</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>32032887.50010811</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.926628158384923e-07</v>
@@ -1612,7 +1567,7 @@
         <v>109.577</v>
       </c>
       <c r="C9" t="n">
-        <v>957.9365299796642</v>
+        <v>361.6025114834835</v>
       </c>
       <c r="D9" t="n">
         <v>1.38276e-07</v>
@@ -1645,16 +1600,13 @@
         <v>-10284.4133261859</v>
       </c>
       <c r="Y9" t="n">
-        <v>454.8255420182748</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>373621188.1538545</v>
+        <v>145.1706909905666</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.918950822923622e-07</v>
+        <v>1.523318159334787e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9493776349719382</v>
+        <v>0.9996225804612201</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1617,7 @@
         <v>107.128</v>
       </c>
       <c r="C10" t="n">
-        <v>1031.018556650496</v>
+        <v>352.533515791932</v>
       </c>
       <c r="D10" t="n">
         <v>1.38275e-07</v>
@@ -1698,16 +1650,13 @@
         <v>-10323.95713170192</v>
       </c>
       <c r="Y10" t="n">
-        <v>448.7143466524704</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>122915166.3643759</v>
+        <v>149.2858415269355</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.908091545169312e-07</v>
+        <v>1.591696904709362e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9502431792854391</v>
+        <v>0.9997276167609468</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1667,7 @@
         <v>107.184</v>
       </c>
       <c r="C11" t="n">
-        <v>1289.084343123685</v>
+        <v>107.184</v>
       </c>
       <c r="D11" t="n">
         <v>1.38246e-07</v>
@@ -1750,11 +1699,10 @@
       <c r="X11" t="n">
         <v>-10463.5038952236</v>
       </c>
-      <c r="Y11" t="n">
-        <v>442.5118569111033</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>242129805.007102</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.898921551635108e-07</v>
@@ -1771,7 +1719,7 @@
         <v>98.173</v>
       </c>
       <c r="C12" t="n">
-        <v>940.8527741993943</v>
+        <v>341.6561894652119</v>
       </c>
       <c r="D12" t="n">
         <v>1.38252e-07</v>
@@ -1804,16 +1752,13 @@
         <v>-9974.061216264234</v>
       </c>
       <c r="Y12" t="n">
-        <v>385.3947832595061</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>14512.37229573186</v>
+        <v>147.5907502064775</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.837559702970311e-07</v>
+        <v>1.653210345354545e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9999959393445056</v>
+        <v>0.9996595590956611</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1769,7 @@
         <v>97.65899999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>1055.114043491164</v>
+        <v>97.65899999999999</v>
       </c>
       <c r="D13" t="n">
         <v>1.38252e-07</v>
@@ -1856,11 +1801,10 @@
       <c r="X13" t="n">
         <v>-10103.12217246724</v>
       </c>
-      <c r="Y13" t="n">
-        <v>430.6108211227326</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>32925772.60776133</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>1.879020514223816e-07</v>
@@ -1877,7 +1821,7 @@
         <v>97.04899999999998</v>
       </c>
       <c r="C14" t="n">
-        <v>1195.902374718577</v>
+        <v>339.5360307737552</v>
       </c>
       <c r="D14" t="n">
         <v>1.38236e-07</v>
@@ -1910,16 +1854,13 @@
         <v>-10203.67937700934</v>
       </c>
       <c r="Y14" t="n">
-        <v>424.82509227475</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>350350998.1575538</v>
+        <v>139.5237288643458</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87167093282658e-07</v>
+        <v>1.688635895224027e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9531575649746007</v>
+        <v>0.9996425068165601</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1871,7 @@
         <v>91.786</v>
       </c>
       <c r="C15" t="n">
-        <v>1092.227374981745</v>
+        <v>334.3011856538374</v>
       </c>
       <c r="D15" t="n">
         <v>1.38235e-07</v>
@@ -1963,16 +1904,13 @@
         <v>-9962.51997390038</v>
       </c>
       <c r="Y15" t="n">
-        <v>419.2251962838653</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>917008079.7492678</v>
+        <v>137.7795714403348</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.863720582175968e-07</v>
+        <v>1.718224863515911e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9538076613799175</v>
+        <v>0.9973546047890247</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1921,7 @@
         <v>87.50200000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>1058.999931553616</v>
+        <v>538.8682349253738</v>
       </c>
       <c r="D16" t="n">
         <v>1.38211e-07</v>
@@ -2016,16 +1954,13 @@
         <v>-9779.586126269876</v>
       </c>
       <c r="Y16" t="n">
-        <v>413.475995297416</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>169918089.9228762</v>
+        <v>0.543561878336522</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.854355722526172e-07</v>
+        <v>7.051248212194628e-08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9545528211312724</v>
+        <v>0.6929787462290383</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1971,7 @@
         <v>86.09699999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>1066.91867473423</v>
+        <v>86.09699999999998</v>
       </c>
       <c r="D17" t="n">
         <v>1.38191e-07</v>
@@ -2068,11 +2003,10 @@
       <c r="X17" t="n">
         <v>-9762.714503639863</v>
       </c>
-      <c r="Y17" t="n">
-        <v>407.8608773168519</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>334897920.0237986</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.847148475461929e-07</v>
@@ -2089,7 +2023,7 @@
         <v>84.90300000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>1226.026119207718</v>
+        <v>84.90300000000002</v>
       </c>
       <c r="D18" t="n">
         <v>1.38217e-07</v>
@@ -2121,11 +2055,10 @@
       <c r="X18" t="n">
         <v>-9791.801966194686</v>
       </c>
-      <c r="Y18" t="n">
-        <v>402.1940793513439</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>329347362.2599905</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.839783417340264e-07</v>
@@ -2142,7 +2075,7 @@
         <v>81.95100000000002</v>
       </c>
       <c r="C19" t="n">
-        <v>1173.816976959743</v>
+        <v>334.1439853309033</v>
       </c>
       <c r="D19" t="n">
         <v>1.38204e-07</v>
@@ -2175,16 +2108,13 @@
         <v>-9688.696603969463</v>
       </c>
       <c r="Y19" t="n">
-        <v>386.2119766468502</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3254.195744528191</v>
+        <v>112.589836360293</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.870003710897893e-07</v>
+        <v>1.616906008931532e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8676658522992389</v>
+        <v>0.9998345267388703</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2125,7 @@
         <v>79.39999999999998</v>
       </c>
       <c r="C20" t="n">
-        <v>1189.142268512911</v>
+        <v>447.4624531405108</v>
       </c>
       <c r="D20" t="n">
         <v>1.38201e-07</v>
@@ -2228,16 +2158,13 @@
         <v>-9628.025938073208</v>
       </c>
       <c r="Y20" t="n">
-        <v>390.8372265071988</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>854551446.8637075</v>
+        <v>0.08302146457254778</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.825029071544421e-07</v>
+        <v>1.336053464211262e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9569949429779769</v>
+        <v>0.9864732088691101</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2175,7 @@
         <v>77.44400000000002</v>
       </c>
       <c r="C21" t="n">
-        <v>1296.820145462669</v>
+        <v>144.9918342544219</v>
       </c>
       <c r="D21" t="n">
         <v>1.38224e-07</v>
@@ -2281,10 +2208,7 @@
         <v>-9567.236172464309</v>
       </c>
       <c r="Y21" t="n">
-        <v>383.9009836199369</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>9807.638003366283</v>
+        <v>681.4610814346922</v>
       </c>
       <c r="AA21" t="n">
         <v>2.695082237132001e-07</v>
@@ -2301,7 +2225,7 @@
         <v>74.32099999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>1231.493400678894</v>
+        <v>523.308969301479</v>
       </c>
       <c r="D22" t="n">
         <v>1.38183e-07</v>
@@ -2334,16 +2258,13 @@
         <v>-9408.347395802168</v>
       </c>
       <c r="Y22" t="n">
-        <v>379.7667170734993</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>414478115.7529508</v>
+        <v>0.860960094545797</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.810659795871835e-07</v>
+        <v>2.524918971067003e-07</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9581947374788823</v>
+        <v>0.6119413900505389</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2421,7 @@
         <v>159.045</v>
       </c>
       <c r="C2" t="n">
-        <v>1158.02455300956</v>
+        <v>436.5539872617217</v>
       </c>
       <c r="D2" t="n">
         <v>1.26222e-07</v>
@@ -2533,16 +2454,13 @@
         <v>-9422.928647581273</v>
       </c>
       <c r="Y2" t="n">
-        <v>404.7456383436996</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12663.70046711942</v>
+        <v>130.3137070631984</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.961351237379376e-07</v>
+        <v>1.213940282879496e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9989956283335211</v>
+        <v>0.9998264362169335</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2471,7 @@
         <v>148.058</v>
       </c>
       <c r="C3" t="n">
-        <v>1047.47297542439</v>
+        <v>405.6758324118443</v>
       </c>
       <c r="D3" t="n">
         <v>1.24867e-07</v>
@@ -2586,16 +2504,13 @@
         <v>-10697.82883941937</v>
       </c>
       <c r="Y3" t="n">
-        <v>497.361488090615</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>272500641.6775718</v>
+        <v>152.2884305317824</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.803074358482611e-07</v>
+        <v>1.395268982635405e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9431919351530109</v>
+        <v>0.9994620226380219</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2521,7 @@
         <v>144.494</v>
       </c>
       <c r="C4" t="n">
-        <v>1177.757821910586</v>
+        <v>410.2495606959276</v>
       </c>
       <c r="D4" t="n">
         <v>1.24229e-07</v>
@@ -2639,16 +2554,13 @@
         <v>-11461.02016369687</v>
       </c>
       <c r="Y4" t="n">
-        <v>490.9292903205533</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>538263103.0608996</v>
+        <v>142.0274708315704</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.755091809728803e-07</v>
+        <v>1.40337013857182e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9465185824057925</v>
+        <v>0.9985866367303811</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2571,7 @@
         <v>134.744</v>
       </c>
       <c r="C5" t="n">
-        <v>1033.162750477414</v>
+        <v>398.598247419095</v>
       </c>
       <c r="D5" t="n">
         <v>1.23792e-07</v>
@@ -2692,16 +2604,13 @@
         <v>-11453.90399392915</v>
       </c>
       <c r="Y5" t="n">
-        <v>485.1270312468699</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>531599230.7145907</v>
+        <v>145.4394444814085</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.724789585196178e-07</v>
+        <v>1.426564821919704e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9486443685463221</v>
+        <v>0.9988062624659183</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2621,7 @@
         <v>129.321</v>
       </c>
       <c r="C6" t="n">
-        <v>1008.32001038719</v>
+        <v>390.8358531527761</v>
       </c>
       <c r="D6" t="n">
         <v>1.23538e-07</v>
@@ -2745,16 +2654,13 @@
         <v>-11541.56319972459</v>
       </c>
       <c r="Y6" t="n">
-        <v>479.8626264619209</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>525484866.432004</v>
+        <v>148.9997723261673</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.704402094990969e-07</v>
+        <v>1.489571102754933e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.950147569215644</v>
+        <v>0.9986817179922552</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2671,7 @@
         <v>125.398</v>
       </c>
       <c r="C7" t="n">
-        <v>1028.603751201471</v>
+        <v>384.8870249584696</v>
       </c>
       <c r="D7" t="n">
         <v>1.2336e-07</v>
@@ -2798,16 +2704,13 @@
         <v>-11500.88834006986</v>
       </c>
       <c r="Y7" t="n">
-        <v>474.607936270931</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>268881413.8394894</v>
+        <v>152.6826722719882</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69132117389684e-07</v>
+        <v>1.547829271924819e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.951114823638282</v>
+        <v>0.9974737651501109</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2721,7 @@
         <v>120.6</v>
       </c>
       <c r="C8" t="n">
-        <v>989.4925425537057</v>
+        <v>398.9767792507864</v>
       </c>
       <c r="D8" t="n">
         <v>1.23243e-07</v>
@@ -2851,16 +2754,13 @@
         <v>-11462.61975899953</v>
       </c>
       <c r="Y8" t="n">
-        <v>469.2907598083517</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>390544936.1868502</v>
+        <v>128.9150739994734</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.679658385701025e-07</v>
+        <v>1.389129569933256e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9520256578241579</v>
+        <v>0.9989185599964979</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2771,7 @@
         <v>119.231</v>
       </c>
       <c r="C9" t="n">
-        <v>1055.90102231171</v>
+        <v>398.6331304161772</v>
       </c>
       <c r="D9" t="n">
         <v>1.23148e-07</v>
@@ -2904,16 +2804,13 @@
         <v>-11547.34065857199</v>
       </c>
       <c r="Y9" t="n">
-        <v>463.8590223891536</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>797670753.2086676</v>
+        <v>125.5064062515913</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.669914090478229e-07</v>
+        <v>1.471414431942009e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9528012917036756</v>
+        <v>0.9973721829641924</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2821,7 @@
         <v>113.814</v>
       </c>
       <c r="C10" t="n">
-        <v>1041.67981592214</v>
+        <v>113.814</v>
       </c>
       <c r="D10" t="n">
         <v>1.23045e-07</v>
@@ -2956,11 +2853,10 @@
       <c r="X10" t="n">
         <v>-11339.343005484</v>
       </c>
-      <c r="Y10" t="n">
-        <v>435.1470132697332</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19065.49048632301</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.616785888729669e-07</v>
@@ -2977,7 +2873,7 @@
         <v>114.1</v>
       </c>
       <c r="C11" t="n">
-        <v>1156.338246051769</v>
+        <v>393.4405744918123</v>
       </c>
       <c r="D11" t="n">
         <v>1.23009e-07</v>
@@ -3010,16 +2906,13 @@
         <v>-11575.92274465447</v>
       </c>
       <c r="Y11" t="n">
-        <v>452.3540705714025</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>494654973.0891057</v>
+        <v>121.253191639261</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.652048056888331e-07</v>
+        <v>1.54129348694883e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9542824025188228</v>
+        <v>0.9962077584895057</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2923,7 @@
         <v>109.333</v>
       </c>
       <c r="C12" t="n">
-        <v>1109.152132895335</v>
+        <v>389.2539329493716</v>
       </c>
       <c r="D12" t="n">
         <v>1.22943e-07</v>
@@ -3063,16 +2956,13 @@
         <v>-11402.43312596591</v>
       </c>
       <c r="Y12" t="n">
-        <v>446.739680857137</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>977203389.2654747</v>
+        <v>119.283369711728</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.642619133738038e-07</v>
+        <v>1.547162919267179e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9550794879471066</v>
+        <v>0.9967968622224848</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2973,7 @@
         <v>106.611</v>
       </c>
       <c r="C13" t="n">
-        <v>1163.109125483596</v>
+        <v>368.7464055584406</v>
       </c>
       <c r="D13" t="n">
         <v>1.22922e-07</v>
@@ -3116,16 +3006,13 @@
         <v>-11384.84990869904</v>
       </c>
       <c r="Y13" t="n">
-        <v>441.2043787231522</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>362173327.5330236</v>
+        <v>132.714998360169</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.636429486747324e-07</v>
+        <v>1.572835781433576e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9556287687657727</v>
+        <v>0.9994246125022498</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3023,7 @@
         <v>101.192</v>
       </c>
       <c r="C14" t="n">
-        <v>1057.358223791863</v>
+        <v>191.6845471898861</v>
       </c>
       <c r="D14" t="n">
         <v>1.22883e-07</v>
@@ -3169,10 +3056,7 @@
         <v>-11079.83760917102</v>
       </c>
       <c r="Y14" t="n">
-        <v>435.8325133960838</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>242216250.6369408</v>
+        <v>743.6161424607378</v>
       </c>
       <c r="AA14" t="n">
         <v>1.628753421057765e-07</v>
@@ -3189,7 +3073,7 @@
         <v>100.108</v>
       </c>
       <c r="C15" t="n">
-        <v>1096.239877428677</v>
+        <v>360.8545623267019</v>
       </c>
       <c r="D15" t="n">
         <v>1.22869e-07</v>
@@ -3222,16 +3106,13 @@
         <v>-11044.36899255705</v>
       </c>
       <c r="Y15" t="n">
-        <v>430.6467462647433</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>353121807.6940942</v>
+        <v>129.5410478852713</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.624473674092704e-07</v>
+        <v>1.62496291065582e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9566933676713527</v>
+        <v>0.9994428058207168</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3123,7 @@
         <v>99.22000000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>1273.300340756153</v>
+        <v>357.2333447185609</v>
       </c>
       <c r="D16" t="n">
         <v>1.22842e-07</v>
@@ -3275,16 +3156,13 @@
         <v>-11222.44230193034</v>
       </c>
       <c r="Y16" t="n">
-        <v>425.5678611514442</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>465815180.7540883</v>
+        <v>124.9933705547369</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.617788793708483e-07</v>
+        <v>1.545711416421309e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9572855097640788</v>
+        <v>0.9999175214297932</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3173,7 @@
         <v>96.62399999999997</v>
       </c>
       <c r="C17" t="n">
-        <v>1381.224062462744</v>
+        <v>142.1311421244711</v>
       </c>
       <c r="D17" t="n">
         <v>1.22817e-07</v>
@@ -3328,10 +3206,7 @@
         <v>-11128.24050024595</v>
       </c>
       <c r="Y17" t="n">
-        <v>365.2967479947008</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13962.29282862893</v>
+        <v>746.9899770238337</v>
       </c>
       <c r="AA17" t="n">
         <v>1.800072698738132e-07</v>
@@ -3348,7 +3223,7 @@
         <v>93.05500000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>1199.488976808801</v>
+        <v>151.5893214937331</v>
       </c>
       <c r="D18" t="n">
         <v>1.22823e-07</v>
@@ -3381,10 +3256,7 @@
         <v>-10991.06095853327</v>
       </c>
       <c r="Y18" t="n">
-        <v>365.7437024421812</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>13793.30733250387</v>
+        <v>733.4241795535743</v>
       </c>
       <c r="AA18" t="n">
         <v>1.873980059352311e-07</v>
@@ -3401,7 +3273,7 @@
         <v>90.387</v>
       </c>
       <c r="C19" t="n">
-        <v>1230.78777967036</v>
+        <v>347.402310853315</v>
       </c>
       <c r="D19" t="n">
         <v>1.22813e-07</v>
@@ -3434,16 +3306,13 @@
         <v>-10865.3657687703</v>
       </c>
       <c r="Y19" t="n">
-        <v>410.4845870465296</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>28480514.64362854</v>
+        <v>121.9129313179795</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.598592026793065e-07</v>
+        <v>1.651622435907756e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9590819315809704</v>
+        <v>0.9997515722643651</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3323,7 @@
         <v>88.02199999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>1300.720744304423</v>
+        <v>343.9342104663964</v>
       </c>
       <c r="D20" t="n">
         <v>1.22799e-07</v>
@@ -3487,16 +3356,13 @@
         <v>-10830.89718086393</v>
       </c>
       <c r="Y20" t="n">
-        <v>405.5357371961852</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>332667321.6845441</v>
+        <v>118.2136467457048</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.594754498883078e-07</v>
+        <v>1.626414114609732e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9594389673524796</v>
+        <v>0.9999526867950295</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3373,7 @@
         <v>87.18299999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>1388.888351323479</v>
+        <v>340.6238558259784</v>
       </c>
       <c r="D21" t="n">
         <v>1.22782e-07</v>
@@ -3540,16 +3406,13 @@
         <v>-10889.83940663235</v>
       </c>
       <c r="Y21" t="n">
-        <v>400.6292131971126</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>656494006.9787445</v>
+        <v>121.9141261439913</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.589969247623025e-07</v>
+        <v>1.803977710026419e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9598792407823505</v>
+        <v>0.9993830686025157</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3423,7 @@
         <v>85.15499999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>1539.63457063241</v>
+        <v>336.6331407235271</v>
       </c>
       <c r="D22" t="n">
         <v>1.22782e-07</v>
@@ -3593,16 +3456,13 @@
         <v>-10810.36290001218</v>
       </c>
       <c r="Y22" t="n">
-        <v>395.7406033550092</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>647991773.7160977</v>
+        <v>121.0914262434111</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.585264482049269e-07</v>
+        <v>1.784358586492543e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9603345422969221</v>
+        <v>0.999295154611737</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3619,7 @@
         <v>209.035</v>
       </c>
       <c r="C2" t="n">
-        <v>2643.789572726341</v>
+        <v>566.6576172027108</v>
       </c>
       <c r="D2" t="n">
         <v>1.33531e-07</v>
@@ -3792,10 +3652,7 @@
         <v>-5726.098901218926</v>
       </c>
       <c r="Y2" t="n">
-        <v>418.0204060570979</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13280.29912317816</v>
+        <v>1238.645023195556</v>
       </c>
       <c r="AA2" t="n">
         <v>1.782262012239833e-07</v>
@@ -3812,7 +3669,7 @@
         <v>154.019</v>
       </c>
       <c r="C3" t="n">
-        <v>996.1845897541477</v>
+        <v>387.7153959175112</v>
       </c>
       <c r="D3" t="n">
         <v>1.33344e-07</v>
@@ -3845,16 +3702,13 @@
         <v>-6518.575708509353</v>
       </c>
       <c r="Y3" t="n">
-        <v>406.9356579485685</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12685.62596056101</v>
+        <v>183.2428164817985</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.840975831861445e-07</v>
+        <v>1.654592813396711e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9998888089043908</v>
+        <v>0.9925466300275718</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3719,7 @@
         <v>144.379</v>
       </c>
       <c r="C4" t="n">
-        <v>1021.949889376084</v>
+        <v>256.0188443967652</v>
       </c>
       <c r="D4" t="n">
         <v>1.31803e-07</v>
@@ -3898,10 +3752,7 @@
         <v>-7485.110977076128</v>
       </c>
       <c r="Y4" t="n">
-        <v>402.9730350635263</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12462.25431193797</v>
+        <v>1046.484081386222</v>
       </c>
       <c r="AA4" t="n">
         <v>1.890058265048753e-07</v>
@@ -3918,7 +3769,7 @@
         <v>133.923</v>
       </c>
       <c r="C5" t="n">
-        <v>912.022027951748</v>
+        <v>346.2564702440825</v>
       </c>
       <c r="D5" t="n">
         <v>1.30535e-07</v>
@@ -3951,16 +3802,13 @@
         <v>-8087.332519489385</v>
       </c>
       <c r="Y5" t="n">
-        <v>491.6636738253705</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>269674749.3423757</v>
+        <v>215.9580490473573</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.015777721681117e-07</v>
+        <v>1.880435855069965e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9331563818601806</v>
+        <v>0.9999301367272067</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3819,7 @@
         <v>135.055</v>
       </c>
       <c r="C6" t="n">
-        <v>1148.657876703629</v>
+        <v>336.5952105738144</v>
       </c>
       <c r="D6" t="n">
         <v>1.29573e-07</v>
@@ -4004,16 +3852,13 @@
         <v>-8860.775408076453</v>
       </c>
       <c r="Y6" t="n">
-        <v>485.9214518122515</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>399597565.6290065</v>
+        <v>223.7314362568284</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.944049037367472e-07</v>
+        <v>2.635527950740507e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9375121193153352</v>
+        <v>0.9795386118336112</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3869,7 @@
         <v>126.454</v>
       </c>
       <c r="C7" t="n">
-        <v>1025.15621820514</v>
+        <v>333.7933963890671</v>
       </c>
       <c r="D7" t="n">
         <v>1.28854e-07</v>
@@ -4057,16 +3902,13 @@
         <v>-9077.780506269131</v>
       </c>
       <c r="Y7" t="n">
-        <v>479.976610980483</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>197206831.3016371</v>
+        <v>213.6570190854971</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.892266163094472e-07</v>
+        <v>1.975354033535818e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9407542024929905</v>
+        <v>0.9980209592788023</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3919,7 @@
         <v>126.4</v>
       </c>
       <c r="C8" t="n">
-        <v>1217.286065684708</v>
+        <v>326.9602367999551</v>
       </c>
       <c r="D8" t="n">
         <v>1.28259e-07</v>
@@ -4110,16 +3952,13 @@
         <v>-9520.059202138427</v>
       </c>
       <c r="Y8" t="n">
-        <v>473.6629101608175</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>130250474.9436368</v>
+        <v>211.4863988086538</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.852393989027738e-07</v>
+        <v>1.993688238503378e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9432845055454072</v>
+        <v>0.9994120103540315</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3969,7 @@
         <v>115.272</v>
       </c>
       <c r="C9" t="n">
-        <v>983.719593997243</v>
+        <v>321.5036555112013</v>
       </c>
       <c r="D9" t="n">
         <v>1.2785e-07</v>
@@ -4163,16 +4002,13 @@
         <v>-9359.790435706926</v>
       </c>
       <c r="Y9" t="n">
-        <v>467.1998543859579</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>384480061.2012399</v>
+        <v>218.1641865148651</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.823038878499942e-07</v>
+        <v>2.559572321769129e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9452261901838206</v>
+        <v>0.9863800638747779</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4019,7 @@
         <v>116.248</v>
       </c>
       <c r="C10" t="n">
-        <v>1184.20254081543</v>
+        <v>401.598684828852</v>
       </c>
       <c r="D10" t="n">
         <v>1.27535e-07</v>
@@ -4216,16 +4052,13 @@
         <v>-9755.057238820251</v>
       </c>
       <c r="Y10" t="n">
-        <v>441.4782816300599</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19176.86040800497</v>
+        <v>115.9813165871188</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.619796231614761e-07</v>
+        <v>1.338572462234393e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9998890413369721</v>
+        <v>0.9992824994891025</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4069,7 @@
         <v>108.895</v>
       </c>
       <c r="C11" t="n">
-        <v>1042.691437737922</v>
+        <v>397.1261616386629</v>
       </c>
       <c r="D11" t="n">
         <v>1.27265e-07</v>
@@ -4269,16 +4102,13 @@
         <v>-9649.279662247052</v>
       </c>
       <c r="Y11" t="n">
-        <v>454.1850923297379</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>255881195.3342048</v>
+        <v>119.852627393032</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.777501202237959e-07</v>
+        <v>1.429831427006072e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9483804323038032</v>
+        <v>0.999990353663238</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4265,7 @@
         <v>155.151</v>
       </c>
       <c r="C2" t="n">
-        <v>1103.404530857678</v>
+        <v>360.1994574328643</v>
       </c>
       <c r="D2" t="n">
         <v>1.31674e-07</v>
@@ -4468,16 +4298,13 @@
         <v>-7844.41869113777</v>
       </c>
       <c r="Y2" t="n">
-        <v>406.6757508190286</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12642.56926853817</v>
+        <v>207.0408511741169</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.924358387235392e-07</v>
+        <v>1.647900276962217e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9997028775464016</v>
+        <v>0.9996778644362969</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4315,7 @@
         <v>147.662</v>
       </c>
       <c r="C3" t="n">
-        <v>1130.83455855947</v>
+        <v>147.662</v>
       </c>
       <c r="D3" t="n">
         <v>1.29589e-07</v>
@@ -4520,11 +4347,10 @@
       <c r="X3" t="n">
         <v>-9073.047758489638</v>
       </c>
-      <c r="Y3" t="n">
-        <v>403.7519722451961</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12432.76348186441</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>2.149230094569739e-07</v>
@@ -4541,7 +4367,7 @@
         <v>136.335</v>
       </c>
       <c r="C4" t="n">
-        <v>1032.618790728345</v>
+        <v>570.0430832935148</v>
       </c>
       <c r="D4" t="n">
         <v>1.28507e-07</v>
@@ -4574,16 +4400,13 @@
         <v>-9633.593617101664</v>
       </c>
       <c r="Y4" t="n">
-        <v>491.0772645139172</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>135072206.8318982</v>
+        <v>0.04259180586369507</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.890940657958642e-07</v>
+        <v>1.767076899894438e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9403958798607552</v>
+        <v>0.9478938382433714</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4417,7 @@
         <v>134.586</v>
       </c>
       <c r="C5" t="n">
-        <v>1103.128901420841</v>
+        <v>476.3186741708611</v>
       </c>
       <c r="D5" t="n">
         <v>1.27906e-07</v>
@@ -4627,16 +4450,13 @@
         <v>-10133.09697532537</v>
       </c>
       <c r="Y5" t="n">
-        <v>486.5792081841189</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1066030428.940031</v>
+        <v>65.43099374871019</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.848622104889686e-07</v>
+        <v>1.047707640880917e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9431254484829242</v>
+        <v>0.9998611504099959</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4467,7 @@
         <v>132.3480000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1182.085323827921</v>
+        <v>443.3127677829556</v>
       </c>
       <c r="D6" t="n">
         <v>1.2756e-07</v>
@@ -4680,16 +4500,13 @@
         <v>-10350.66085402469</v>
       </c>
       <c r="Y6" t="n">
-        <v>481.3002605669151</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>131931694.6908549</v>
+        <v>95.88724846941393</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.822322986399571e-07</v>
+        <v>1.180767518337226e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9448907885277107</v>
+        <v>0.9995845527518615</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4517,7 @@
         <v>126.07</v>
       </c>
       <c r="C7" t="n">
-        <v>1109.752179695507</v>
+        <v>387.6560337491177</v>
       </c>
       <c r="D7" t="n">
         <v>1.27313e-07</v>
@@ -4733,16 +4550,13 @@
         <v>-10352.62168042783</v>
       </c>
       <c r="Y7" t="n">
-        <v>475.5761945644315</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>390898171.2236999</v>
+        <v>148.4575589142123</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.800972400513979e-07</v>
+        <v>1.471980234554052e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9463967156440627</v>
+        <v>0.9997239526423916</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4567,7 @@
         <v>120.049</v>
       </c>
       <c r="C8" t="n">
-        <v>1039.063654003086</v>
+        <v>381.3776824062912</v>
       </c>
       <c r="D8" t="n">
         <v>1.27132e-07</v>
@@ -4786,16 +4600,13 @@
         <v>-10236.73152171815</v>
       </c>
       <c r="Y8" t="n">
-        <v>469.4991716414882</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>128941831.0295638</v>
+        <v>148.8976512455532</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.783459648837793e-07</v>
+        <v>1.514950650601717e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9476695140069712</v>
+        <v>0.9996615512473418</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4617,7 @@
         <v>117.192</v>
       </c>
       <c r="C9" t="n">
-        <v>1073.658771559905</v>
+        <v>376.8539013588187</v>
       </c>
       <c r="D9" t="n">
         <v>1.26985e-07</v>
@@ -4839,16 +4650,13 @@
         <v>-10235.41958354107</v>
       </c>
       <c r="Y9" t="n">
-        <v>463.4254608838797</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>380876671.3098059</v>
+        <v>148.0907880000422</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.769803435356875e-07</v>
+        <v>1.525410955602472e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9486745646100498</v>
+        <v>0.9998862917167373</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4667,7 @@
         <v>112.386</v>
       </c>
       <c r="C10" t="n">
-        <v>997.549922844421</v>
+        <v>371.868247527083</v>
       </c>
       <c r="D10" t="n">
         <v>1.26859e-07</v>
@@ -4892,16 +4700,13 @@
         <v>-10204.35551686627</v>
       </c>
       <c r="Y10" t="n">
-        <v>452.3551432983907</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19033.55547754413</v>
+        <v>146.1939323116107</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57660098914171e-07</v>
+        <v>1.542492053474473e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9999173347112819</v>
+        <v>0.999968654729969</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4717,7 @@
         <v>112.249</v>
       </c>
       <c r="C11" t="n">
-        <v>1216.99695337526</v>
+        <v>84.17393390083748</v>
       </c>
       <c r="D11" t="n">
         <v>1.26796e-07</v>
@@ -4945,10 +4750,7 @@
         <v>-10422.60324982645</v>
       </c>
       <c r="Y11" t="n">
-        <v>451.4474092345619</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>247499140.3841373</v>
+        <v>864.0499853922237</v>
       </c>
       <c r="AA11" t="n">
         <v>1.743270847449702e-07</v>
@@ -4965,7 +4767,7 @@
         <v>106.749</v>
       </c>
       <c r="C12" t="n">
-        <v>1103.850852041727</v>
+        <v>363.3912833618828</v>
       </c>
       <c r="D12" t="n">
         <v>1.26736e-07</v>
@@ -4998,16 +4800,13 @@
         <v>-10263.56464186314</v>
       </c>
       <c r="Y12" t="n">
-        <v>445.7804411165236</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1218887979.656995</v>
+        <v>145.8300097186927</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.733676593565875e-07</v>
+        <v>1.722747884851695e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9515292137810646</v>
+        <v>0.9954802531878971</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4817,7 @@
         <v>104.573</v>
       </c>
       <c r="C13" t="n">
-        <v>1222.368995521193</v>
+        <v>360.5937415329954</v>
       </c>
       <c r="D13" t="n">
         <v>1.26678e-07</v>
@@ -5051,16 +4850,13 @@
         <v>-10325.78309714612</v>
       </c>
       <c r="Y13" t="n">
-        <v>440.2005039536013</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>481573007.1813665</v>
+        <v>136.6665846488773</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.723032509058292e-07</v>
+        <v>1.634214463287535e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9524001624491674</v>
+        <v>0.9978051496000589</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4867,7 @@
         <v>101.169</v>
       </c>
       <c r="C14" t="n">
-        <v>1207.059766125852</v>
+        <v>356.4839194605513</v>
       </c>
       <c r="D14" t="n">
         <v>1.26634e-07</v>
@@ -5104,16 +4900,13 @@
         <v>-10263.64102231978</v>
       </c>
       <c r="Y14" t="n">
-        <v>434.723897092129</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>237769632.4421493</v>
+        <v>132.2715465214674</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.712948978600426e-07</v>
+        <v>1.574148140764438e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9532413970005716</v>
+        <v>0.9989873859510656</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4917,7 @@
         <v>98.55499999999995</v>
       </c>
       <c r="C15" t="n">
-        <v>1219.590923293906</v>
+        <v>351.6080538580483</v>
       </c>
       <c r="D15" t="n">
         <v>1.26593e-07</v>
@@ -5157,16 +4950,13 @@
         <v>-10241.78598667324</v>
       </c>
       <c r="Y15" t="n">
-        <v>371.2507098873601</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>14271.00293336709</v>
+        <v>139.7247322083331</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.830378588769889e-07</v>
+        <v>1.715933374726662e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9999349518940444</v>
+        <v>0.997856034309522</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4967,7 @@
         <v>95.04999999999995</v>
       </c>
       <c r="C16" t="n">
-        <v>1148.061002173263</v>
+        <v>347.2832470784322</v>
       </c>
       <c r="D16" t="n">
         <v>1.26532e-07</v>
@@ -5210,16 +5000,13 @@
         <v>-10115.92548771846</v>
       </c>
       <c r="Y16" t="n">
-        <v>370.5408170808202</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14088.60709471307</v>
+        <v>137.4212482753082</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.866074475234489e-07</v>
+        <v>1.720494803012082e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9999189357108623</v>
+        <v>0.997759686726807</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5017,7 @@
         <v>91.50100000000003</v>
       </c>
       <c r="C17" t="n">
-        <v>1182.993583628027</v>
+        <v>483.8708606305227</v>
       </c>
       <c r="D17" t="n">
         <v>1.26501e-07</v>
@@ -5263,16 +5050,13 @@
         <v>-10017.24339804782</v>
       </c>
       <c r="Y17" t="n">
-        <v>418.7338970947847</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>228612614.3248598</v>
+        <v>0.08066719005441447</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.688584923609476e-07</v>
+        <v>1.400404728881619e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9552802430315779</v>
+        <v>0.977087857298037</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5067,7 @@
         <v>89.58100000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>1190.342001831529</v>
+        <v>477.1396283983201</v>
       </c>
       <c r="D18" t="n">
         <v>1.26465e-07</v>
@@ -5316,16 +5100,13 @@
         <v>-10020.23849438376</v>
       </c>
       <c r="Y18" t="n">
-        <v>413.399184936012</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>225758056.4968992</v>
+        <v>0.002548030666965827</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68121973185646e-07</v>
+        <v>1.361072848055471e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9559048362101588</v>
+        <v>0.9815430238892092</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5117,7 @@
         <v>88.363</v>
       </c>
       <c r="C19" t="n">
-        <v>1405.448328981055</v>
+        <v>209.4129670760968</v>
       </c>
       <c r="D19" t="n">
         <v>1.26436e-07</v>
@@ -5369,10 +5150,7 @@
         <v>-10042.57369212209</v>
       </c>
       <c r="Y19" t="n">
-        <v>408.0633665346227</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>122370120.8085435</v>
+        <v>709.8147147650506</v>
       </c>
       <c r="AA19" t="n">
         <v>1.673873645501824e-07</v>
@@ -5389,7 +5167,7 @@
         <v>86.37099999999998</v>
       </c>
       <c r="C20" t="n">
-        <v>1470.80188225358</v>
+        <v>332.8665247858694</v>
       </c>
       <c r="D20" t="n">
         <v>1.26448e-07</v>
@@ -5422,16 +5200,13 @@
         <v>-10071.80720284362</v>
       </c>
       <c r="Y20" t="n">
-        <v>396.6682220815492</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>15040.31542558245</v>
+        <v>125.666420981305</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.716931347568358e-07</v>
+        <v>1.691126831237372e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9999999763913315</v>
+        <v>0.9995980062282763</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5217,7 @@
         <v>83.75</v>
       </c>
       <c r="C21" t="n">
-        <v>1455.196093228655</v>
+        <v>350.1099792667131</v>
       </c>
       <c r="D21" t="n">
         <v>1.26408e-07</v>
@@ -5475,16 +5250,13 @@
         <v>-9901.44086903851</v>
       </c>
       <c r="Y21" t="n">
-        <v>397.5219674641309</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>542188241.5899316</v>
+        <v>111.463685743762</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.661870710057581e-07</v>
+        <v>1.9933159117251e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9576145308456261</v>
+        <v>0.9893811427957924</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5267,7 @@
         <v>82.41199999999998</v>
       </c>
       <c r="C22" t="n">
-        <v>1773.537207127594</v>
+        <v>377.1000800203544</v>
       </c>
       <c r="D22" t="n">
         <v>1.26399e-07</v>
@@ -5528,16 +5300,13 @@
         <v>-9956.995427501939</v>
       </c>
       <c r="Y22" t="n">
-        <v>375.5911874316374</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3216.194448504606</v>
+        <v>69.41337139568014</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.15235095117835e-06</v>
+        <v>1.376995180561874e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.7292236451365459</v>
+        <v>0.9999133607220535</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5463,7 @@
         <v>210.2189999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2359.939086937136</v>
+        <v>380.8526935726225</v>
       </c>
       <c r="D2" t="n">
         <v>1.39652e-07</v>
@@ -5727,16 +5496,13 @@
         <v>-4906.653469620401</v>
       </c>
       <c r="Y2" t="n">
-        <v>429.6230202017823</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13632.91162896371</v>
+        <v>239.1191903432328</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76095697154734e-07</v>
+        <v>1.896106474643178e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9997723017464323</v>
+        <v>0.9865147514512298</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5513,7 @@
         <v>161.701</v>
       </c>
       <c r="C3" t="n">
-        <v>1213.229944636781</v>
+        <v>491.0604641926202</v>
       </c>
       <c r="D3" t="n">
         <v>1.38938e-07</v>
@@ -5780,16 +5546,13 @@
         <v>-5956.536332184563</v>
       </c>
       <c r="Y3" t="n">
-        <v>418.3909006030254</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>13015.70243212981</v>
+        <v>87.41029580984089</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.858001589130673e-07</v>
+        <v>9.982129187510363e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9999042869934802</v>
+        <v>0.9998957322753346</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5563,7 @@
         <v>146.492</v>
       </c>
       <c r="C4" t="n">
-        <v>1080.630655736488</v>
+        <v>353.4011417969356</v>
       </c>
       <c r="D4" t="n">
         <v>1.36576e-07</v>
@@ -5833,16 +5596,13 @@
         <v>-6971.035278165876</v>
       </c>
       <c r="Y4" t="n">
-        <v>415.9180064078726</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12778.77446574732</v>
+        <v>219.2130848488418</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.859463378083317e-07</v>
+        <v>1.724337524533802e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9999991021158158</v>
+        <v>0.9992604822166351</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5613,7 @@
         <v>138.17</v>
       </c>
       <c r="C5" t="n">
-        <v>1012.296523676937</v>
+        <v>347.4742433903804</v>
       </c>
       <c r="D5" t="n">
         <v>1.34733e-07</v>
@@ -5886,16 +5646,13 @@
         <v>-7715.468949892682</v>
       </c>
       <c r="Y5" t="n">
-        <v>411.2921404591351</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>12610.20393195065</v>
+        <v>220.0235360128802</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.978829766619678e-07</v>
+        <v>1.808051120979774e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9996175485744294</v>
+        <v>0.9987102416994608</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5663,7 @@
         <v>134.57</v>
       </c>
       <c r="C6" t="n">
-        <v>1061.092724218701</v>
+        <v>134.57</v>
       </c>
       <c r="D6" t="n">
         <v>1.33341e-07</v>
@@ -5938,11 +5695,10 @@
       <c r="X6" t="n">
         <v>-8355.624879283245</v>
       </c>
-      <c r="Y6" t="n">
-        <v>497.9991348708024</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>275902571.6437891</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>2.060720263312138e-07</v>
@@ -5959,7 +5715,7 @@
         <v>128.045</v>
       </c>
       <c r="C7" t="n">
-        <v>1051.848698773465</v>
+        <v>128.045</v>
       </c>
       <c r="D7" t="n">
         <v>1.32392e-07</v>
@@ -5991,11 +5747,10 @@
       <c r="X7" t="n">
         <v>-8663.688710141796</v>
       </c>
-      <c r="Y7" t="n">
-        <v>491.2385879836768</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>235478182.0657036</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.99405388123095e-07</v>
@@ -6012,7 +5767,7 @@
         <v>122.949</v>
       </c>
       <c r="C8" t="n">
-        <v>1023.582371831255</v>
+        <v>328.0308903184102</v>
       </c>
       <c r="D8" t="n">
         <v>1.31695e-07</v>
@@ -6045,16 +5800,13 @@
         <v>-8980.05141716383</v>
       </c>
       <c r="Y8" t="n">
-        <v>484.2022281744278</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>265067634.3005174</v>
+        <v>229.543662406341</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.943512660502939e-07</v>
+        <v>2.239866878784139e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9400341856764237</v>
+        <v>0.9957181834734088</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5817,7 @@
         <v>118.582</v>
       </c>
       <c r="C9" t="n">
-        <v>1072.44472888291</v>
+        <v>325.024100000898</v>
       </c>
       <c r="D9" t="n">
         <v>1.31155e-07</v>
@@ -6098,16 +5850,13 @@
         <v>-9199.663776734364</v>
       </c>
       <c r="Y9" t="n">
-        <v>477.2630158202608</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>522997955.0189785</v>
+        <v>215.7902786965983</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.905462105206098e-07</v>
+        <v>1.989356325724182e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9424188685858628</v>
+        <v>0.9990959231375911</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5867,7 @@
         <v>112.477</v>
       </c>
       <c r="C10" t="n">
-        <v>1025.661816279425</v>
+        <v>319.0517218009256</v>
       </c>
       <c r="D10" t="n">
         <v>1.30746e-07</v>
@@ -6151,16 +5900,13 @@
         <v>-9259.912521421697</v>
       </c>
       <c r="Y10" t="n">
-        <v>470.6356380197503</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>193889728.1771298</v>
+        <v>213.735987165905</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.874661518942262e-07</v>
+        <v>1.998220995930935e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9444193908480624</v>
+        <v>0.999551597375451</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5917,7 @@
         <v>112.05</v>
       </c>
       <c r="C11" t="n">
-        <v>1283.878746732733</v>
+        <v>112.05</v>
       </c>
       <c r="D11" t="n">
         <v>1.30443e-07</v>
@@ -6203,11 +5949,10 @@
       <c r="X11" t="n">
         <v>-9554.076816665018</v>
       </c>
-      <c r="Y11" t="n">
-        <v>464.3983617687056</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>381171840.461351</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.85087056957529e-07</v>
@@ -6370,7 +6115,7 @@
         <v>156.597</v>
       </c>
       <c r="C2" t="n">
-        <v>1163.452015238964</v>
+        <v>467.9868850712442</v>
       </c>
       <c r="D2" t="n">
         <v>1.42306e-07</v>
@@ -6403,10 +6148,7 @@
         <v>-5330.651193525006</v>
       </c>
       <c r="Y2" t="n">
-        <v>406.5263877950339</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12642.72418967486</v>
+        <v>1143.814389389751</v>
       </c>
       <c r="AA2" t="n">
         <v>1.902781240056709e-07</v>
@@ -6423,7 +6165,7 @@
         <v>144.466</v>
       </c>
       <c r="C3" t="n">
-        <v>1041.435274115405</v>
+        <v>348.3785274326452</v>
       </c>
       <c r="D3" t="n">
         <v>1.35224e-07</v>
@@ -6456,16 +6198,13 @@
         <v>-7786.252547697837</v>
       </c>
       <c r="Y3" t="n">
-        <v>402.5632672503307</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12428.16809904474</v>
+        <v>216.4931515639106</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.029988712923931e-07</v>
+        <v>1.865093004478816e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9999110807662449</v>
+        <v>0.9997036463503266</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6215,7 @@
         <v>140.4159999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>1059.467741471273</v>
+        <v>349.7996971724941</v>
       </c>
       <c r="D4" t="n">
         <v>1.32918e-07</v>
@@ -6509,16 +6248,13 @@
         <v>-8918.000010221309</v>
       </c>
       <c r="Y4" t="n">
-        <v>490.7816655345515</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>403831423.0850303</v>
+        <v>201.2298847192366</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.016494255454809e-07</v>
+        <v>1.709176886409174e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.935798926456311</v>
+        <v>0.9998765001861996</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6265,7 @@
         <v>131.302</v>
       </c>
       <c r="C5" t="n">
-        <v>947.4126166327284</v>
+        <v>413.1607760911345</v>
       </c>
       <c r="D5" t="n">
         <v>1.31922e-07</v>
@@ -6562,16 +6298,13 @@
         <v>-9212.277538662594</v>
       </c>
       <c r="Y5" t="n">
-        <v>485.0273788493913</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>399159616.1825728</v>
+        <v>127.1167951277386</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.950740920061707e-07</v>
+        <v>1.286597059743368e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9396962624956577</v>
+        <v>0.9995473482644203</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6315,7 @@
         <v>129.833</v>
       </c>
       <c r="C6" t="n">
-        <v>1103.02785397401</v>
+        <v>675.1784235970138</v>
       </c>
       <c r="D6" t="n">
         <v>1.31428e-07</v>
@@ -6615,16 +6348,13 @@
         <v>-9598.420101327862</v>
       </c>
       <c r="Y6" t="n">
-        <v>479.0293725002069</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>393594127.5226604</v>
+        <v>1.209518945849398</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.913407660562732e-07</v>
+        <v>3.381985957694052e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9420708134570979</v>
+        <v>0.5756874944254146</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6365,7 @@
         <v>123.119</v>
       </c>
       <c r="C7" t="n">
-        <v>1018.073763783344</v>
+        <v>123.119</v>
       </c>
       <c r="D7" t="n">
         <v>1.31122e-07</v>
@@ -6667,11 +6397,10 @@
       <c r="X7" t="n">
         <v>-9671.259169719857</v>
       </c>
-      <c r="Y7" t="n">
-        <v>473.0622106069381</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>519419597.5195135</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.884529039014557e-07</v>
@@ -6688,7 +6417,7 @@
         <v>121.6370000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1135.459616912134</v>
+        <v>655.3035760076276</v>
       </c>
       <c r="D8" t="n">
         <v>1.30908e-07</v>
@@ -6721,16 +6450,13 @@
         <v>-9823.446539917808</v>
       </c>
       <c r="Y8" t="n">
-        <v>467.4286805380581</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>25998813.56134218</v>
+        <v>0.9516449005011711</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.861501394209685e-07</v>
+        <v>3.060570278272389e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9456611105861568</v>
+        <v>0.5842458981528724</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6467,7 @@
         <v>117.744</v>
       </c>
       <c r="C9" t="n">
-        <v>1091.44860630519</v>
+        <v>43.36328958117315</v>
       </c>
       <c r="D9" t="n">
         <v>1.30734e-07</v>
@@ -6774,10 +6500,7 @@
         <v>-9892.228548268542</v>
       </c>
       <c r="Y9" t="n">
-        <v>461.9733608989825</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>506282223.6626672</v>
+        <v>922.3435561231249</v>
       </c>
       <c r="AA9" t="n">
         <v>1.845545453528326e-07</v>
@@ -6794,7 +6517,7 @@
         <v>111.126</v>
       </c>
       <c r="C10" t="n">
-        <v>1033.710589136977</v>
+        <v>637.0964839910166</v>
       </c>
       <c r="D10" t="n">
         <v>1.30613e-07</v>
@@ -6827,16 +6550,13 @@
         <v>-9772.807842384238</v>
       </c>
       <c r="Y10" t="n">
-        <v>456.7392632204899</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>267490486.5192766</v>
+        <v>0.9123351704406527</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.831211419317002e-07</v>
+        <v>2.737396528092794e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9478254228755277</v>
+        <v>0.5936696426392537</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6567,7 @@
         <v>109.556</v>
       </c>
       <c r="C11" t="n">
-        <v>1111.14077669072</v>
+        <v>127.8591935997878</v>
       </c>
       <c r="D11" t="n">
         <v>1.30519e-07</v>
@@ -6880,10 +6600,7 @@
         <v>-9835.281599579974</v>
       </c>
       <c r="Y11" t="n">
-        <v>431.5640462242851</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>18801.07281796883</v>
+        <v>851.8685480210017</v>
       </c>
       <c r="AA11" t="n">
         <v>1.597913339886611e-07</v>
@@ -6900,7 +6617,7 @@
         <v>107.623</v>
       </c>
       <c r="C12" t="n">
-        <v>1154.038641858809</v>
+        <v>508.7390054394026</v>
       </c>
       <c r="D12" t="n">
         <v>1.30417e-07</v>
@@ -6933,16 +6650,13 @@
         <v>-9947.876997571244</v>
       </c>
       <c r="Y12" t="n">
-        <v>446.955114352198</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>244719590.4818788</v>
+        <v>1.290920325456238</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.804911603909267e-07</v>
+        <v>1.275487827309383e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9498015790391859</v>
+        <v>0.9800828472684898</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6667,7 @@
         <v>102.094</v>
       </c>
       <c r="C13" t="n">
-        <v>986.8981265301948</v>
+        <v>613.3948442575859</v>
       </c>
       <c r="D13" t="n">
         <v>1.30343e-07</v>
@@ -6986,16 +6700,13 @@
         <v>-9746.406023358328</v>
       </c>
       <c r="Y13" t="n">
-        <v>442.3124520156859</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>484349398.751979</v>
+        <v>0.8668747427880447</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.795544539557422e-07</v>
+        <v>2.417687283784144e-07</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9505111675785279</v>
+        <v>0.6046654390025965</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6717,7 @@
         <v>103.254</v>
       </c>
       <c r="C14" t="n">
-        <v>1193.764220349209</v>
+        <v>608.4108158161742</v>
       </c>
       <c r="D14" t="n">
         <v>1.30268e-07</v>
@@ -7039,16 +6750,13 @@
         <v>-9976.647378674983</v>
       </c>
       <c r="Y14" t="n">
-        <v>437.6535848804979</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>957617410.9524475</v>
+        <v>0.8497108763567891</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.786284545913437e-07</v>
+        <v>2.506112599646621e-07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9512147569789502</v>
+        <v>0.6030323996697812</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6767,7 @@
         <v>98.05700000000002</v>
       </c>
       <c r="C15" t="n">
-        <v>1019.748058931598</v>
+        <v>602.4137222331517</v>
       </c>
       <c r="D15" t="n">
         <v>1.3021e-07</v>
@@ -7092,16 +6800,13 @@
         <v>-9758.860268520661</v>
       </c>
       <c r="Y15" t="n">
-        <v>376.286958931379</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>14384.64403881321</v>
+        <v>0.6930934641738566</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.795452761962009e-07</v>
+        <v>2.548137118334641e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9999579292659954</v>
+        <v>0.6026395244414132</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6817,7 @@
         <v>97.98000000000002</v>
       </c>
       <c r="C16" t="n">
-        <v>1189.948053595146</v>
+        <v>595.4755096546407</v>
       </c>
       <c r="D16" t="n">
         <v>1.30167e-07</v>
@@ -7145,16 +6850,13 @@
         <v>-9909.661166001237</v>
       </c>
       <c r="Y16" t="n">
-        <v>375.0470348808144</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14226.21648973086</v>
+        <v>0.6754193179619425</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.803149429303379e-07</v>
+        <v>2.498508541016659e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9998326290590018</v>
+        <v>0.6048536714042086</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6867,7 @@
         <v>97.19100000000003</v>
       </c>
       <c r="C17" t="n">
-        <v>1311.887432640683</v>
+        <v>591.2481547451321</v>
       </c>
       <c r="D17" t="n">
         <v>1.30108e-07</v>
@@ -7198,16 +6900,13 @@
         <v>-9933.115345005439</v>
       </c>
       <c r="Y17" t="n">
-        <v>423.4207669624959</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>347168929.1431149</v>
+        <v>0.8182299155965876</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.760298822197493e-07</v>
+        <v>2.687970148721283e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9532664706814449</v>
+        <v>0.6007807624155752</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6917,7 @@
         <v>93.07099999999997</v>
       </c>
       <c r="C18" t="n">
-        <v>1212.699557708002</v>
+        <v>583.9093004984604</v>
       </c>
       <c r="D18" t="n">
         <v>1.30087e-07</v>
@@ -7251,16 +6950,13 @@
         <v>-9841.999226486749</v>
       </c>
       <c r="Y18" t="n">
-        <v>418.6335670009601</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>116107200.4301946</v>
+        <v>0.7677114349800016</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.751255444743452e-07</v>
+        <v>2.602783999757189e-07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9540290363052227</v>
+        <v>0.6038625959869034</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6967,7 @@
         <v>89.29300000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1070.583422218474</v>
+        <v>578.4330223579506</v>
       </c>
       <c r="D19" t="n">
         <v>1.30049e-07</v>
@@ -7304,16 +7000,13 @@
         <v>-9705.656288385184</v>
       </c>
       <c r="Y19" t="n">
-        <v>413.8931146539479</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>113545739.5923299</v>
+        <v>0.8540094933319931</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.744172360890317e-07</v>
+        <v>2.679834196847002e-07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9546077214151859</v>
+        <v>0.6027999335975223</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7017,7 @@
         <v>87.60700000000003</v>
       </c>
       <c r="C20" t="n">
-        <v>1160.722349859492</v>
+        <v>567.3961667516703</v>
       </c>
       <c r="D20" t="n">
         <v>1.30006e-07</v>
@@ -7357,16 +7050,13 @@
         <v>-9670.69153992405</v>
       </c>
       <c r="Y20" t="n">
-        <v>409.0849011173936</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>670518833.5164906</v>
+        <v>1.017334898547292</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.737191179104628e-07</v>
+        <v>2.622250449986214e-07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9551744915128674</v>
+        <v>0.6045854738814479</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7067,7 @@
         <v>85.87400000000002</v>
       </c>
       <c r="C21" t="n">
-        <v>1304.559223552188</v>
+        <v>560.5993963959106</v>
       </c>
       <c r="D21" t="n">
         <v>1.29972e-07</v>
@@ -7410,16 +7100,13 @@
         <v>-9665.57285770849</v>
       </c>
       <c r="Y21" t="n">
-        <v>387.7908753102142</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6692.121581603515</v>
+        <v>0.9967198298730898</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.738064730148106e-07</v>
+        <v>2.570768618653348e-07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9719671782897866</v>
+        <v>0.6068896690352011</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7117,7 @@
         <v>83.32300000000004</v>
       </c>
       <c r="C22" t="n">
-        <v>1215.305039881726</v>
+        <v>241.1835826843511</v>
       </c>
       <c r="D22" t="n">
         <v>1.29958e-07</v>
@@ -7463,10 +7150,7 @@
         <v>-9637.663903255019</v>
       </c>
       <c r="Y22" t="n">
-        <v>399.4904205218741</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>219135433.561069</v>
+        <v>675.6673792859636</v>
       </c>
       <c r="AA22" t="n">
         <v>1.721173291768883e-07</v>
@@ -7629,7 +7313,7 @@
         <v>164.145</v>
       </c>
       <c r="C2" t="n">
-        <v>1255.80980786205</v>
+        <v>400.0510364601861</v>
       </c>
       <c r="D2" t="n">
         <v>1.46536e-07</v>
@@ -7662,16 +7346,13 @@
         <v>-4916.883607405103</v>
       </c>
       <c r="Y2" t="n">
-        <v>406.7013749986835</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12673.95832488556</v>
+        <v>165.2630187406387</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.041051549785037e-07</v>
+        <v>1.372705150034191e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9997809166510686</v>
+        <v>0.998873489956705</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7363,7 @@
         <v>150.611</v>
       </c>
       <c r="C3" t="n">
-        <v>1107.115626127752</v>
+        <v>350.506839365687</v>
       </c>
       <c r="D3" t="n">
         <v>1.39868e-07</v>
@@ -7715,16 +7396,13 @@
         <v>-7108.066875592928</v>
       </c>
       <c r="Y3" t="n">
-        <v>402.3967333229889</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12438.40576673371</v>
+        <v>204.6289845765121</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.908832667328552e-07</v>
+        <v>1.676996774844431e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.999995659168511</v>
+        <v>0.9996908770100092</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7413,7 @@
         <v>141.379</v>
       </c>
       <c r="C4" t="n">
-        <v>1000.206041668434</v>
+        <v>141.379</v>
       </c>
       <c r="D4" t="n">
         <v>1.37166e-07</v>
@@ -7767,11 +7445,10 @@
       <c r="X4" t="n">
         <v>-8241.051550060061</v>
       </c>
-      <c r="Y4" t="n">
-        <v>399.0392363469371</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12260.68819178515</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>2.044897567485924e-07</v>
@@ -7788,7 +7465,7 @@
         <v>134.634</v>
       </c>
       <c r="C5" t="n">
-        <v>1000.157846104174</v>
+        <v>134.634</v>
       </c>
       <c r="D5" t="n">
         <v>1.35893e-07</v>
@@ -7820,11 +7497,10 @@
       <c r="X5" t="n">
         <v>-8947.291811173791</v>
       </c>
-      <c r="Y5" t="n">
-        <v>483.2367862327099</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>795434118.2919952</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>2.042513512471488e-07</v>
@@ -7841,7 +7517,7 @@
         <v>127.058</v>
       </c>
       <c r="C6" t="n">
-        <v>960.0230227551526</v>
+        <v>407.611930030552</v>
       </c>
       <c r="D6" t="n">
         <v>1.35239e-07</v>
@@ -7874,16 +7550,13 @@
         <v>-9270.857118003354</v>
       </c>
       <c r="Y6" t="n">
-        <v>476.0343846787736</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>913377199.1937584</v>
+        <v>128.1161013512184</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.982868915923945e-07</v>
+        <v>1.353979255133625e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9409886443805884</v>
+        <v>0.9999920231649017</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7567,7 @@
         <v>120.492</v>
       </c>
       <c r="C7" t="n">
-        <v>969.5653888213758</v>
+        <v>456.6956379118301</v>
       </c>
       <c r="D7" t="n">
         <v>1.34888e-07</v>
@@ -7927,16 +7600,13 @@
         <v>-9449.576603802907</v>
       </c>
       <c r="Y7" t="n">
-        <v>468.5608150129989</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>769263496.4838506</v>
+        <v>67.19159725808309</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94258544206764e-07</v>
+        <v>1.098069008173198e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9437235128304052</v>
+        <v>0.9999988204555111</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7617,7 @@
         <v>113.827</v>
       </c>
       <c r="C8" t="n">
-        <v>923.0865994699102</v>
+        <v>629.9212973201249</v>
       </c>
       <c r="D8" t="n">
         <v>1.34727e-07</v>
@@ -7980,16 +7650,13 @@
         <v>-9527.183326988787</v>
       </c>
       <c r="Y8" t="n">
-        <v>461.0746054231596</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>191129122.1236848</v>
+        <v>8.054755904205203</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.911993270942463e-07</v>
+        <v>2.501480378316305e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9459606737290084</v>
+        <v>0.6002271206678972</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7667,7 @@
         <v>111.611</v>
       </c>
       <c r="C9" t="n">
-        <v>1006.304417225533</v>
+        <v>509.4409187847888</v>
       </c>
       <c r="D9" t="n">
         <v>1.34625e-07</v>
@@ -8033,16 +7700,13 @@
         <v>-9769.071633018755</v>
       </c>
       <c r="Y9" t="n">
-        <v>453.9242508402796</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>372760312.7674243</v>
+        <v>2.405638388032988</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.889777124154979e-07</v>
+        <v>1.119304828256204e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.94763584162269</v>
+        <v>0.9872315743307487</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7717,7 @@
         <v>107.979</v>
       </c>
       <c r="C10" t="n">
-        <v>1111.378115128727</v>
+        <v>104.304030476849</v>
       </c>
       <c r="D10" t="n">
         <v>1.34624e-07</v>
@@ -8086,10 +7750,7 @@
         <v>-9898.147979322495</v>
       </c>
       <c r="Y10" t="n">
-        <v>433.2829199540236</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>18601.14084679451</v>
+        <v>837.8295129323412</v>
       </c>
       <c r="AA10" t="n">
         <v>1.673282442456265e-07</v>
@@ -8106,7 +7767,7 @@
         <v>103.611</v>
       </c>
       <c r="C11" t="n">
-        <v>1143.57240934804</v>
+        <v>375.6579518432681</v>
       </c>
       <c r="D11" t="n">
         <v>1.34624e-07</v>
@@ -8139,16 +7800,13 @@
         <v>-9966.186121799577</v>
       </c>
       <c r="Y11" t="n">
-        <v>440.7223450521758</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>361616311.7910796</v>
+        <v>121.0050309685899</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.854817428250025e-07</v>
+        <v>1.489423884010486e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9504812654111526</v>
+        <v>0.9991171113938115</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7963,7 @@
         <v>137.29</v>
       </c>
       <c r="C2" t="n">
-        <v>979.8305464705882</v>
+        <v>486.8759643142221</v>
       </c>
       <c r="D2" t="n">
         <v>1.37658e-07</v>
@@ -8338,16 +7996,13 @@
         <v>-9101.12092754331</v>
       </c>
       <c r="Y2" t="n">
-        <v>404.4399193174224</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12345.21611574376</v>
+        <v>61.24951964288145</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.99883031353931e-07</v>
+        <v>9.95450099956209e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9998882259251549</v>
+        <v>0.9999882985420225</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8013,7 @@
         <v>132.749</v>
       </c>
       <c r="C3" t="n">
-        <v>964.5952938566454</v>
+        <v>411.4939819584769</v>
       </c>
       <c r="D3" t="n">
         <v>1.36808e-07</v>
@@ -8391,16 +8046,13 @@
         <v>-9557.452151639169</v>
       </c>
       <c r="Y3" t="n">
-        <v>488.3659983783317</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>269850633.6384178</v>
+        <v>132.8528708506747</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.021145338287357e-07</v>
+        <v>1.326246438232803e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9398572149639584</v>
+        <v>0.9989644151899881</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8063,7 @@
         <v>130.929</v>
       </c>
       <c r="C4" t="n">
-        <v>1038.479552603714</v>
+        <v>405.079370811399</v>
       </c>
       <c r="D4" t="n">
         <v>1.36447e-07</v>
@@ -8444,16 +8096,13 @@
         <v>-9835.01333775173</v>
       </c>
       <c r="Y4" t="n">
-        <v>481.8846398858158</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>461881724.3072599</v>
+        <v>130.3830317506073</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.988277955919509e-07</v>
+        <v>1.309833296378263e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.94196544878889</v>
+        <v>0.9997083739706025</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8113,7 @@
         <v>126.822</v>
       </c>
       <c r="C5" t="n">
-        <v>1046.76818274176</v>
+        <v>126.822</v>
       </c>
       <c r="D5" t="n">
         <v>1.36289e-07</v>
@@ -8496,11 +8145,10 @@
       <c r="X5" t="n">
         <v>-9902.70273760533</v>
       </c>
-      <c r="Y5" t="n">
-        <v>474.9741872024891</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>129967435.5110029</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.964067020412649e-07</v>
@@ -8517,7 +8165,7 @@
         <v>120.126</v>
       </c>
       <c r="C6" t="n">
-        <v>990.5088401429487</v>
+        <v>390.6339993069756</v>
       </c>
       <c r="D6" t="n">
         <v>1.36206e-07</v>
@@ -8550,16 +8198,13 @@
         <v>-9762.399579159044</v>
       </c>
       <c r="Y6" t="n">
-        <v>468.1697256762132</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>256938874.3915394</v>
+        <v>130.490186971668</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.947734700580416e-07</v>
+        <v>1.365293523382235e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9448496271848609</v>
+        <v>0.9998128562010972</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8215,7 @@
         <v>116.328</v>
       </c>
       <c r="C7" t="n">
-        <v>1031.950715761211</v>
+        <v>526.6724335545671</v>
       </c>
       <c r="D7" t="n">
         <v>1.36181e-07</v>
@@ -8603,16 +8248,13 @@
         <v>-9770.418568911437</v>
       </c>
       <c r="Y7" t="n">
-        <v>461.8220178493131</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>17788407.85547392</v>
+        <v>0.9449520611710795</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.927872500261712e-07</v>
+        <v>1.518808117732833e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9463822055227681</v>
+        <v>0.9624666818724528</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8265,7 @@
         <v>111.123</v>
       </c>
       <c r="C8" t="n">
-        <v>1030.84451196451</v>
+        <v>632.9397243143508</v>
       </c>
       <c r="D8" t="n">
         <v>1.36158e-07</v>
@@ -8656,16 +8298,13 @@
         <v>-9670.831283868571</v>
       </c>
       <c r="Y8" t="n">
-        <v>455.8673221642141</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>499497517.2968128</v>
+        <v>0.9363762026245556</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.919593652997132e-07</v>
+        <v>2.918020225370546e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9470254613061763</v>
+        <v>0.5884866988635957</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8315,7 @@
         <v>106.431</v>
       </c>
       <c r="C9" t="n">
-        <v>971.7208900437239</v>
+        <v>628.7716310329437</v>
       </c>
       <c r="D9" t="n">
         <v>1.36135e-07</v>
@@ -8709,16 +8348,13 @@
         <v>-9581.306293118661</v>
       </c>
       <c r="Y9" t="n">
-        <v>450.3495627653526</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>246920193.1798993</v>
+        <v>1.047231829800822</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.90864635234706e-07</v>
+        <v>3.305302426536541e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9478747392038033</v>
+        <v>0.5808686235771552</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8365,7 @@
         <v>104.567</v>
       </c>
       <c r="C10" t="n">
-        <v>1024.32566357718</v>
+        <v>380.9897368904705</v>
       </c>
       <c r="D10" t="n">
         <v>1.36074e-07</v>
@@ -8762,16 +8398,13 @@
         <v>-9607.697271928855</v>
       </c>
       <c r="Y10" t="n">
-        <v>433.8294656084345</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>18519.18294441571</v>
+        <v>117.4510308657245</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.681629965889808e-07</v>
+        <v>1.459807414149358e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9998751517380779</v>
+        <v>0.9983568041878775</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8415,7 @@
         <v>102.786</v>
       </c>
       <c r="C11" t="n">
-        <v>1077.522493135924</v>
+        <v>378.4185419985265</v>
       </c>
       <c r="D11" t="n">
         <v>1.36079e-07</v>
@@ -8815,16 +8448,13 @@
         <v>-9635.946465106061</v>
       </c>
       <c r="Y11" t="n">
-        <v>440.1205649007259</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>248156617.5353783</v>
+        <v>115.5979822344307</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.888682204305977e-07</v>
+        <v>1.48009552533157e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9494278332461855</v>
+        <v>0.9982215899513142</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8465,7 @@
         <v>98.75400000000002</v>
       </c>
       <c r="C12" t="n">
-        <v>994.5099983067635</v>
+        <v>292.3421478988295</v>
       </c>
       <c r="D12" t="n">
         <v>1.36102e-07</v>
@@ -8868,16 +8498,13 @@
         <v>-9513.390534011367</v>
       </c>
       <c r="Y12" t="n">
-        <v>382.8694290590216</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>14469.59741488218</v>
+        <v>207.0272837760581</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.862969646006185e-07</v>
+        <v>2.372643037614867e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9999393712832486</v>
+        <v>0.9999361564870493</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8515,7 @@
         <v>94.11799999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>992.1539921021799</v>
+        <v>171.8198627191779</v>
       </c>
       <c r="D13" t="n">
         <v>1.36091e-07</v>
@@ -8921,10 +8548,7 @@
         <v>-9371.071786548766</v>
       </c>
       <c r="Y13" t="n">
-        <v>430.2630813247082</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>119801808.4312982</v>
+        <v>776.8968702238933</v>
       </c>
       <c r="AA13" t="n">
         <v>1.870885169653327e-07</v>
@@ -8941,7 +8565,7 @@
         <v>93.03299999999996</v>
       </c>
       <c r="C14" t="n">
-        <v>991.1879716898829</v>
+        <v>281.5686994245898</v>
       </c>
       <c r="D14" t="n">
         <v>1.36096e-07</v>
@@ -8974,16 +8598,13 @@
         <v>-9344.808101891927</v>
       </c>
       <c r="Y14" t="n">
-        <v>425.4186914818209</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>350390756.63888</v>
+        <v>213.3900148748561</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.865259779459644e-07</v>
+        <v>2.983471637692719e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9513691556777275</v>
+        <v>0.9902020093365473</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8615,7 @@
         <v>91.27699999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>1099.822213150909</v>
+        <v>278.1202783703171</v>
       </c>
       <c r="D15" t="n">
         <v>1.36134e-07</v>
@@ -9027,16 +8648,13 @@
         <v>-9375.785307874887</v>
       </c>
       <c r="Y15" t="n">
-        <v>420.4897265050199</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>584701814.4546447</v>
+        <v>207.587046571055</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.857085210908023e-07</v>
+        <v>2.562949320106654e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9520788412508524</v>
+        <v>0.9989878327730087</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8665,7 @@
         <v>87.447</v>
       </c>
       <c r="C16" t="n">
-        <v>990.0702302213865</v>
+        <v>263.1534052097318</v>
       </c>
       <c r="D16" t="n">
         <v>1.36277e-07</v>
@@ -9080,16 +8698,13 @@
         <v>-9210.873821406965</v>
       </c>
       <c r="Y16" t="n">
-        <v>415.4866774599119</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>343793953.5746257</v>
+        <v>212.6977760004465</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.852958126006104e-07</v>
+        <v>2.60558896207303e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9525870515467489</v>
+        <v>0.9973081272803079</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8715,7 @@
         <v>86.803</v>
       </c>
       <c r="C17" t="n">
-        <v>1149.640203432681</v>
+        <v>247.5243996091247</v>
       </c>
       <c r="D17" t="n">
         <v>1.36349e-07</v>
@@ -9133,10 +8748,7 @@
         <v>-9244.894357243344</v>
       </c>
       <c r="Y17" t="n">
-        <v>392.9751011143074</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6800.783006640148</v>
+        <v>697.3590938281105</v>
       </c>
       <c r="AA17" t="n">
         <v>5.356609355350524e-07</v>
@@ -9153,7 +8765,7 @@
         <v>82.68099999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>1089.662904311614</v>
+        <v>253.1453726768919</v>
       </c>
       <c r="D18" t="n">
         <v>1.36447e-07</v>
@@ -9186,16 +8798,13 @@
         <v>-9094.909101556685</v>
       </c>
       <c r="Y18" t="n">
-        <v>405.8943965311582</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>888811135.5946382</v>
+        <v>204.7857426799792</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.841049705917868e-07</v>
+        <v>2.494893865628354e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9537673865691624</v>
+        <v>0.9996318852689394</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8815,7 @@
         <v>82.83499999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>1233.470705629034</v>
+        <v>271.6752088793789</v>
       </c>
       <c r="D19" t="n">
         <v>1.36478e-07</v>
@@ -9239,10 +8848,7 @@
         <v>-9187.541307310519</v>
       </c>
       <c r="Y19" t="n">
-        <v>383.6129946062841</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3295.095923306363</v>
+        <v>664.6875980186073</v>
       </c>
       <c r="AA19" t="n">
         <v>2.81412877121526e-06</v>
@@ -9259,7 +8865,7 @@
         <v>81.00900000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>1215.796057556671</v>
+        <v>246.8292855175999</v>
       </c>
       <c r="D20" t="n">
         <v>1.36544e-07</v>
@@ -9292,16 +8898,13 @@
         <v>-9111.269712031131</v>
       </c>
       <c r="Y20" t="n">
-        <v>380.2516164576234</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3259.133067576397</v>
+        <v>202.8611118469443</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.403575972039832e-06</v>
+        <v>2.61009624832326e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7484743821202079</v>
+        <v>0.9987113277099234</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8915,7 @@
         <v>79.14699999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>1313.980347482655</v>
+        <v>241.9780207568798</v>
       </c>
       <c r="D21" t="n">
         <v>1.36603e-07</v>
@@ -9345,16 +8948,13 @@
         <v>-9078.588658721843</v>
       </c>
       <c r="Y21" t="n">
-        <v>392.8432717743761</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>107719829.1197938</v>
+        <v>209.6762052692786</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.825235297600877e-07</v>
+        <v>2.85265057613666e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.955279690106187</v>
+        <v>0.9982259224856607</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8965,7 @@
         <v>78.04400000000004</v>
       </c>
       <c r="C22" t="n">
-        <v>1258.178056584324</v>
+        <v>237.8895948923308</v>
       </c>
       <c r="D22" t="n">
         <v>1.3662e-07</v>
@@ -9398,16 +8998,13 @@
         <v>-9055.588524306166</v>
       </c>
       <c r="Y22" t="n">
-        <v>381.7539626031968</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6189.487186110757</v>
+        <v>212.0365509999505</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.909160522697561e-07</v>
+        <v>3.035434608890816e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8355441216339506</v>
+        <v>0.9968991506577087</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9161,7 @@
         <v>132.198</v>
       </c>
       <c r="C2" t="n">
-        <v>1100.035775917173</v>
+        <v>426.0549329911551</v>
       </c>
       <c r="D2" t="n">
         <v>1.48587e-07</v>
@@ -9597,16 +9194,13 @@
         <v>-5125.45594776426</v>
       </c>
       <c r="Y2" t="n">
-        <v>394.0273055527683</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11885.6028818909</v>
+        <v>104.1236629254671</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.97948087298246e-07</v>
+        <v>1.184812401854728e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.999999213679143</v>
+        <v>0.999579020542448</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9211,7 @@
         <v>121.381</v>
       </c>
       <c r="C3" t="n">
-        <v>932.229388860159</v>
+        <v>331.9312248511531</v>
       </c>
       <c r="D3" t="n">
         <v>1.4166e-07</v>
@@ -9650,16 +9244,13 @@
         <v>-7701.821708693514</v>
       </c>
       <c r="Y3" t="n">
-        <v>467.4287572890287</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>256549186.5122571</v>
+        <v>192.4858415064213</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.181598486608101e-07</v>
+        <v>1.794244816072111e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9336117382660001</v>
+        <v>0.9996664037799582</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9261,7 @@
         <v>117.897</v>
       </c>
       <c r="C4" t="n">
-        <v>1018.304647277355</v>
+        <v>310.7837475955075</v>
       </c>
       <c r="D4" t="n">
         <v>1.40262e-07</v>
@@ -9703,16 +9294,13 @@
         <v>-8738.453666687641</v>
       </c>
       <c r="Y4" t="n">
-        <v>460.322971337899</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>252804608.0011402</v>
+        <v>210.4896076211499</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.061608372826926e-07</v>
+        <v>2.131884711283871e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9406617542949743</v>
+        <v>0.9982942301444357</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9311,7 @@
         <v>112.633</v>
       </c>
       <c r="C5" t="n">
-        <v>1028.210968145772</v>
+        <v>306.4518696495924</v>
       </c>
       <c r="D5" t="n">
         <v>1.39783e-07</v>
@@ -9756,16 +9344,13 @@
         <v>-9151.082280136625</v>
       </c>
       <c r="Y5" t="n">
-        <v>452.8972180414294</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>255803581.5874311</v>
+        <v>202.6489916076483</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.005989739130881e-07</v>
+        <v>1.999344000466601e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9442940925952736</v>
+        <v>0.9998283139890556</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9361,7 @@
         <v>107.253</v>
       </c>
       <c r="C6" t="n">
-        <v>1043.828025669308</v>
+        <v>298.4557396581797</v>
       </c>
       <c r="D6" t="n">
         <v>1.39562e-07</v>
@@ -9809,16 +9394,13 @@
         <v>-9348.650045344886</v>
       </c>
       <c r="Y6" t="n">
-        <v>445.0636877213517</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>243658313.1678612</v>
+        <v>211.0034392670857</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.97140394558811e-07</v>
+        <v>2.340550598696776e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9467047746450715</v>
+        <v>0.9993858134814191</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9411,7 @@
         <v>102.761</v>
       </c>
       <c r="C7" t="n">
-        <v>1100.801712569618</v>
+        <v>373.6198081965938</v>
       </c>
       <c r="D7" t="n">
         <v>1.39515e-07</v>
@@ -9862,16 +9444,13 @@
         <v>-9503.690102312696</v>
       </c>
       <c r="Y7" t="n">
-        <v>385.3661195390713</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14547.46765430388</v>
+        <v>115.7998853880339</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.008013279205159e-07</v>
+        <v>1.469451818172141e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9992962544183825</v>
+        <v>0.9986913081768766</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9461,7 @@
         <v>96.03199999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>997.8732534491644</v>
+        <v>96.03199999999998</v>
       </c>
       <c r="D8" t="n">
         <v>1.39503e-07</v>
@@ -9914,11 +9493,10 @@
       <c r="X8" t="n">
         <v>-9405.70016972862</v>
       </c>
-      <c r="Y8" t="n">
-        <v>430.3080223354208</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>472047266.44802</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.924431853210026e-07</v>
@@ -9935,7 +9513,7 @@
         <v>94.892</v>
       </c>
       <c r="C9" t="n">
-        <v>1227.852638126394</v>
+        <v>94.892</v>
       </c>
       <c r="D9" t="n">
         <v>1.39566e-07</v>
@@ -9967,11 +9545,10 @@
       <c r="X9" t="n">
         <v>-9633.690206354831</v>
       </c>
-      <c r="Y9" t="n">
-        <v>423.6776555416881</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>118879938.0130415</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.908423511782025e-07</v>
@@ -9988,7 +9565,7 @@
         <v>90.32500000000005</v>
       </c>
       <c r="C10" t="n">
-        <v>1259.548712205572</v>
+        <v>575.3398436610039</v>
       </c>
       <c r="D10" t="n">
         <v>1.39635e-07</v>
@@ -10021,16 +9598,13 @@
         <v>-9636.609214677765</v>
       </c>
       <c r="Y10" t="n">
-        <v>417.5579821825693</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>684358810.9056885</v>
+        <v>0.7166952147494591</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.894254397876975e-07</v>
+        <v>2.727652165713491e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9528759661385404</v>
+        <v>0.5990129283558633</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9615,7 @@
         <v>87.31099999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>1231.891983627613</v>
+        <v>568.24911844516</v>
       </c>
       <c r="D11" t="n">
         <v>1.39687e-07</v>
@@ -10074,16 +9648,13 @@
         <v>-9670.766551158607</v>
       </c>
       <c r="Y11" t="n">
-        <v>411.8004330729737</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>225184336.6018699</v>
+        <v>0.7869542216427844</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.883334130830972e-07</v>
+        <v>2.811923761107804e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.953822149758292</v>
+        <v>0.5979811960485171</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 43.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.562517861787804e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9998984313897374</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111.034</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>393.1375121203559</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.21877e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-85.479</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.498064984013751</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.13056517263901</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.54534966393635</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.709603545391055</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.67345789147953</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.48389126762358</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.75694325943202</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-11487.07792864877</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>115.5092190178254</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.413227815671875e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9988396973911638</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9978925374209698</v>
+      </c>
+      <c r="D13" t="n">
+        <v>389.9470332465943</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9918845727629654</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.21706e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-85.53100000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.615822070002371</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.30971990842309</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.657069891783118</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.312833693690826</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.98943798105245</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.54226836466799</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>23.29816343455167</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-11672.04758836881</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>115.0396688281925</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.437609888003083e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9988362067970054</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107.058</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9641911486571686</v>
+      </c>
+      <c r="D14" t="n">
+        <v>369.0961940355513</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9388475600938214</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.21654e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.57599999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3759338438155597</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.266491423414512</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.309548961343252</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.625008559950261</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26.11067964817921</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.54356734158762</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>23.31049877075992</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-11511.17811510823</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>132.068863318476</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.570583015879457e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.999500924167575</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101.009</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.909712340364213</v>
+      </c>
+      <c r="D15" t="n">
+        <v>364.346271688827</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9267654712564934</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.21681e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.614</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7278953813868868</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.111526830766749</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.092392684115601</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.05296493605384</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.50876778046046</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>22.98447655082196</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-11131.44345889026</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>130.9867566470461</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.612990674537793e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9993955617918182</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100.884</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9085865590719957</v>
+      </c>
+      <c r="D16" t="n">
+        <v>360.7839381604804</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.917704179930887</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.21714e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.657</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4239175232880282</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.418244385936854</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.534634398464361</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.661322897361482</v>
+      </c>
+      <c r="L16" t="n">
+        <v>26.26360988055358</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.5734402858692</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>23.5978199794432</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-11316.36532269195</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>127.5376804222755</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.593846945440637e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9996314215325894</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96.67000000000002</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8706342201487834</v>
+      </c>
+      <c r="D17" t="n">
+        <v>356.5982934557671</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9070574098423796</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.21763e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.343806164094166</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.028813004435182</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.304540802828944</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.685005772423159</v>
+      </c>
+      <c r="L17" t="n">
+        <v>26.37018502618132</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.57321150208318</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>23.59559264896013</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-11120.50638872414</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>125.4162914120047</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.607748093762147e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9997189049285887</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92.58099999999996</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.833807662517787</v>
+      </c>
+      <c r="D18" t="n">
+        <v>352.3763342996183</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8963182688904567</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.21797e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-85.74299999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2465965043653856</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7742734912069574</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.204670621169021</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.406985535341656</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.44237205809437</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.57396297053552</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.60291016483175</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10928.84622222615</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>122.8375684266353</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.61324777700663e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9998222867757806</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92.83600000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8361042563539098</v>
+      </c>
+      <c r="D19" t="n">
+        <v>363.5614150790643</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.924769079191209</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.21849e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-85.77500000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.592475060556911</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.549254021929868</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.618783363779842</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.098627842702488</v>
+      </c>
+      <c r="L19" t="n">
+        <v>26.52515620004833</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.6201997380898</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>24.06203076246477</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11028.15515365553</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>105.6634490798958</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.557502360943997e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9996830018059121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>88.91300000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8007727362789777</v>
+      </c>
+      <c r="D20" t="n">
+        <v>358.5103441400158</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9119209769793242</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2186e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-85.812</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4121955186703252</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.233672573071515</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.668458148705125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.349063866725893</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.57090745224842</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.62176336246442</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>24.07786908152043</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10849.98111226879</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>105.3298916078426</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.589970239593471e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9997109639480265</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>85.56799999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.770646828899256</v>
+      </c>
+      <c r="D21" t="n">
+        <v>353.163383995616</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8983202393759306</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.21908e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-85.848</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2590538658664723</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.091883927589709</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.437694252952816</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.335138704223782</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26.50995549484729</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.62426279911098</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>24.10322973688432</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10685.70562937583</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>103.214824506067</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.562517861787804e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9998984313897374</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>2.524918971067003e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.6119413900505389</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>152.116</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1173.231563150335</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.3932e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.14100000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.475774105996191</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.340798365733638</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.382780009481888</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.03928351258479</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.35271666777359</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.75361082380941</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.6301883770523</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-10237.77529729316</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-486.9281747797837</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.002963919265197e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9998150281767894</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>136.16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8951063661942205</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1062.987620544652</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9060339441348996</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.38816e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-84.389</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.04694676317254729</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.771695213200041</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.085177194395737</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.746459548249609</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.16123754457142</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.86801453331059</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.27553172399951</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10225.80026693201</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-415.2241597101865</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.033548430802535e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9994891820039503</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>130.073</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8550908517184254</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1034.384902024568</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8816545126411877</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3855e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.54000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1850965405114281</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.147893602295457</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.276609371526637</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.145533763439372</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.06246853764968</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.99463662222448</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>19.04702207835942</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10455.1848436522</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-404.9035518725938</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.990652598113316e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9440582907179439</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>123.693</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8131491756291251</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1359.184169524242</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.158496082286255</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.38423e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.642</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.09669975221970598</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8256110082463605</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.182731477283581</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.872594246667172</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.25437825847916</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.05229228180562</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>19.42024977459458</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10473.11808597432</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-687.9789024176778</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.967874488134689e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9456830340559175</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>123.217</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8100199847484818</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1065.558087822047</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9082248733240986</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.38341e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.72499999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6335791408776297</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.484297514765185</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.002531433575686</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.710192882424346</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.96151564682213</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.1484519955907</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>20.0762762800646</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10723.71554120652</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-448.2570379018582</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.951177372400178e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9468978798471355</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>117.8629999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7748231612716608</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1116.461100401698</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9516118858955701</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.3832e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.79000000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2772725054151764</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.278317337541601</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.596067949537625</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.344036184494658</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.10891866197506</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.15410263922493</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>20.11620436901852</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10561.92770538805</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-498.8464189543818</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.939213991495241e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9478156635032924</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>112.949</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7425188671803099</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1151.354994819718</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9813535801305289</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.38292e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.846</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3371762925458369</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.013924433197723</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.43869779539055</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.302741488649794</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.19344868475416</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.15259833623313</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20.10555932756268</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10382.57052443704</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-535.0952903431721</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.926628158384923e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9487789283146691</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>109.577</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.720351573798943</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1178.593180473253</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.004569956597929</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.38276e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.901</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.120312834783556</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9116036561180713</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.144913857574066</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.77475913896488</v>
+      </c>
+      <c r="L30" t="n">
+        <v>23.17191207971772</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.16967435030494</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20.227060204375</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10284.4133261859</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-565.0367699786013</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.918950822923622e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9493776349719382</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>107.128</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7042520181966394</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1271.005953575688</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.083337674757753</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.38275e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.96599999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1636217802792677</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.096067955142881</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.417222021543542</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.864394796488423</v>
+      </c>
+      <c r="L31" t="n">
+        <v>23.34335892261344</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.21713930138537</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>20.57261359278333</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10323.95713170192</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-651.0187726879689</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.908091545169312e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9502431792854391</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107.184</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7046201583002448</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1289.084343123687</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.098746729641561</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.38246e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-85.01900000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.738026075196713</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.632282004893971</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.94876068170361</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.815732595296071</v>
+      </c>
+      <c r="L32" t="n">
+        <v>23.8487517607747</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.28212837708256</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>21.06530631163319</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10463.5038952236</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-674.6284682443269</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.898921551635108e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9509534874983399</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98.173</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6453824712719242</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1331.501212293001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.134900606251747</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.38252e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-85.07599999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7391401177011701</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.968595493828279</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.585611969117083</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.5388302555615</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.21878386703551</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.58479756704478</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9974.061216264234</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-717.8995930573194</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.837559702970311e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9999959393445056</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97.65899999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6420034710352626</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1329.53440061493</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.133224200894232</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.38252e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-85.127</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2715608159208113</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.305258456062109</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.376470415448587</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.311155078345822</v>
+      </c>
+      <c r="L34" t="n">
+        <v>23.94836444987298</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.28312877332847</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>21.07307454636441</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10103.12217246724</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-722.7667832439737</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.879020514223816e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9525751409833911</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97.04899999999998</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.637993373478135</v>
+      </c>
+      <c r="D35" t="n">
+        <v>339.5360307737552</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2894024005474594</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.38236e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-85.188</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.7016771247678796</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.469482987166348</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.968066630154539</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.680085860792805</v>
+      </c>
+      <c r="L35" t="n">
+        <v>24.32197932690363</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.3412444748015</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21.53437854716059</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10203.67937700934</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>139.5237288643458</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.688635895224027e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9996425068165601</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91.786</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6033947776696732</v>
+      </c>
+      <c r="D36" t="n">
+        <v>334.3011856538374</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2849404978128779</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.38235e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.23999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2809168972164609</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.176690574905693</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.137352179047209</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.981282355905681</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24.1586797275439</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.32769129915327</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21.42500507312465</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-9962.51997390038</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>137.7795714403348</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.718224863515911e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9973546047890247</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87.50200000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5752320597438798</v>
+      </c>
+      <c r="D37" t="n">
+        <v>538.8682349253738</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4593025382631344</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.38211e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.29600000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09617405587563245</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7306858390665311</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.105656533393577</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.150539355246621</v>
+      </c>
+      <c r="L37" t="n">
+        <v>24.42343665120592</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.32683850046057</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21.41816009015758</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9779.586126269876</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.543561878336522</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.051248212194628e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.6929787462290383</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86.09699999999998</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5659956875016434</v>
+      </c>
+      <c r="D38" t="n">
+        <v>348.9347700128432</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2974133845119981</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.38191e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.34</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1634627236718083</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9053999980693651</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.210340920245432</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.89697110336235</v>
+      </c>
+      <c r="L38" t="n">
+        <v>24.38769466395458</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.35856119094636</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.67575560179438</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9762.714503639863</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>112.0217796893801</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.683784154990684e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9934626921160109</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>84.90300000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5581464145783482</v>
+      </c>
+      <c r="D39" t="n">
+        <v>342.7629661489112</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2921528681247986</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.38217e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.393</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3959331006745198</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.12444271927814</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.689852375216731</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.553662756328057</v>
+      </c>
+      <c r="L39" t="n">
+        <v>24.81134427145725</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.40076229016793</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>22.02817729008412</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9791.801966194686</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>115.1932474560575</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.889352259220669e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.991471347627451</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>81.95100000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.53874017197402</v>
+      </c>
+      <c r="D40" t="n">
+        <v>334.1439853309033</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2848065086432445</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.38204e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.437</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3419375932295302</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.084158237929219</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.613375277855167</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.188023407280983</v>
+      </c>
+      <c r="L40" t="n">
+        <v>24.81346526841397</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.41476181194837</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>22.14762714149477</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9688.696603969463</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>112.589836360293</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.616906008931532e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9998345267388703</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79.39999999999998</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5219700754687211</v>
+      </c>
+      <c r="D41" t="n">
+        <v>447.4624531405108</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.3813931257858377</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.38201e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.488</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3894763862806926</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.195977061298191</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.639990820451866</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.186855874680746</v>
+      </c>
+      <c r="L41" t="n">
+        <v>24.97210622964122</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.43925964484517</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>22.3597933157277</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9628.025938073208</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.08302146457254778</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.336053464211262e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9864732088691101</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>77.44400000000002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5091114675642274</v>
+      </c>
+      <c r="D42" t="n">
+        <v>531.7185011145255</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.4532084865555158</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.38224e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.535</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4796944412396227</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.222430354674741</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.579462796360525</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.399082055532102</v>
+      </c>
+      <c r="L42" t="n">
+        <v>25.09746798441813</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.46225202544657</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>22.56264523749822</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9567.236172464309</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.6949605473428572</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.48189142676577e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.6122513847719943</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>74.32099999999997</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.4885810828578189</v>
+      </c>
+      <c r="D43" t="n">
+        <v>523.308969301479</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.4460406502330209</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.38183e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.58199999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1336079939815636</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8549879087056381</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.253063567280239</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.259235063803729</v>
+      </c>
+      <c r="L43" t="n">
+        <v>25.14070926973163</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.46557665444269</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.59228138957229</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9408.347395802168</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.860960094545797</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.524918971067003e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.6119413900505389</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.784358586492543e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.999295154611737</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>159.045</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>436.5539872617217</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.26222e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.042</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.02006141162594387</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6813320833303445</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.707953526058151</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.480321398676549</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.99694208181844</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.43059951118163</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16.031162259784</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9422.928647581273</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>130.3137070631984</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.213940282879496e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9998264362169335</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>148.058</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9309189223175832</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1127.128321250138</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.581876134770944</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.24867e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-84.63800000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2762480576915456</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.066072704473001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.257522493590164</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.659652668156382</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.09300658904428</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.94673674351195</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.7476574448952</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10697.82883941937</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-453.8643452770906</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.803074358482611e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9431919351530109</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>144.494</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.908510170077651</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1157.149354269861</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.650644337320255</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.24229e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.883</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7168368032680483</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.642542448772186</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.829883268286677</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.50600067035771</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.84349840746794</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.1843403406146</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20.33258849785576</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-11461.02016369687</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-489.3990252073327</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.755091809728803e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9465185824057925</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>134.744</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.847206765380867</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1182.92247407474</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.709681983423411</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.23792e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.03</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2031251485576933</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.078695432394456</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.229066733129253</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.048984791357706</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.62508192127668</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.2415026110381</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>20.75459768106075</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-11453.90399392915</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-520.6073616984394</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.724789585196178e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9486443685463221</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>129.321</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8131094973120815</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1205.155656262001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.76061080972212</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.23538e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-85.136</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03395802345199635</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9319088656741357</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.111161901781046</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.356790024948748</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.34239052383703</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.30334346330827</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>21.23127879177869</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-11541.56319972459</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-547.0952221133434</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.704402094990969e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.950147569215644</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>125.398</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7884435222735704</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1266.340875700292</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.900765799078817</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.2336e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-85.20099999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1329775345315374</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7097266183052781</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.997218785342924</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.062876720936861</v>
+      </c>
+      <c r="L28" t="n">
+        <v>24.50968509135404</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.33059210203039</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>21.44832106403827</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-11500.88834006986</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-605.66440733852</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.69132117389684e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.951114823638282</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7582759596340661</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1267.914054120122</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.904369427646496</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.23243e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-85.27</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.08366829408212841</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7393174921803723</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.970054884312112</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.633529961926851</v>
+      </c>
+      <c r="L29" t="n">
+        <v>24.75138470299545</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.35871986952019</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>21.67705964981787</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11462.61975899953</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-613.6463017984979</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.679658385701025e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9520256578241579</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>119.231</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7496683328617688</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1324.919085546901</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.034948996474493</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.23148e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-85.324</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2351602019831642</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9440310824274031</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.422868039114056</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.255352333376808</v>
+      </c>
+      <c r="L30" t="n">
+        <v>25.1598097739164</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.40757389299669</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>22.08613573582901</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11547.34065857199</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-668.1221002857462</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.669914090478229e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9528012917036756</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>113.814</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7156087899651046</v>
+      </c>
+      <c r="D31" t="n">
+        <v>397.184987991961</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9098187156262112</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.23045e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-85.378</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1330945602294581</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8811545346006974</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.068586909892362</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.01340445945948</v>
+      </c>
+      <c r="L31" t="n">
+        <v>25.23352874722596</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.40392988344449</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>22.05509184559907</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11339.343005484</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>122.2285038748345</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.511540022655397e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9965020572469636</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7174070231695432</v>
+      </c>
+      <c r="D32" t="n">
+        <v>393.4405744918123</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9012415095774577</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.23009e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-85.432</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4376277717160629</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.183673057268587</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.232100154517358</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.363768364743894</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25.50777088932153</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.48002114924114</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>22.72194872631269</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11575.92274465447</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>121.253191639261</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.54129348694883e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9962077584895057</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>109.333</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.687434373919331</v>
+      </c>
+      <c r="D33" t="n">
+        <v>389.2539329493716</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.891651306155651</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.22943e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-85.494</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1966747041883397</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9134407392466988</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.304483691803782</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.990541152965071</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25.69701343928157</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.48528646505123</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>22.76958536501676</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-11402.43312596591</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>119.283369711728</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.547162919267179e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9967968622224848</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106.611</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6703197208337264</v>
+      </c>
+      <c r="D34" t="n">
+        <v>368.7464055584406</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.844675381094093</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.22922e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-85.536</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3807435652225644</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.195777418575569</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.543820356756943</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.370227939882775</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25.92292508756285</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.51266748418475</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>23.02055762487994</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-11384.84990869904</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>132.714998360169</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.572835781433576e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9994246125022498</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101.192</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6362476028796884</v>
+      </c>
+      <c r="D35" t="n">
+        <v>364.902279927266</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8358697677144357</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.22883e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-85.58799999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.05021640564264288</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6401151916227621</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.907868985058256</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.834980755357262</v>
+      </c>
+      <c r="L35" t="n">
+        <v>25.98172781645002</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.49221507848974</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>22.83257488128287</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-11079.83760917102</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>129.9011479431514</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.565092929818383e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.999698544327655</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100.108</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6294319217831433</v>
+      </c>
+      <c r="D36" t="n">
+        <v>360.8545623267019</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8265977928415147</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.22869e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.616</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.139709482255082</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.835509936486323</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.306556527966307</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.410321456584334</v>
+      </c>
+      <c r="L36" t="n">
+        <v>26.13340088562437</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.51352262591496</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>23.02848473922619</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11044.36899255705</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>129.5410478852713</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.62496291065582e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9994428058207168</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99.22000000000003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.623848596309221</v>
+      </c>
+      <c r="D37" t="n">
+        <v>357.2333447185609</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8183027876100771</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.22842e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.666</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4287646241859284</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.237987456612016</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.491203568809191</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.537775901320875</v>
+      </c>
+      <c r="L37" t="n">
+        <v>26.3653022063356</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.57432410905598</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>23.60642840734059</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11222.44230193034</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>124.9933705547369</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.545711416421309e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9999175214297932</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>96.62399999999997</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6075261718381589</v>
+      </c>
+      <c r="D38" t="n">
+        <v>353.6498722863588</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8100942440237971</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.22817e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.708</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3865148380764288</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.081118707873803</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.424469058195723</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.359618002481254</v>
+      </c>
+      <c r="L38" t="n">
+        <v>26.41190443918372</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.58786958777797</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>23.73914996465069</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-11128.24050024595</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>126.8079978461378</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.672397251324642e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9994935503215576</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93.05500000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5850859819547929</v>
+      </c>
+      <c r="D39" t="n">
+        <v>350.1622915313835</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8021053563793362</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.22823e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.747</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4382917020114817</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.006561296247088</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.475784677602883</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.546300417133263</v>
+      </c>
+      <c r="L39" t="n">
+        <v>26.59395066007152</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.59321992049954</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>23.79198503063794</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10991.06095853327</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>124.6112302786286</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.679897900032576e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9996376762595744</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90.387</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.568310855418278</v>
+      </c>
+      <c r="D40" t="n">
+        <v>347.402310853315</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7957831585330163</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.22813e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.786</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4026974429185312</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.012567217288507</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.427655325333039</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.842658370462146</v>
+      </c>
+      <c r="L40" t="n">
+        <v>26.74030907279414</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.60104075517688</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>23.86964032774446</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10865.3657687703</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>121.9129313179795</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.651622435907756e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9997515722643651</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>88.02199999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5534408500738786</v>
+      </c>
+      <c r="D41" t="n">
+        <v>343.9342104663964</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7878388939331847</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.22799e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.834</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1870615141255193</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9420821154372865</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.322813455832535</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.610268182771206</v>
+      </c>
+      <c r="L41" t="n">
+        <v>26.93514943143227</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.62590043864432</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>24.11987506486819</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10830.89718086393</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>118.2136467457048</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.626414114609732e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9999526867950295</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87.18299999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5481656135056117</v>
+      </c>
+      <c r="D42" t="n">
+        <v>340.6238558259784</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7802559723770626</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.22782e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.86799999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5226983461511077</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.326017170318513</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.705209874580485</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.318176688153188</v>
+      </c>
+      <c r="L42" t="n">
+        <v>27.08265147976215</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.66290251126932</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>24.50218679043504</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10889.83940663235</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>121.9141261439913</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.803977710026419e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9993830686025157</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>85.15499999999997</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5354145053286805</v>
+      </c>
+      <c r="D43" t="n">
+        <v>336.6331407235271</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7711145712699898</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.22782e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.90600000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6525958339876212</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.344528814498283</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.661386503885761</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.086375350911268</v>
+      </c>
+      <c r="L43" t="n">
+        <v>27.1659141625917</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.67765532804282</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>24.65801046179894</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10810.36290001218</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>121.0914262434111</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.784358586492543e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.999295154611737</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.429831427006072e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.999990353663238</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>209.035</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>401.2613795187285</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.33531e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-80.646</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3997101335746112</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9579531812400802</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.735497319427433</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.323191850930975</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.339553448209161</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.61148465490307</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.931361708390968</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5726.098901218926</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>200.0148252407723</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.553770695062358e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9934428615604237</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>154.019</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7368096251823859</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1213.267103520583</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.023632887310938</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.33344e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-82.31100000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5967151955278622</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.679509173521366</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.476501196981239</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11.98563313399784</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.91405985065113</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.23591938899878</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6518.575708509353</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-505.4999413960589</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.840975831861445e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9998888089043908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>144.379</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.690692946157342</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1104.057617687545</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.751467432554181</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.31803e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.16500000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.04418395448903512</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8406701237290288</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.149325092385044</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.663839249465283</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.16753972167822</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.66840459879103</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.20219815765341</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7485.110977076128</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-435.8891044052908</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.890058265048753e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9996584835899288</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>133.923</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6406726146339131</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1134.384532389937</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.827046384953654</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.30535e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.69799999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0502142075191835</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3797962221137179</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.801349248435532</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.454533421364928</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15.9366079875371</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.07286087970242</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.56684513451065</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8087.332519489385</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-472.5236358466956</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.015777721681117e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9331563818601806</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>135.055</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6460879756978498</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1169.962110781625</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.91571073245293</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.29573e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.039</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5233815184556738</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.265704394096411</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.464744512004526</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.507658125371115</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17.43268953513221</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.43320913555776</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.04292176921274</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8860.775408076453</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-510.9122883967842</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.944049037367472e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9375121193153352</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>126.454</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6049417561652354</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1221.774982934549</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.04483572378668</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.28854e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.292</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.076969724710381</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.107292483000662</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.990187261550909</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.46852211007045</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.58621265841869</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.76377519673984</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9077.780506269131</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-562.8196445067099</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.892266163094472e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9407542024929905</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6046834262204897</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1322.594231834298</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.296091523736008</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.28259e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.48699999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6005000136375176</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.50258524869654</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.449600726062259</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.469345186179327</v>
+      </c>
+      <c r="L18" t="n">
+        <v>19.40775849416005</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.77606535230156</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.75324396651028</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9520.059202138427</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-655.3977525309872</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.852393989027738e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9432845055454072</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>115.272</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5514483220513312</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1340.584147692002</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.340924933518132</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.2785e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.639</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.06845624205007139</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4906574316985448</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.898076374934577</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.850772477552279</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.01685330212042</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.80329664906893</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.90479430418617</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9359.790435706926</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-680.5465040796907</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.823038878499942e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9452261901838206</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>116.248</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5561173966082236</v>
+      </c>
+      <c r="D20" t="n">
+        <v>401.598684828852</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.000840612446999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.27535e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.768</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3844162719373275</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.355443940790754</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.419399196025323</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.331231812774295</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20.69534187491804</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.95602581339388</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.80497656734565</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9755.057238820251</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>115.9813165871188</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.338572462234393e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9992824994891025</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>108.895</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5209414691319635</v>
+      </c>
+      <c r="D21" t="n">
+        <v>397.1261616386629</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9896944533136349</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.27265e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.88</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1701202404786945</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8702167958898136</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.139342119021276</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.955301753832355</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21.13439463484062</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.98779446968977</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19.00367767416309</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9649.279662247052</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>119.852627393032</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.429831427006072e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.999990353663238</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.376995180561874e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9999133607220535</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>155.151</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1149.581462854682</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.31674e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.20099999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3544044141700317</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.240948333529991</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.351081730863987</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.158546604184598</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.61755631499368</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.75686995902248</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.47849269998558</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7844.41869113777</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-459.4701707071359</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.924358387235392e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9997028775464016</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>147.662</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9517308944189852</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1115.29882839323</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9701781599919677</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.29589e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.946</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5999897874378282</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.352317126395047</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.490257460014134</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.039347227454787</v>
+      </c>
+      <c r="L24" t="n">
+        <v>17.37420708027346</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.40086647281839</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.89838146188267</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9073.047758489638</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-445.8076928555338</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.149230094569739e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9997357816521073</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>136.335</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8787245973277648</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1142.142066600957</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9935286045451263</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.28507e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.324</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1698237576725094</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.180341544415037</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.327529705965993</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.195336681214826</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.20239856177039</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.68099121148317</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.24360535910375</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9633.593617101664</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-482.1067577723513</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.890940657958642e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9403958798607552</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>134.586</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8674517083357504</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1121.442864821319</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9755227455012294</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.27906e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.529</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5454179952246183</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.398937973783689</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.727365961141865</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.737049762833533</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.31473087706724</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.87281736834721</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.30365586519027</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10133.09697532537</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-471.5035931061269</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.848622104889686e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9431254484829242</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>132.3480000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8530270510663809</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1182.085323827921</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.028274517312174</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.2756e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.65600000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6468688324261942</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.431477444353858</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.535392329224563</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.18396786692971</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20.81016608073797</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.97273533993433</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.90896901900303</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10350.66085402469</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-528.7239217890933</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.822322986399571e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9448907885277107</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>126.07</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8125632448388987</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1352.420120012293</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.176445657582121</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.27313e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.77200000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3798237901184996</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.229116883733857</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.614935696077886</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.526548905527156</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.50313580674187</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.02392868172051</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.23483551983694</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10352.62168042783</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-678.3840186052639</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.800972400513979e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9463967156440627</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>120.049</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7737558894238518</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1310.730650511814</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.140180746527489</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.27132e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.866</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1235251076517488</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9754441742102534</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.872187948900396</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.710947272191799</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.7234467247179</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.04530412314432</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19.37423764942856</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10236.73152171815</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-651.5735117673054</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.783459648837793e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9476695140069712</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>117.192</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7553415704700582</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1331.55640035258</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.158296687427449</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.26985e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.93899999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2194417997159607</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.023845494173272</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.126436183806898</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.783635213303251</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.00509831412915</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.08828942822355</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.66076169421184</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10235.41958354107</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-676.4290803617671</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.769803435356875e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9486745646100498</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>112.386</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7243652957441461</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1399.957206581304</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.217797304337946</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.26859e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-85.026</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2266007871599048</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7975615402076944</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.92268743175522</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.920602720443727</v>
+      </c>
+      <c r="L31" t="n">
+        <v>22.40619861057819</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.12680688794293</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.92478131305116</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10204.35551686627</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-741.7205909939219</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.57660098914171e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9999173347112819</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>112.249</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7234822849997745</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1448.108092140099</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.259682883668031</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.26796e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-85.096</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4205543320746853</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.271799809568574</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.554690850673257</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.403377152249709</v>
+      </c>
+      <c r="L32" t="n">
+        <v>22.79974487726218</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.21278467146085</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>20.54042114758403</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10422.60324982645</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-790.6804099526441</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.743270847449702e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9507432195730967</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106.749</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6880329485468996</v>
+      </c>
+      <c r="D33" t="n">
+        <v>363.3912833618828</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3161074661551139</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.26736e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-85.155</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2535042373929217</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9700550319072805</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.19006491689411</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.124252942047283</v>
+      </c>
+      <c r="L33" t="n">
+        <v>22.92222518536044</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.21836579054334</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.58169882942542</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10263.56464186314</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>145.8300097186927</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.722747884851695e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9954802531878971</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>104.573</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6740079019793622</v>
+      </c>
+      <c r="D34" t="n">
+        <v>360.5937415329954</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3136739354143342</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.26678e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-85.22</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3624341700110033</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.227086479201673</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.369425581267661</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.75240656818286</v>
+      </c>
+      <c r="L34" t="n">
+        <v>23.34193895378793</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.26918221924089</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20.96529037908487</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10325.78309714612</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>136.6665846488773</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.634214463287535e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9978051496000589</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101.169</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6520679853819825</v>
+      </c>
+      <c r="D35" t="n">
+        <v>356.4839194605513</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3100988759642293</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.26634e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-85.285</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2727990876512653</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.096057014803005</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.301491138172305</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.987584661558331</v>
+      </c>
+      <c r="L35" t="n">
+        <v>23.51356602066616</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.29428391070608</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21.16008480675994</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10263.64102231978</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>132.2715465214674</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.574148140764438e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9989873859510656</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98.55499999999995</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6352198825660159</v>
+      </c>
+      <c r="D36" t="n">
+        <v>351.6080538580483</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3058574491840904</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.26593e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.33799999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5455520381181017</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.160940591579517</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.405711564648111</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.327624614454526</v>
+      </c>
+      <c r="L36" t="n">
+        <v>23.69331796829992</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.32539904225365</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21.40661618350779</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10241.78598667324</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>139.7247322083331</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.715933374726662e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.997856034309522</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>95.04999999999995</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6126289872446838</v>
+      </c>
+      <c r="D37" t="n">
+        <v>347.2832470784322</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3020953784484711</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.26532e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.39100000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3015502624735869</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9661854673862428</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.12152435412739</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.093404841174725</v>
+      </c>
+      <c r="L37" t="n">
+        <v>23.86988557308976</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.33485663091844</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21.48269046211154</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10115.92548771846</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>137.4212482753082</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.720494803012082e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.997759686726807</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91.50100000000003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5897544972317292</v>
+      </c>
+      <c r="D38" t="n">
+        <v>483.8708606305227</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.4209104585150122</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.26501e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.44</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.156884837427829</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8603255926133673</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.306880512467143</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.231890674690672</v>
+      </c>
+      <c r="L38" t="n">
+        <v>24.07675127273935</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.34918501267336</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.59897751061589</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10017.24339804782</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.08066719005441447</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.400404728881619e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.977087857298037</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>89.58100000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5773794561427256</v>
+      </c>
+      <c r="D39" t="n">
+        <v>477.1396283983201</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.4150550820587084</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.26465e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.492</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3006683079209203</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.041138244082948</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.099587729303634</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.989572779915354</v>
+      </c>
+      <c r="L39" t="n">
+        <v>24.19251502075264</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.38391162875087</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.88609463819268</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10020.23849438376</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.002548030666965827</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.361072848055471e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9815430238892092</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>88.363</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5695290394518888</v>
+      </c>
+      <c r="D40" t="n">
+        <v>364.6458390193933</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.3171987812972311</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.26436e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.538</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4456952176819545</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.274863190948975</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.307591231035479</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.527706771257221</v>
+      </c>
+      <c r="L40" t="n">
+        <v>24.46852268750228</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.4219028213531</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>22.20905654856715</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10042.57369212209</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>97.78277651148099</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.513006547054653e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9995016270329236</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>86.37099999999998</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5566899343220474</v>
+      </c>
+      <c r="D41" t="n">
+        <v>332.8665247858694</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2895545340121293</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.26448e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.604</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4160785005036447</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.232299277192768</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.778803121870737</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.998402178870927</v>
+      </c>
+      <c r="L41" t="n">
+        <v>24.85712647448448</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.46456485809695</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>22.58325389037036</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10071.80720284362</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>125.666420981305</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.691126831237372e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9995980062282763</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5397967141687775</v>
+      </c>
+      <c r="D42" t="n">
+        <v>350.1099792667131</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.3045543013518219</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.26408e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.63</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4452103540508591</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.143570692945262</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.272634424652358</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.529323469763023</v>
+      </c>
+      <c r="L42" t="n">
+        <v>24.69904286047521</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.46018208192284</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>22.5442326720281</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9901.44086903851</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>111.463685743762</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.9933159117251e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9893811427957924</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>82.41199999999998</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.531172857409878</v>
+      </c>
+      <c r="D43" t="n">
+        <v>377.1000800203544</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.3280324989617751</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.26399e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.691</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5754502226072059</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.546719961598293</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.7608144066603</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.068726595157379</v>
+      </c>
+      <c r="L43" t="n">
+        <v>25.11667288035622</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.50748958817188</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.97267493502651</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9956.995427501939</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>69.41337139568014</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.376995180561874e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9999133607220535</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.85087056957529e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.946007829065397</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>210.2189999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>380.8526935726225</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.39652e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.28100000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1146316828067182</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7840212850958661</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.697444560885033</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.073637778868484</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.854044009088873</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.43146814434007</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.526180134975394</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4906.653469620401</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>239.1191903432328</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.896106474643178e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9865147514512298</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>161.701</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7692025934858413</v>
+      </c>
+      <c r="D13" t="n">
+        <v>491.0604641926202</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.289371120330498</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.38938e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.46299999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4167006627657125</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9941867980624347</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.973418795610133</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.363233524614934</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10.51004439527396</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.2843643292851</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.991118926571867</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-5956.536332184563</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>87.41029580984089</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.982129187510363e-10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9998957322753346</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>146.492</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.696854232966573</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1523.094915623616</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.999170653976708</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.36576e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.57899999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1407654690218086</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9307829421784474</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.063164701408363</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.568052484173761</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12.83533003890617</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.23755006454805</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.00301676073075</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6971.035278165876</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-776.1241744885635</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.859463378083317e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9999991021158158</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>138.17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6572669454235823</v>
+      </c>
+      <c r="D15" t="n">
+        <v>347.4742433903804</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9123586343340975</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.34733e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.238</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1404552189876341</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8017318981992715</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.834684822075591</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.389232816537859</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.68142902309558</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.77015761713605</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.52098910127571</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-7715.468949892682</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>220.0235360128802</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.808051120979774e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9987102416994608</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>134.57</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6401419472074362</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1156.663918172929</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.03703751527327</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.33341e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.655</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1916619688938439</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.092626031514734</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.434438776238661</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.056207040511231</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16.26086172761088</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.13889687054176</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.81675557844247</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8355.624879283245</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-491.0438156947745</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.060720263312138e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9330450462422147</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>128.045</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6091028879406714</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1199.162629836977</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.148625833752481</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.32392e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.952</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1457133103712917</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8412103800271707</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.009707942309766</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.621480790823135</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17.31945622839273</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.34544783306758</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.65665373048136</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8663.688710141796</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-535.6964288195826</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.99405388123095e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9369498524599772</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>122.949</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5848615015769268</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1281.112513975916</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.363800586411313</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.31695e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.18899999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1756337913171277</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8518660094531794</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.159353487492581</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.906418277217292</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18.30343342044674</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.53091970359502</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.49594230121561</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8980.05141716383</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-614.7161904344155</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.943512660502939e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9400341856764237</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>118.582</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5640879273519521</v>
+      </c>
+      <c r="D19" t="n">
+        <v>325.024100000898</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8534115827092636</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31155e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.36799999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1791496812357724</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9091043665810022</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.268333221349141</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.102262764286349</v>
+      </c>
+      <c r="L19" t="n">
+        <v>19.10213949443775</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.66738375692333</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.17303966190399</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9199.663776734364</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>215.7902786965983</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.989356325724182e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9990959231375911</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>112.477</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5350467845437378</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1426.509006016194</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.745566278223476</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.30746e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.51900000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.05044876704027373</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8641634560604031</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.180425159899577</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.830687712391539</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19.70515488251706</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.7501538257503</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.61139418433698</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9259.912521421697</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-757.2697264118397</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.874661518942262e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9444193908480624</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.533015569477545</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1524.820225673076</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.003700778296627</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.30443e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.642</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5249074740817415</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.420562082252159</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.488979276858108</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.345392384512293</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.27296710282083</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.8818227022586</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.35662202035759</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9554.076816665018</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-850.0830006856287</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.85087056957529e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.946007829065397</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>2.512983352900975e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.6093971882880923</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>156.597</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1231.544288821183</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.42306e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.05960886685827692</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8709805314737928</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.7609097573077</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.081471180612329</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9.662577267808693</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.80803281961077</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.217191926709539</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-5330.651193525006</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-523.0613366165403</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.902781240056709e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9999383188321949</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>144.466</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9225336372982877</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1067.938370938296</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8671538495465008</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.35224e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.29000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3163668276813403</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.133183326842582</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.266481540846609</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.013847614041132</v>
+      </c>
+      <c r="L24" t="n">
+        <v>14.92152194812426</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.83759170343708</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.74083065649531</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7786.252547697837</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-410.9880336934664</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.029988712923931e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9999110807662449</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>140.4159999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8966710728813445</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1073.636611645624</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8717807563975589</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.32918e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.937</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4352094542020332</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.174014612661243</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.345899164330677</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.796160662782817</v>
+      </c>
+      <c r="L25" t="n">
+        <v>17.37911636378105</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.406450606668</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.92315153544811</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8918.000010221309</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-423.979128864129</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.016494255454809e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.935798926456311</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>131.302</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8384707242156614</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1170.545650925192</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9504697975950359</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.31922e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.221</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.06213590705918972</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8535761500454822</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.861627189955541</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.419185027535506</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18.55571192495933</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.59079509749448</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.78636139048578</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9212.277538662594</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-513.5546869823077</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.950740920061707e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9396962624956577</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>129.833</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8290899570234423</v>
+      </c>
+      <c r="D27" t="n">
+        <v>675.1784235970138</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5482372251860185</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.31428e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.39100000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3800046835878143</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.431035218039846</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.470708251277147</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.14139108526691</v>
+      </c>
+      <c r="L27" t="n">
+        <v>19.47379097674646</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.76041595398152</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.66730197519954</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9598.420101327862</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.209518945849398</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.381985957694052e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.5756874944254146</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>123.119</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7862155724566882</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1163.175873269417</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9444856216927386</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.31122e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.533</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2700908663110408</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9498596209804127</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.474221101342276</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.137233657737396</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20.06979569143826</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.84147896049464</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.12168655372665</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9671.259169719857</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-524.6757309065789</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.884529039014557e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9440308768844026</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>121.6370000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7767517896255997</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1228.721092561943</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9977075966452311</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.30908e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.629</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4265672169254108</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.448762354855692</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.516757373651028</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.057803782017665</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20.4625132331745</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.92651739183607</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.62408867942026</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9823.446539917808</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-587.9171726836992</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.861501394209685e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9456611105861568</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>117.744</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7518917986934616</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1215.886136100997</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9872857575141099</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.30734e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.73099999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4552319842863794</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.404668005361177</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.59702826592178</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.095742839364547</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.89436060009053</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.99006427642644</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.01803486729019</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9892.228548268542</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-584.6415623490291</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.845545453528326e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9467734134339629</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>111.126</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7096304526906643</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1399.512574297136</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.136388343481118</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.30613e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.807</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1505232608781688</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.023311427474708</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.15637139061261</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.869170013938338</v>
+      </c>
+      <c r="L31" t="n">
+        <v>21.20445953005314</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.00453847256939</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.11009969566631</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9772.807842384238</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-747.2266426061956</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.831211419317002e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9478254228755277</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>109.556</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6996047178426148</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1327.05646675542</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.077554805621859</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.30519e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.878</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3095322409849081</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.318337033220233</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.392839000933385</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.354463138623346</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.57882433494729</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.05765847991218</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.45573065087112</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9835.281599579974</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-692.9160292771705</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.597913339886611e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9999972783639973</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107.623</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6872609309246024</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1453.115068499048</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.179912961059606</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.30417e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.959</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4395331992096812</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.115723509171313</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.543292030614381</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.219296245403276</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21.89699663339411</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.12188335730089</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19.89063917113916</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9947.876997571244</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-806.548623002472</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.804911603909267e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9498015790391859</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>102.094</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6519537411316946</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1449.572973249478</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.177036819875142</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.30343e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-85.014</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.08662598976392412</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8735530977319437</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.125929232164609</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.845522040166058</v>
+      </c>
+      <c r="L34" t="n">
+        <v>22.01738011180716</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.11057003409572</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.81262760123422</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9746.406023358328</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-809.3899605615367</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.795544539557422e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9505111675785279</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>103.254</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6593612904461771</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1449.343777883779</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.176850715836676</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.30268e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-85.068</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6186418229937373</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.401735886956014</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.668824821116524</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.793499492043711</v>
+      </c>
+      <c r="L35" t="n">
+        <v>22.39248186452674</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.19282027189048</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20.39410805037572</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-9976.647378674983</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-814.4077313603042</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.786284545913437e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9512147569789502</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98.05700000000002</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.626174192353621</v>
+      </c>
+      <c r="D36" t="n">
+        <v>602.4137222331517</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.489153112641831</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.3021e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.126</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.213950989592435</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8952682635437815</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.071429962429696</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.060564384534883</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22.48740032788779</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.17991225279945</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.30061086878671</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-9758.860268520661</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.6930934641738566</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.548137118334641e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.6026395244414132</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97.98000000000002</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6256824843387804</v>
+      </c>
+      <c r="D37" t="n">
+        <v>595.4755096546407</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4835193626894423</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.30167e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.182</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4689698471852871</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.280552378852972</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.652732597872371</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.834665332889926</v>
+      </c>
+      <c r="L37" t="n">
+        <v>22.8867804894568</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.24525866733592</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>20.78294006953185</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9909.661166001237</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.6754193179619425</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.498508541016659e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.6048536714042086</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97.19100000000003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6206440736412575</v>
+      </c>
+      <c r="D38" t="n">
+        <v>591.2481547451321</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.480086798430178</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.30108e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.227</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5472879766288816</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.502814893312586</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.896157807703604</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.771292955259984</v>
+      </c>
+      <c r="L38" t="n">
+        <v>22.97121833171535</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.28075196465225</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.05462758697695</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9933.115345005439</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.8182299155965876</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.687970148721283e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.6007807624155752</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93.07099999999997</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5943345019380956</v>
+      </c>
+      <c r="D39" t="n">
+        <v>583.9093004984604</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.4741277319854817</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.30087e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.286</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3225931628812211</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.293903811219536</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.546782545464775</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.508127662851948</v>
+      </c>
+      <c r="L39" t="n">
+        <v>23.21463974109932</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.29584037462348</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.17228227836089</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9841.999226486749</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.7677114349800016</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.602783999757189e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.6038625959869034</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>89.29300000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5702088801190316</v>
+      </c>
+      <c r="D40" t="n">
+        <v>578.4330223579506</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4696810562221994</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.30049e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.32899999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4504001942063772</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.018825339997433</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.217616778885624</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.145883526887121</v>
+      </c>
+      <c r="L40" t="n">
+        <v>23.28256993521964</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.29893838289193</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>21.19660210689043</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9705.656288385184</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.8540094933319931</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.679834196847002e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.6027999335975223</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87.60700000000003</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.559442390339534</v>
+      </c>
+      <c r="D41" t="n">
+        <v>567.3961667516703</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.4607192545992593</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.30006e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.377</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3364349653934542</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.207853808999192</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.330872044191811</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.992339890089732</v>
+      </c>
+      <c r="L41" t="n">
+        <v>23.46109240877554</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.32316930768758</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.38875905435805</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9670.69153992405</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.017334898547292</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.622250449986214e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.6045854738814479</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>85.87400000000002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5483757670964323</v>
+      </c>
+      <c r="D42" t="n">
+        <v>560.5993963959106</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.4552003541281561</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.29972e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.431</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2489376998696005</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.105595333171572</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.247979014734664</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.257693173514006</v>
+      </c>
+      <c r="L42" t="n">
+        <v>23.70461072009237</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.35571614915852</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.65240109565561</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9665.57285770849</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.9967198298730898</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.570768618653348e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.6068896690352011</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83.32300000000004</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5320855444229456</v>
+      </c>
+      <c r="D43" t="n">
+        <v>553.8284368971784</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.449702411780331</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.29958e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.486</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3435494059156975</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.19516783040611</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.325443317766465</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.610145823385347</v>
+      </c>
+      <c r="L43" t="n">
+        <v>24.02101664322306</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.38390616017077</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21.8860488247102</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9637.663903255019</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.967089337012384</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.512983352900975e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.6093971882880923</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.854817428250025e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9504812654111526</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>164.145</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1213.930363327429</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.46536e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-80.31999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3191663407834493</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.323581373630826</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.297582480834405</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.718923911524125</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.817115927035504</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.25551928412541</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.455935831900218</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4916.883607405103</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-505.2940863056073</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.041051549785037e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9997809166510686</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>150.611</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9175485089402666</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1091.825462840636</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8994135873230005</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.39868e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7769901204978937</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.410140311063439</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.691427814944546</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.837974625778998</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.31967765152675</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.41471683543011</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.46889401353725</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7108.066875592928</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-427.0263362675585</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.908832667328552e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.999995659168511</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>141.379</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8613055530171497</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1026.010064532072</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8451968049631273</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.37166e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.59399999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2832702501702717</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.161086506325127</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.414345668445945</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.793399272524229</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16.17710376477499</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.12056153617527</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.7465143923594</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8241.051550060061</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-382.562707400109</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.044897567485924e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9994988221519534</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>134.634</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8202138353285203</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1053.970144414049</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.868229493432454</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.35893e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.039</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1903316903567134</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.097917376647189</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.287879196223056</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.850602832852489</v>
+      </c>
+      <c r="L15" t="n">
+        <v>18.03368759306585</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.48516577153818</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.2806791870285</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8947.291811173791</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-415.2626648231545</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.042513512471488e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9372152002926653</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>127.058</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7740595205458589</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1089.983177541537</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8978959670749576</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.35239e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.318</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1225013414020026</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.793064387829692</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.131436259027911</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.617336588400018</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19.24057335814374</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.67737573901671</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17.22479987946551</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9270.857118003354</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-455.420682092664</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.982868915923945e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9409886443805884</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>120.492</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7340583021109384</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1141.699566419992</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9404984016468211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.34888e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.51300000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1322441926297824</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7132482830140715</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.055998651993042</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.46683316136669</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20.19501551085345</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.80559389034082</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.91769719831354</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9449.576603802907</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-509.2135890910925</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.94258544206764e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9437235128304052</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>113.827</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6934539583904475</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1203.029627211868</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9910202953605333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.34727e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.67400000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4491893089745564</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.786228582966176</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.51250088378609</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.93577914790201</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.89852981274684</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>18.45570112438506</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9527.183326988787</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-571.5012144998291</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.911993270942463e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9459606737290084</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111.611</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6799536994730269</v>
+      </c>
+      <c r="D19" t="n">
+        <v>509.4409187847888</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4196623910027194</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.34625e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.79300000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2954213490297393</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.012122583285205</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.165433332542397</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.072177231206577</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.67233118301949</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.01807146389051</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19.19698561240869</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9769.071633018755</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.405638388032988</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.119304828256204e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9872315743307487</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>107.979</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.657826921319565</v>
+      </c>
+      <c r="D20" t="n">
+        <v>376.8075736996927</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3104029564487117</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.34624e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.899</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3381093448266241</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.257249769975397</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.4951402944205</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.939623297659938</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.12543433481855</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.10289545096438</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19.7600536932658</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9898.147979322495</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>122.7641146167293</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.452707434646449e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9976778518513899</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103.611</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6312163026592342</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1410.954534818779</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.162302696631872</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.34624e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-85.008</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4359154589433544</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.423730256620228</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.220794942921865</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.938280891433217</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.64295695079005</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.17089277067454</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>20.23578563964865</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9966.186121799577</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-778.0794960347589</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.854817428250025e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9504812654111526</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>3.035434608890816e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9968991506577087</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>137.29</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1198.388832920946</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.37658e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.93899999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1158908043594208</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8521700584220727</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.982314245936723</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.728214939519055</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.98776676508053</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.47229885089921</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16.22114759837187</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9101.12092754331</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-528.7573707573519</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.99883031353931e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9998882259251549</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>132.749</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9669240294267613</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1026.586624394327</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8566390108059763</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.36808e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-84.19799999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1753405892997655</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.115637792783331</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.027785560273903</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.663718991129719</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19.22505132879944</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.68515496020835</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.26531340498492</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9557.452151639169</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-392.487145240055</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.021145338287357e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9398572149639584</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>130.929</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9536674193313425</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1069.547960462381</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.89248825680015</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.36447e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.343</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5850701934633005</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.367071938372318</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.596247720054103</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.36359844463819</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20.11954234059651</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.81762399037687</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.98557043939468</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9835.01333775173</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-435.8131144783138</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.988277955919509e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.94196544878889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>126.822</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9237526403962418</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1117.237608145306</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9322830599331925</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.36289e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.458</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4483747376507275</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.308464732147652</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.479662535741855</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.220411496441116</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.51574975438492</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.8931267023886</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.42354229138594</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9902.70273760533</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-484.8629177785313</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.964067020412649e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9436617081568603</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>120.126</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.874979969407823</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1137.965999528308</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.949579942892689</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.36206e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.541</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.246399652915849</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.050917048523854</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.378815443536467</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.87216079633553</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20.69587283657493</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.90912910900869</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.51911349111962</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9762.399579159044</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-511.3930123788631</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.947734700580416e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9448496271848609</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>116.328</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8473159006482632</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1182.112279876358</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9864179700298819</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.36181e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.621</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3201659410488321</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.209104097040859</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.489387644762878</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.033866808645328</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20.97046834852049</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.9600921985341</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.8301787328163</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9770.418568911437</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-557.540549172501</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.927872500261712e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9463822055227681</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>111.123</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8094034525457063</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1208.804507875528</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.008691398541486</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.36158e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.691</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1319360301170859</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9278776668047305</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.239818105526463</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.126814411848562</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.20140078597801</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.98052124933479</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.95781768805162</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9670.831283868571</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-588.6470931370095</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.919593652997132e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9470254613061763</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106.431</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7752276203656498</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1243.949449250218</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.038018225034877</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.36135e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.748</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.07718927628230446</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9416468852430222</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.135134657264378</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.5268602865481</v>
+      </c>
+      <c r="L30" t="n">
+        <v>21.21331607308323</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.99892763269111</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.07430598264733</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9581.306293118661</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-625.9814401083736</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.90864635234706e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9478747392038033</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104.567</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7616505207953969</v>
+      </c>
+      <c r="D31" t="n">
+        <v>380.9897368904705</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3179182969870041</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.36074e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.798</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2455771177932837</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.285528780662506</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.487630330881704</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.411307495256704</v>
+      </c>
+      <c r="L31" t="n">
+        <v>21.49312924628606</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.04101803178727</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.34612417454283</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9607.697271928855</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>117.4510308657245</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.459807414149358e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9983568041878775</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102.786</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7486779809163088</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1328.809283346351</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.108829827884427</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.36079e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.855</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3964586916917593</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.195324931905536</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.286015989682812</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.996566733479924</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.60167961514784</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.08380951057404</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.63050628420563</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9635.946465106061</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-712.0705753149591</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.888682204305977e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9494278332461855</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98.75400000000002</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7193094908587665</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1401.22912847083</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.169260835863668</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.36102e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.90300000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2749191033792211</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.011234613546258</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.186659958345635</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.831192492374423</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21.70626785086153</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.09040828442785</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19.67510395075628</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9513.390534011367</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-780.2310817053838</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.862969646006185e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9999393712832486</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>94.11799999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6855415543739531</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1440.981318098479</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.202432197725208</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.36091e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.95699999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.01402474631829343</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7259683539709454</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.305702576634166</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.008124399739439</v>
+      </c>
+      <c r="L34" t="n">
+        <v>21.91898671473949</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.09265344524387</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.69032393829497</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9371.071786548766</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-821.421532569165</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.870885169653327e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9508947121992659</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93.03299999999996</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6776385752786072</v>
+      </c>
+      <c r="D35" t="n">
+        <v>281.5686994245898</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2349560440564988</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.36096e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.98999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1276273139326751</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.97281382720262</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.023885340001792</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.965798654623943</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.9057053413802</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.1168705858537</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.8559978885862</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-9344.808101891927</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>213.3900148748561</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.983471637692719e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9902020093365473</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91.27699999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6648481316920388</v>
+      </c>
+      <c r="D36" t="n">
+        <v>278.1202783703171</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2320784963361419</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.36134e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.047</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3171604229391747</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.07774233328126</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.361017719402256</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.354861910623639</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22.19928480095127</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.15933099306569</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.15328987989476</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-9375.785307874887</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>207.587046571055</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.562949320106654e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9989878327730087</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87.447</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6369509796780539</v>
+      </c>
+      <c r="D37" t="n">
+        <v>263.1534052097318</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2195893335957774</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.36277e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.07899999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1642306698301901</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9509172450193797</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.238658214971963</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.288497415177595</v>
+      </c>
+      <c r="L37" t="n">
+        <v>22.18211336701598</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.15305956671632</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>20.108821981592</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9210.873821406965</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>212.6977760004465</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.60558896207303e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9973081272803079</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86.803</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.632260179182752</v>
+      </c>
+      <c r="D38" t="n">
+        <v>256.8576000075838</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2143357756276155</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.36349e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.11799999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3621367603538769</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.082851335200883</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.455579958915111</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.554513852731096</v>
+      </c>
+      <c r="L38" t="n">
+        <v>22.29152202334002</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.19294677907739</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.39502863661771</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9244.894357243344</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>207.6404455474678</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.530080454894363e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9990356988378672</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>82.68099999999998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6022361424721393</v>
+      </c>
+      <c r="D39" t="n">
+        <v>253.1453726768919</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2112380937828642</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.36447e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.16800000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.07417774993210335</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6368461158630987</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.116471346194173</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.793055141053359</v>
+      </c>
+      <c r="L39" t="n">
+        <v>22.373754174085</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.19227593676838</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.39014789756453</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9094.909101556685</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>204.7857426799792</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.494893865628354e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9996318852689394</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>82.83499999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6033578556340593</v>
+      </c>
+      <c r="D40" t="n">
+        <v>250.0603000225821</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2086637434805586</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.36478e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.20399999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4275165735261316</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.292831339362761</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.511314984415803</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.224326081744509</v>
+      </c>
+      <c r="L40" t="n">
+        <v>22.48078785035523</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.24495352083824</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.78063461813544</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9187.541307310519</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>211.2823208650893</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.787747176745048e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.997586681616108</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>81.00900000000001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5900575424284364</v>
+      </c>
+      <c r="D41" t="n">
+        <v>246.8292855175999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2059676114604471</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.36544e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.238</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.505567439057852</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.266764738297561</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.749316943150072</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.843899924969643</v>
+      </c>
+      <c r="L41" t="n">
+        <v>22.60127559401313</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.25628889508883</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.86661998500331</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9111.269712031131</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>202.8611118469443</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.61009624832326e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9987113277099234</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79.14699999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.576495010561585</v>
+      </c>
+      <c r="D42" t="n">
+        <v>241.9780207568798</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.2019194556136542</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.36603e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.271</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5309342504509555</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.308301696325595</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.572363745696753</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.203528694615589</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22.6016576617577</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.27619462846373</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.01934702871606</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9078.588658721843</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>209.6762052692786</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.85265057613666e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9982259224856607</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78.04400000000004</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5684609221356257</v>
+      </c>
+      <c r="D43" t="n">
+        <v>237.8895948923308</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.198507853509032</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.3662e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.301</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7540155135865494</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.386026435887621</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.83857827464217</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.877575967946975</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22.69201878714392</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.29618691802891</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21.17499992964578</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9055.588524306166</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>212.0365509999505</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.035434608890816e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9968991506577087</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.5979811960485171</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>132.198</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1230.365611655943</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.48587e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-81.322</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1522952004524268</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9707985009277427</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.094954644884572</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.581260975455717</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.05934187865892</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.02918359955979</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.561208770010582</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5125.45594776426</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-567.53379819311</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.97948087298246e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.999999213679143</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>121.381</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9181757666530507</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1115.865576850893</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.906938202985903</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.4166e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.672</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7493128319177687</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.941343027615481</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.479607125652862</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.16771714433503</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.09342005273813</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.643746121247</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7701.821708693514</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-487.932790687635</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.181598486608101e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9336117382660001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>117.897</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8918213588707848</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1142.531257360227</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9286111758459339</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.40262e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.233</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.282484200710549</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.118964661918477</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.376067775135447</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.040657739720026</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18.86094483220467</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.60220700984418</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.84287355208352</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8738.453666687641</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-520.6135161504492</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.061608372826926e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9406617542949743</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>112.633</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8520022995809317</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1206.558043707127</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9806500053941092</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.39783e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.511</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2622528604492774</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.111887112376603</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.283128864914738</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.923594446904668</v>
+      </c>
+      <c r="L15" t="n">
+        <v>20.20088428656643</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.81700727223844</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17.98207848188511</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9151.082280136625</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-584.0470569052579</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.005989739130881e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9442940925952736</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107.253</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.811305768619798</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1316.998019769155</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.070411922515141</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.39562e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.69</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2945883825148151</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9762829560378943</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.311597773655121</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.621600016044733</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21.06686723279877</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.94560410174707</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18.74069219158655</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9348.650045344886</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-687.9314388155047</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.97140394558811e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9467047746450715</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102.761</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7773264345905387</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1454.155556538794</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.181888978985403</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.39515e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.836</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2988381937997537</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.276094195623116</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.441256422833471</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.034837395979847</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.87021715013726</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.05300945687455</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19.42498420527015</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9503.690102312696</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-816.816402943113</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.008013279205159e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9992962544183825</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96.03199999999998</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7264255132452836</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1469.790597389738</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.194596617026343</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.39503e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.959</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.08351811103036726</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7083054018467531</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.969724649697181</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.655505784152161</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22.38378679168592</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.09272163989831</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>19.69078659868019</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-9405.70016972862</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-841.0392125271376</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.924431853210026e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9503222146828666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>94.892</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7178020847516605</v>
+      </c>
+      <c r="D19" t="n">
+        <v>588.0509627066397</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4779481457671631</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.39566e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-85.05500000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.556857447700721</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.388148968740496</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.409800112945712</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.790124384708069</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.9193021905932</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.1982615453858</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>20.43377896695346</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9633.690206354831</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.040788677953959</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.181910437226049e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.5874964331123401</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90.32500000000005</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6832554199004528</v>
+      </c>
+      <c r="D20" t="n">
+        <v>575.3398436610039</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4676169735324906</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.39635e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-85.152</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.384354701182811</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.319257943815123</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.536554187188836</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.355619648522989</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23.51931048151438</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.24952107295046</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>20.81519695331701</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9636.609214677765</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.7166952147494591</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.727652165713491e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.5990129283558633</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87.31099999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6604562852690661</v>
+      </c>
+      <c r="D21" t="n">
+        <v>568.24911844516</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4618538693391764</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.39687e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-85.21899999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5255122293785485</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.383280383699607</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.502282760836736</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.546782106764319</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.94725421003658</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.29825037858569</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21.19119635597688</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-9670.766551158607</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.7869542216427844</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.811923761107804e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.5979811960485171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
